--- a/outputs/results/12b/results_12b_final.xlsx
+++ b/outputs/results/12b/results_12b_final.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U85"/>
+  <dimension ref="A1:W85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -552,49 +562,55 @@
         <v>0.125</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1831758483242265</v>
+        <v>0.1837752887737757</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09122389628104793</v>
+        <v>0.8210624144715146</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>0.0949516375392184</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2222222222222222</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2916666666666667</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08750000000000001</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05833333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02916666666666667</v>
+        <v>0.75</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -617,55 +633,61 @@
         <v>2001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.875</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0561472351020488</v>
+        <v>0.05718204291103608</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2823529411764706</v>
+        <v>0.4519146799592487</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>0.2672788676115457</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0375</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="T3" t="n">
-        <v>0.025</v>
+        <v>0.92</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0125</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -688,55 +710,61 @@
         <v>2001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.875</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="F4" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G4" t="n">
-        <v>0.121742770075798</v>
+        <v>0.1326147019863129</v>
       </c>
       <c r="H4" t="n">
-        <v>0.522675633430481</v>
+        <v>0.7141602635383606</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>0.5328157544136047</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O4" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T4" t="n">
         <v>0.88</v>
       </c>
-      <c r="S4" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.025</v>
-      </c>
       <c r="U4" t="n">
-        <v>0.0125</v>
+        <v>0.725</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9083333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -759,55 +787,61 @@
         <v>2001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.25</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1600052361472709</v>
+        <v>0.1352161349405697</v>
       </c>
       <c r="H5" t="n">
-        <v>1.300705435871653e-07</v>
+        <v>0.6252888313685369</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>0.5511728401087567</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.075</v>
+        <v>0.125</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05</v>
+        <v>0.84</v>
       </c>
       <c r="U5" t="n">
-        <v>0.025</v>
+        <v>0.7374999999999999</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.8250000000000001</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9125</v>
       </c>
     </row>
     <row r="6">
@@ -830,55 +864,61 @@
         <v>2001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8958333333333333</v>
+        <v>0.375</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2121169116598058</v>
+        <v>0.1652340273646639</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9068219633943428</v>
+        <v>0.5276073619631904</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2857142857142857</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0625</v>
+        <v>0.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.72</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02083333333333334</v>
+        <v>0.7749999999999999</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.925</v>
       </c>
     </row>
     <row r="7">
@@ -901,55 +941,61 @@
         <v>2001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="F7" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.08257389515823275</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.003082405039805831</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.002327620718404498</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>18</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>0.25</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.1102600918006365</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.009680070421468673</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>21</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.0375</v>
-      </c>
       <c r="T7" t="n">
-        <v>0.025</v>
+        <v>0.72</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0125</v>
+        <v>0.7749999999999999</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.925</v>
       </c>
     </row>
     <row r="8">
@@ -972,55 +1018,61 @@
         <v>2002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5833333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4300547054110133</v>
+        <v>0.4630188952615621</v>
       </c>
       <c r="H8" t="n">
-        <v>0.663812004632659</v>
+        <v>0.0949516375392184</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>0.6719212714825128</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.08</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.125</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08333333333333334</v>
+        <v>0.08</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.2875</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1916666666666667</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.09583333333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1049,49 +1101,55 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0451054236909176</v>
+        <v>0.05686623667260197</v>
       </c>
       <c r="H9" t="n">
-        <v>0.545790035283727</v>
+        <v>0.2672788676115457</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.5448839738417572</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.05</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.01666666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -1114,55 +1172,61 @@
         <v>2002</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07728493958711624</v>
+        <v>0.0906388983130455</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6937016248703003</v>
+        <v>0.5328157544136047</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.5814501643180847</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.025</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.008333333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -1185,55 +1249,61 @@
         <v>2002</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5833333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4616694834296106</v>
+        <v>0.4631126446785032</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7417925436734171</v>
+        <v>0.5511728401087567</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>0.6635875145711901</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>14</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.125</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.125</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08333333333333334</v>
+        <v>0.44</v>
       </c>
       <c r="U11" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.175</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1166666666666667</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.05833333333333334</v>
       </c>
     </row>
     <row r="12">
@@ -1265,46 +1335,52 @@
         <v>0.2130889204417722</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.8425925925925926</v>
       </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.25</v>
+        <v>0.04</v>
       </c>
       <c r="R12" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.075</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="U12" t="n">
-        <v>0.025</v>
+        <v>0.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="13">
@@ -1327,55 +1403,61 @@
         <v>2002</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7916666666666666</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05070693633000434</v>
+        <v>0.069692950398791</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2072573464424945</v>
+        <v>0.002327620718404498</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>0.4485861228052856</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.04</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.04</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02083333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
@@ -1398,56 +1480,32 @@
         <v>2008</v>
       </c>
       <c r="E14" t="n">
-        <v>0.375</v>
+        <v>0.3611111111111112</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5865063598710034</v>
+        <v>0.5764741980828433</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5098728236500527</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.0003426246448590228</v>
-      </c>
-      <c r="I14" t="n">
-        <v>16</v>
-      </c>
+        <v>0.5619095848567998</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.0009144036573601353</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1469,56 +1527,32 @@
         <v>2008</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4895833333333334</v>
+        <v>0.4756944444444444</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6179359243697479</v>
+        <v>0.6194642857142857</v>
       </c>
       <c r="G15" t="n">
-        <v>0.614984</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>16</v>
-      </c>
+        <v>0.626464</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>9</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1543,53 +1577,29 @@
         <v>0.4861111111111111</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6229916121460238</v>
+        <v>0.6206570537473923</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6358895897865295</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.001354562235064805</v>
-      </c>
-      <c r="I16" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6481840014457703</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.1777777777777778</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.08888888888888889</v>
-      </c>
+        <v>0.001618588343262672</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1611,56 +1621,32 @@
         <v>2008</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3402777777777778</v>
+        <v>0.3611111111111112</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5710335514294451</v>
+        <v>0.624083019322663</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5908596673905517</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4.568221092737065e-05</v>
-      </c>
-      <c r="I17" t="n">
-        <v>16</v>
-      </c>
+        <v>0.5635373478723227</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.1</v>
-      </c>
+        <v>1.552788756768869e-05</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1682,56 +1668,32 @@
         <v>2008</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.3645833333333334</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6124999999999999</v>
+        <v>0.615625</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6832927615033462</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6571553263241421</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>9</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1753,56 +1715,32 @@
         <v>2008</v>
       </c>
       <c r="E19" t="n">
-        <v>0.625</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7252919333082377</v>
+        <v>0.6584886920845453</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6126608297603905</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.421227358443719e-05</v>
-      </c>
-      <c r="I19" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6298669869849081</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.8205128205128205</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.6956521739130435</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.2333333333333333</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.1555555555555556</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.07777777777777778</v>
-      </c>
+        <v>6.824587925004975e-06</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1824,55 +1762,61 @@
         <v>2009</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7714425555618011</v>
+        <v>0.8020515652433222</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2205441333509373</v>
+        <v>0.1784110993291389</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4414598957633341</v>
+        <v>0.0009144036573601353</v>
       </c>
       <c r="I20" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4079443559646846</v>
+      </c>
+      <c r="K20" t="n">
         <v>16</v>
       </c>
-      <c r="J20" t="n">
-        <v>7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8205128205128205</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="R20" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2333333333333333</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="21">
@@ -1895,54 +1839,60 @@
         <v>2009</v>
       </c>
       <c r="E21" t="n">
-        <v>0.638888888888889</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7317536450645719</v>
+        <v>0.6785398287596177</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2655584566128624</v>
+        <v>0.284846956564098</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1642315720101805</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.2819618495135074</v>
+      </c>
+      <c r="K21" t="n">
         <v>16</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
         <v>0.64</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
       <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
         <v>0.64</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.3</v>
       </c>
-      <c r="T21" t="n">
+      <c r="V21" t="n">
         <v>0.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1966,55 +1916,61 @@
         <v>2009</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.611111111111111</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6546819959044223</v>
+        <v>0.6983957102287714</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3714910447597504</v>
+        <v>0.3982347846031189</v>
       </c>
       <c r="H22" t="n">
-        <v>0.02352490834891796</v>
+        <v>0.001618588343262672</v>
       </c>
       <c r="I22" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.003841368714347482</v>
+      </c>
+      <c r="K22" t="n">
         <v>16</v>
       </c>
-      <c r="J22" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8421052631578947</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.8</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="R22" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.68</v>
       </c>
       <c r="U22" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.1777777777777778</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.08888888888888889</v>
       </c>
     </row>
     <row r="23">
@@ -2037,55 +1993,61 @@
         <v>2009</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7444331219806763</v>
+        <v>0.6133417791527059</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2369984395980911</v>
+        <v>0.524148169290532</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4310298584365538</v>
+        <v>1.552788756768869e-05</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J23" t="n">
+        <v>7.971823237396175e-09</v>
+      </c>
+      <c r="K23" t="n">
+        <v>14</v>
+      </c>
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>2</v>
       </c>
-      <c r="M23" t="n">
-        <v>0.8205128205128205</v>
-      </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7567567567567568</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="Q23" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="S23" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="R23" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.2333333333333333</v>
-      </c>
       <c r="T23" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.3208333333333333</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.1902777777777778</v>
       </c>
     </row>
     <row r="24">
@@ -2108,54 +2070,60 @@
         <v>2009</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6458333333333333</v>
+        <v>0.4583333333333334</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7511458333333333</v>
+        <v>0.6228571428571428</v>
       </c>
       <c r="G24" t="n">
-        <v>0.313669502135048</v>
+        <v>0.6</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>16</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>9</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
         <v>0.64</v>
       </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
       <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
         <v>0.64</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.3</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.2</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2179,54 +2147,60 @@
         <v>2009</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5347222222222222</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6462810453435454</v>
+        <v>0.6659958501251071</v>
       </c>
       <c r="G25" t="n">
-        <v>0.482497914375094</v>
+        <v>0.5065050409424113</v>
       </c>
       <c r="H25" t="n">
-        <v>6.802663028485531e-06</v>
+        <v>6.824587925004975e-06</v>
       </c>
       <c r="I25" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.001587236476027979</v>
+      </c>
+      <c r="K25" t="n">
         <v>16</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>9</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
         <v>0.64</v>
       </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
       <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
         <v>0.64</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.3</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.2</v>
       </c>
-      <c r="U25" t="n">
+      <c r="W25" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2250,55 +2224,61 @@
         <v>2010</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5933333333333333</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6009764796606901</v>
+        <v>0.5070797258297258</v>
       </c>
       <c r="G26" t="n">
-        <v>0.462651516315676</v>
+        <v>0.4625613492751702</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8357399084843402</v>
+        <v>0.4079443559646846</v>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>2009</v>
       </c>
       <c r="J26" t="n">
+        <v>0.9749481715862276</v>
+      </c>
+      <c r="K26" t="n">
         <v>10</v>
       </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6206896551724138</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.27</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2133333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1566666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="27">
@@ -2321,55 +2301,61 @@
         <v>2010</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4466666666666667</v>
       </c>
       <c r="F27" t="n">
-        <v>0.42589508530685</v>
+        <v>0.3941454125509853</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3533496577136402</v>
+        <v>0.2706002752399383</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3205606899313307</v>
+        <v>0.2819618495135074</v>
       </c>
       <c r="I27" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5307970336483052</v>
+      </c>
+      <c r="K27" t="n">
         <v>10</v>
       </c>
-      <c r="J27" t="n">
-        <v>15</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>0.4</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.3</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1</v>
+        <v>0.28</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="28">
@@ -2392,55 +2378,61 @@
         <v>2010</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.5733333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4799596157719728</v>
+        <v>0.4927841012280371</v>
       </c>
       <c r="G28" t="n">
-        <v>0.376446545124054</v>
+        <v>0.2801659405231476</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09784837067127228</v>
+        <v>0.003841368714347482</v>
       </c>
       <c r="I28" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.01625379361212254</v>
+      </c>
+      <c r="K28" t="n">
         <v>10</v>
       </c>
-      <c r="J28" t="n">
-        <v>13</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6060606060606061</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1733333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U28" t="n">
-        <v>0.08666666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="29">
@@ -2463,55 +2455,61 @@
         <v>2010</v>
       </c>
       <c r="E29" t="n">
-        <v>0.62</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6987895256916996</v>
+        <v>0.6375876411170528</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4097468804483028</v>
+        <v>0.2710999361432416</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9936514111704592</v>
+        <v>7.971823237396175e-09</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>2009</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.03993485121265434</v>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L29" t="n">
         <v>14</v>
       </c>
       <c r="M29" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R29" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.37</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T29" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="U29" t="n">
-        <v>0.4566666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="30">
@@ -2534,54 +2532,60 @@
         <v>2010</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4533333333333333</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3768990658464343</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4962243253487426</v>
+        <v>0.3040523629748155</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.6315789473684211</v>
+      </c>
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2010</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5147823734236777</v>
+        <v>0.6002505827505827</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4018680147158371</v>
+        <v>0.2876569461831974</v>
       </c>
       <c r="H31" t="n">
-        <v>0.001111154599566572</v>
+        <v>0.001587236476027979</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J31" t="n">
-        <v>13</v>
+        <v>0.01743351022927634</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L31" t="n">
+        <v>7</v>
+      </c>
+      <c r="M31" t="n">
         <v>2</v>
       </c>
-      <c r="M31" t="n">
-        <v>0.6060606060606061</v>
-      </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.64</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="R31" t="n">
-        <v>0.48</v>
+        <v>0.2</v>
       </c>
       <c r="S31" t="n">
-        <v>0.26</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1733333333333333</v>
+        <v>0.64</v>
       </c>
       <c r="U31" t="n">
-        <v>0.08666666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.2266666666666667</v>
       </c>
     </row>
     <row r="32">
@@ -2679,52 +2689,58 @@
         <v>0.7933333333333333</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8018414918414918</v>
+        <v>0.7671717171717171</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2288056604495035</v>
+        <v>0.2209145478782308</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5207668870685651</v>
+        <v>0.9749481715862276</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>0.5108381158978048</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.72</v>
+        <v>10</v>
       </c>
       <c r="N32" t="n">
+        <v>15</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W32" t="n">
         <v>0.9</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.13</v>
       </c>
     </row>
     <row r="33">
@@ -2747,55 +2763,61 @@
         <v>2011</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.76</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7308333333333333</v>
+        <v>0.7245545682387787</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2267831049810215</v>
+        <v>0.216291258520259</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5640755320597821</v>
+        <v>0.5307970336483052</v>
       </c>
       <c r="I33" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.5374323181892141</v>
+      </c>
+      <c r="K33" t="n">
         <v>8</v>
       </c>
-      <c r="J33" t="n">
-        <v>4</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
+        <v>5</v>
+      </c>
+      <c r="M33" t="n">
         <v>2</v>
       </c>
-      <c r="L33" t="n">
-        <v>11</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.7272727272727273</v>
-      </c>
       <c r="N33" t="n">
+        <v>10</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="P33" t="n">
         <v>0.8</v>
       </c>
-      <c r="O33" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="R33" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.76</v>
-      </c>
       <c r="S33" t="n">
-        <v>0.22</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T33" t="n">
-        <v>0.2133333333333334</v>
+        <v>0.72</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2066666666666667</v>
+        <v>0.24</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.2133333333333333</v>
       </c>
     </row>
     <row r="34">
@@ -2818,55 +2840,61 @@
         <v>2011</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8733333333333333</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8384099672257567</v>
+        <v>0.7008848994143112</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1533974409103394</v>
+        <v>0.2054103314876556</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5449708700180054</v>
+        <v>0.01625379361212254</v>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>0.5462316870689392</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L34" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V34" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.1933333333333334</v>
+      <c r="W34" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="35">
@@ -2889,55 +2917,61 @@
         <v>2011</v>
       </c>
       <c r="E35" t="n">
-        <v>0.76</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7557448107448107</v>
+        <v>0.5438706945228684</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2243169500719387</v>
+        <v>0.3425772878472221</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8917110644340588</v>
+        <v>0.03993485121265434</v>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>2010</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>2.364437221973575e-32</v>
       </c>
       <c r="K35" t="n">
         <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7368421052631579</v>
+        <v>7</v>
       </c>
       <c r="N35" t="n">
-        <v>0.7</v>
+        <v>11</v>
       </c>
       <c r="O35" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="P35" t="n">
         <v>0.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="R35" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S35" t="n">
-        <v>0.25</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="T35" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U35" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.57</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.6133333333333333</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.6566666666666666</v>
       </c>
     </row>
     <row r="36">
@@ -2960,55 +2994,61 @@
         <v>2011</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.59</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5181818181818181</v>
+        <v>0.4894083694083695</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3262565966005779</v>
+        <v>0.3571700515707979</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5384615384615385</v>
+        <v>0.6315789473684211</v>
       </c>
       <c r="I36" t="n">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="J36" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L36" t="n">
+        <v>11</v>
+      </c>
+      <c r="M36" t="n">
         <v>3</v>
       </c>
-      <c r="M36" t="n">
-        <v>0.625</v>
-      </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O36" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.8</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="R36" t="n">
-        <v>0.52</v>
+        <v>0.3</v>
       </c>
       <c r="S36" t="n">
-        <v>0.24</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T36" t="n">
-        <v>0.16</v>
+        <v>0.44</v>
       </c>
       <c r="U36" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.4299999999999999</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.3866666666666667</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.3433333333333334</v>
       </c>
     </row>
     <row r="37">
@@ -3031,55 +3071,61 @@
         <v>2011</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8600000000000001</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8255483405483405</v>
+        <v>0.7773809523809524</v>
       </c>
       <c r="G37" t="n">
-        <v>0.175041012584231</v>
+        <v>0.1737954800058087</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5896137652913739</v>
+        <v>0.01743351022927634</v>
       </c>
       <c r="I37" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0.4153172933096386</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L37" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W37" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.1066666666666667</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.1033333333333333</v>
       </c>
     </row>
     <row r="38">
@@ -3102,55 +3148,61 @@
         <v>2012</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8057792207792207</v>
+        <v>0.75</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1820026267412815</v>
+        <v>0.2361064549746338</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4569239996556106</v>
+        <v>0.5108381158978048</v>
       </c>
       <c r="I38" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J38" t="n">
-        <v>6</v>
+        <v>0.5240026642695688</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M38" t="n">
-        <v>0.72</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="O38" t="n">
-        <v>0.6</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="P38" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.4</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="R38" t="n">
-        <v>0.72</v>
+        <v>0.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0.19</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T38" t="n">
-        <v>0.16</v>
+        <v>0.68</v>
       </c>
       <c r="U38" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.3066666666666666</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.3033333333333333</v>
       </c>
     </row>
     <row r="39">
@@ -3173,55 +3225,61 @@
         <v>2012</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8733333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8352480852480851</v>
+        <v>0.8687240047534165</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1579551269153233</v>
+        <v>0.1763819933850027</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4118244893895048</v>
+        <v>0.5374323181892141</v>
       </c>
       <c r="I39" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.7497572668767879</v>
+      </c>
+      <c r="K39" t="n">
+        <v>8</v>
+      </c>
+      <c r="L39" t="n">
+        <v>5</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" t="n">
         <v>10</v>
       </c>
-      <c r="J39" t="n">
-        <v>5</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>10</v>
-      </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="P39" t="n">
         <v>0.8</v>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
       <c r="Q39" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S39" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="R39" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0.09999999999999999</v>
-      </c>
       <c r="T39" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.72</v>
       </c>
       <c r="U39" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.24</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.2133333333333333</v>
       </c>
     </row>
     <row r="40">
@@ -3244,55 +3302,61 @@
         <v>2012</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.92</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8566766566766565</v>
+        <v>0.9156746031746031</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1541679799556732</v>
+        <v>0.1641838252544403</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5303398370742798</v>
+        <v>0.5462316870689392</v>
       </c>
       <c r="I40" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.8055983185768127</v>
+      </c>
+      <c r="K40" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" t="n">
+        <v>5</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2</v>
+      </c>
+      <c r="N40" t="n">
         <v>10</v>
       </c>
-      <c r="J40" t="n">
-        <v>4</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>11</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
       <c r="O40" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="R40" t="n">
-        <v>0.84</v>
+        <v>0.2</v>
       </c>
       <c r="S40" t="n">
-        <v>0.08</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T40" t="n">
-        <v>0.05333333333333334</v>
+        <v>0.72</v>
       </c>
       <c r="U40" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.24</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.2133333333333333</v>
       </c>
     </row>
     <row r="41">
@@ -3315,55 +3379,61 @@
         <v>2012</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8432792207792207</v>
+        <v>0.7897493734335839</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2891520057757666</v>
+        <v>0.2092937418944866</v>
       </c>
       <c r="H41" t="n">
-        <v>0.03280988250236398</v>
+        <v>2.364437221973575e-32</v>
       </c>
       <c r="I41" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.6612289648645705</v>
+      </c>
+      <c r="K41" t="n">
         <v>10</v>
       </c>
-      <c r="J41" t="n">
-        <v>6</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7692307692307693</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
         <v>0.4</v>
       </c>
       <c r="R41" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="U41" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="42">
@@ -3386,55 +3456,61 @@
         <v>2012</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6633333333333333</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4930515236397589</v>
+        <v>0.6319841269841271</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3505251175127529</v>
+        <v>0.2318163445234452</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8549222797927462</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J42" t="n">
-        <v>8</v>
+        <v>0.6534653465346533</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L42" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W42" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="43">
@@ -3457,55 +3533,61 @@
         <v>2012</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.92</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8709973798131693</v>
+        <v>0.9233386496544392</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1410939947454191</v>
+        <v>0.2104442303858727</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6244520695965369</v>
+        <v>0.4153172933096386</v>
       </c>
       <c r="I43" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.8622476211363272</v>
+      </c>
+      <c r="K43" t="n">
         <v>9</v>
       </c>
-      <c r="J43" t="n">
-        <v>2</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
       <c r="L43" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
+        <v>6</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="P43" t="n">
         <v>0.9</v>
       </c>
-      <c r="O43" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R43" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.88</v>
-      </c>
       <c r="S43" t="n">
-        <v>0.11</v>
+        <v>0.6</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1033333333333333</v>
+        <v>0.25</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="44">
@@ -3534,49 +3616,55 @@
         <v>0.25</v>
       </c>
       <c r="G44" t="n">
-        <v>0.09768099359929368</v>
+        <v>0.1001118270966074</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3962694950060163</v>
+        <v>0.8769114735537481</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>0.3882716514469505</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O44" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0375</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="T44" t="n">
-        <v>0.025</v>
+        <v>0.92</v>
       </c>
       <c r="U44" t="n">
-        <v>0.0125</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="45">
@@ -3605,49 +3693,55 @@
         <v>0.5</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02668565325738697</v>
+        <v>0.02568094616510423</v>
       </c>
       <c r="H45" t="n">
-        <v>0.270440251572327</v>
+        <v>0.17</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0.2955974842767295</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O45" t="n">
         <v>0.5</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R45" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0125</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T45" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="W45" t="n">
         <v>0.008333333333333333</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0.004166666666666667</v>
       </c>
     </row>
     <row r="46">
@@ -3676,49 +3770,55 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.008356071077287197</v>
+        <v>0.01243449095636606</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6254370808601379</v>
+        <v>0.01189725659787655</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.6932315826416016</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>24</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
@@ -3747,49 +3847,55 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="G47" t="n">
-        <v>0.06771062317752044</v>
+        <v>0.1521615514045577</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4054822920698812</v>
+        <v>0.9228123705048652</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>0.6043763648465391</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O47" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0.01666666666666667</v>
+        <v>0.96</v>
       </c>
       <c r="U47" t="n">
-        <v>0.008333333333333333</v>
+        <v>0.7</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="48">
@@ -3818,31 +3924,31 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.000292205420410548</v>
+        <v>0.0002922054204105488</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9145299145299146</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>0.9145299145299145</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" t="n">
         <v>24</v>
       </c>
-      <c r="M48" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -3857,10 +3963,16 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>0.7</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="49">
@@ -3889,49 +4001,55 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1195659958439588</v>
+        <v>0.03785656917453049</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0009349436569170327</v>
+        <v>0.6163617227386412</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>0.1569393154395376</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O49" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0.01666666666666667</v>
+        <v>0.96</v>
       </c>
       <c r="U49" t="n">
-        <v>0.008333333333333333</v>
+        <v>0.7</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="50">
@@ -3954,55 +4072,61 @@
         <v>2002</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4583333333333334</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="F50" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4757245492139788</v>
+        <v>0.5517436115420502</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5448897249792384</v>
+        <v>0.3882716514469505</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J50" t="n">
-        <v>13</v>
+        <v>0.5737301138455826</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O50" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.0625</v>
       </c>
       <c r="R50" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.1625</v>
+        <v>0.625</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1083333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U50" t="n">
-        <v>0.05416666666666667</v>
+        <v>0.1875</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.0625</v>
       </c>
     </row>
     <row r="51">
@@ -4031,49 +4155,55 @@
         <v>0.1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.07180640826809585</v>
+        <v>0.07784177100133775</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1848486033749054</v>
+        <v>0.2955974842767295</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J51" t="n">
-        <v>9</v>
+        <v>0.1582781192778938</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1818181818181818</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="O51" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.1125</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="T51" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="U51" t="n">
-        <v>0.03750000000000001</v>
+        <v>0.7875</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.8583333333333334</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.9291666666666667</v>
       </c>
     </row>
     <row r="52">
@@ -4096,55 +4226,61 @@
         <v>2002</v>
       </c>
       <c r="E52" t="n">
-        <v>0.04166666666666669</v>
+        <v>0.125</v>
       </c>
       <c r="F52" t="n">
-        <v>0.04</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1641695648431778</v>
+        <v>0.1680999398231506</v>
       </c>
       <c r="H52" t="n">
-        <v>0.05124238878488541</v>
+        <v>0.6932315826416016</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>0.02185294963419437</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M52" t="n">
-        <v>0.07692307692307693</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O52" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>0.3</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T52" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="U52" t="n">
-        <v>0.1</v>
+        <v>0.75</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="53">
@@ -4167,55 +4303,61 @@
         <v>2002</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4166666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="F53" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3957525842271876</v>
+        <v>0.4303482180943258</v>
       </c>
       <c r="H53" t="n">
-        <v>0.08635327756783583</v>
+        <v>0.6043763648465391</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J53" t="n">
-        <v>14</v>
+        <v>0.2298329451401089</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M53" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O53" t="n">
-        <v>0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.5833333333333334</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0.44</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>0.175</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="T53" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.52</v>
       </c>
       <c r="U53" t="n">
-        <v>0.05833333333333334</v>
+        <v>0.8374999999999999</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.8916666666666667</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.9458333333333333</v>
       </c>
     </row>
     <row r="54">
@@ -4247,46 +4389,52 @@
         <v>0.2126371912881646</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.9145299145299145</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J54" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M54" t="n">
-        <v>0.07692307692307693</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O54" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>0.3</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="T54" t="n">
-        <v>0.2</v>
+        <v>0.76</v>
       </c>
       <c r="U54" t="n">
-        <v>0.1</v>
+        <v>0.7625</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.8416666666666667</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.9208333333333334</v>
       </c>
     </row>
     <row r="55">
@@ -4309,55 +4457,61 @@
         <v>2002</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7083333333333333</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="F55" t="n">
-        <v>0.125</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1026603154118692</v>
+        <v>0.05753431607747595</v>
       </c>
       <c r="H55" t="n">
-        <v>0.03830964192992885</v>
+        <v>0.1569393154395376</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J55" t="n">
-        <v>7</v>
+        <v>1.163865151005052e-07</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2222222222222222</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O55" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.2916666666666667</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0.08750000000000001</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T55" t="n">
-        <v>0.05833333333333334</v>
+        <v>0.88</v>
       </c>
       <c r="U55" t="n">
-        <v>0.02916666666666667</v>
+        <v>0.725</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.9083333333333333</v>
       </c>
     </row>
     <row r="56">
@@ -4380,56 +4534,32 @@
         <v>2008</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.4930555555555556</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7461318204821494</v>
+        <v>0.6596023405941883</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5269514292019705</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.0004238894723492777</v>
-      </c>
-      <c r="I56" t="n">
-        <v>15</v>
-      </c>
+        <v>0.5949789787154234</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
-        <v>7</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" t="n">
-        <v>2</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.7894736842105263</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0.6818181818181818</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0.2770833333333333</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0.2055555555555555</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0.1340277777777778</v>
-      </c>
+        <v>2.095342901271278e-05</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4451,56 +4581,32 @@
         <v>2008</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.3923611111111111</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6829166666666667</v>
+        <v>0.6509523809523809</v>
       </c>
       <c r="G57" t="n">
-        <v>0.624008</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6271640000000001</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>9</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4522,56 +4628,32 @@
         <v>2008</v>
       </c>
       <c r="E58" t="n">
-        <v>0.5069444444444444</v>
+        <v>0.5659722222222222</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6754186246867168</v>
+        <v>0.7523041134590047</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6322618722915649</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.0005854230257682502</v>
-      </c>
-      <c r="I58" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6336380839347839</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
-        <v>9</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.001106431591324508</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4593,56 +4675,32 @@
         <v>2008</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4652777777777778</v>
+        <v>0.4305555555555556</v>
       </c>
       <c r="F59" t="n">
-        <v>0.663849557608938</v>
+        <v>0.6672386529799414</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5895138386480303</v>
-      </c>
-      <c r="H59" t="n">
-        <v>6.758511167435938e-06</v>
-      </c>
-      <c r="I59" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6022420672679568</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>9</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N59" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0.1</v>
-      </c>
+        <v>3.074629083628062e-05</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4672,48 +4730,24 @@
       <c r="G60" t="n">
         <v>0.64</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>16</v>
-      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>9</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4735,56 +4769,32 @@
         <v>2008</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4375</v>
+        <v>0.5069444444444444</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6164975491438087</v>
+        <v>0.6792103148077413</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6397414400281456</v>
-      </c>
-      <c r="H61" t="n">
-        <v>4.066190212334127e-07</v>
-      </c>
-      <c r="I61" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6389830189761644</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
-        <v>9</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0.1</v>
-      </c>
+        <v>8.103915832325728e-07</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4806,54 +4816,60 @@
         <v>2009</v>
       </c>
       <c r="E62" t="n">
-        <v>0.5902777777777778</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7317095736389214</v>
+        <v>0.6370509014012303</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4113046110193712</v>
+        <v>0.5073098927030608</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0009987528090520381</v>
+        <v>2.095342901271278e-05</v>
       </c>
       <c r="I62" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.001969129684745444</v>
+      </c>
+      <c r="K62" t="n">
         <v>16</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>9</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
       <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N62" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" t="n">
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
         <v>0.64</v>
       </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
       <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
         <v>0.64</v>
       </c>
-      <c r="S62" t="n">
+      <c r="U62" t="n">
         <v>0.3</v>
       </c>
-      <c r="T62" t="n">
+      <c r="V62" t="n">
         <v>0.2</v>
       </c>
-      <c r="U62" t="n">
+      <c r="W62" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4877,54 +4893,60 @@
         <v>2009</v>
       </c>
       <c r="E63" t="n">
-        <v>0.5208333333333333</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6383482142857142</v>
+        <v>0.6366281512605041</v>
       </c>
       <c r="G63" t="n">
-        <v>0.593212</v>
+        <v>0.6007399999999999</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>16</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>9</v>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
       <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N63" t="n">
-        <v>1</v>
-      </c>
-      <c r="O63" t="n">
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
         <v>0.64</v>
       </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>1</v>
-      </c>
       <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
         <v>0.64</v>
       </c>
-      <c r="S63" t="n">
+      <c r="U63" t="n">
         <v>0.3</v>
       </c>
-      <c r="T63" t="n">
+      <c r="V63" t="n">
         <v>0.2</v>
       </c>
-      <c r="U63" t="n">
+      <c r="W63" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4948,55 +4970,61 @@
         <v>2009</v>
       </c>
       <c r="E64" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.625</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6652778843057228</v>
+        <v>0.6911767766547178</v>
       </c>
       <c r="G64" t="n">
-        <v>0.6223048567771912</v>
+        <v>0.6291800141334534</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0006677798228338361</v>
+        <v>0.001106431591324508</v>
       </c>
       <c r="I64" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.002162893069908023</v>
+      </c>
+      <c r="K64" t="n">
         <v>16</v>
       </c>
-      <c r="J64" t="n">
-        <v>8</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M64" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R64" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U64" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="65">
@@ -5019,55 +5047,61 @@
         <v>2009</v>
       </c>
       <c r="E65" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.3680555555555556</v>
       </c>
       <c r="F65" t="n">
-        <v>0.6603090379935346</v>
+        <v>0.5839629882099847</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5095793659237123</v>
+        <v>0.6019778553220135</v>
       </c>
       <c r="H65" t="n">
-        <v>0.000106223273925163</v>
+        <v>3.074629083628062e-05</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J65" t="n">
+        <v>6.748776543523921e-07</v>
+      </c>
+      <c r="K65" t="n">
+        <v>15</v>
+      </c>
+      <c r="L65" t="n">
         <v>9</v>
       </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
       <c r="M65" t="n">
-        <v>0.7804878048780488</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="R65" t="n">
-        <v>0.64</v>
+        <v>0.0625</v>
       </c>
       <c r="S65" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="U65" t="n">
-        <v>0.1</v>
+        <v>0.34375</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0.15625</v>
       </c>
     </row>
     <row r="66">
@@ -5102,42 +5136,48 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>16</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>9</v>
       </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
       <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
         <v>0.64</v>
       </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1</v>
-      </c>
       <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
         <v>0.64</v>
       </c>
-      <c r="S66" t="n">
+      <c r="U66" t="n">
         <v>0.3</v>
       </c>
-      <c r="T66" t="n">
+      <c r="V66" t="n">
         <v>0.2</v>
       </c>
-      <c r="U66" t="n">
+      <c r="W66" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5161,55 +5201,61 @@
         <v>2009</v>
       </c>
       <c r="E67" t="n">
-        <v>0.6041666666666667</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6997313140076298</v>
+        <v>0.6596410192358082</v>
       </c>
       <c r="G67" t="n">
-        <v>0.6367494291863808</v>
+        <v>0.63989224017819</v>
       </c>
       <c r="H67" t="n">
-        <v>1.573236477062979e-05</v>
+        <v>8.103915832325728e-07</v>
       </c>
       <c r="I67" t="n">
-        <v>14</v>
+        <v>2008</v>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>1.074627012688665e-05</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="L67" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M67" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P67" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="R67" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.2541666666666667</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0.2111111111111111</v>
+        <v>0.64</v>
       </c>
       <c r="U67" t="n">
-        <v>0.1680555555555556</v>
+        <v>0.3</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="68">
@@ -5232,55 +5278,61 @@
         <v>2010</v>
       </c>
       <c r="E68" t="n">
-        <v>0.5800000000000001</v>
+        <v>0.3866666666666667</v>
       </c>
       <c r="F68" t="n">
-        <v>0.524963768115942</v>
+        <v>0.4275751041483307</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5030900380759665</v>
+        <v>0.5236534804223293</v>
       </c>
       <c r="H68" t="n">
-        <v>0.989730736166938</v>
+        <v>0.001969129684745444</v>
       </c>
       <c r="I68" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J68" t="n">
-        <v>7</v>
+        <v>0.01939288522046403</v>
       </c>
       <c r="K68" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L68" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M68" t="n">
-        <v>0.5833333333333334</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U68" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0.3166666666666667</v>
+      <c r="V68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="69">
@@ -5303,54 +5355,60 @@
         <v>2010</v>
       </c>
       <c r="E69" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F69" t="n">
-        <v>0.5287121212121212</v>
+        <v>0.4263427800269906</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3544079999999999</v>
+        <v>0.368104</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K69" t="n">
         <v>10</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>15</v>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
       <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N69" t="n">
-        <v>1</v>
-      </c>
-      <c r="O69" t="n">
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
         <v>0.4</v>
       </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>1</v>
-      </c>
       <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
         <v>0.4</v>
       </c>
-      <c r="S69" t="n">
+      <c r="U69" t="n">
         <v>0.3</v>
       </c>
-      <c r="T69" t="n">
+      <c r="V69" t="n">
         <v>0.2</v>
       </c>
-      <c r="U69" t="n">
+      <c r="W69" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5374,55 +5432,61 @@
         <v>2010</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4633333333333333</v>
+        <v>0.4066666666666667</v>
       </c>
       <c r="F70" t="n">
-        <v>0.451623661426293</v>
+        <v>0.4251940197408969</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3740614056587219</v>
+        <v>0.3805781602859497</v>
       </c>
       <c r="H70" t="n">
-        <v>0.002154259476810694</v>
+        <v>0.002162893069908023</v>
       </c>
       <c r="I70" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.001872273976914585</v>
+      </c>
+      <c r="K70" t="n">
         <v>9</v>
       </c>
-      <c r="J70" t="n">
-        <v>12</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1</v>
-      </c>
       <c r="L70" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M70" t="n">
-        <v>0.5806451612903226</v>
+        <v>1</v>
       </c>
       <c r="N70" t="n">
+        <v>2</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="P70" t="n">
         <v>0.9</v>
       </c>
-      <c r="O70" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="P70" t="n">
+      <c r="Q70" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="R70" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.48</v>
-      </c>
       <c r="S70" t="n">
-        <v>0.31</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T70" t="n">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="U70" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.1766666666666667</v>
       </c>
     </row>
     <row r="71">
@@ -5445,55 +5509,61 @@
         <v>2010</v>
       </c>
       <c r="E71" t="n">
-        <v>0.5733333333333334</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4579013143719026</v>
+        <v>0.3981077075098814</v>
       </c>
       <c r="G71" t="n">
-        <v>0.3738023318957465</v>
+        <v>0.4699142304037951</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1000664228085696</v>
+        <v>6.748776543523921e-07</v>
       </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J71" t="n">
-        <v>10</v>
+        <v>1.415329497931701e-15</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L71" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M71" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>0.5</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.375</v>
       </c>
       <c r="R71" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="S71" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.36</v>
       </c>
       <c r="U71" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.37</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="72">
@@ -5528,42 +5598,48 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>10</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>15</v>
       </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
       <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N72" t="n">
-        <v>1</v>
-      </c>
-      <c r="O72" t="n">
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
         <v>0.4</v>
       </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>1</v>
-      </c>
       <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
         <v>0.4</v>
       </c>
-      <c r="S72" t="n">
+      <c r="U72" t="n">
         <v>0.3</v>
       </c>
-      <c r="T72" t="n">
+      <c r="V72" t="n">
         <v>0.2</v>
       </c>
-      <c r="U72" t="n">
+      <c r="W72" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5587,55 +5663,61 @@
         <v>2010</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5533333333333332</v>
       </c>
       <c r="F73" t="n">
-        <v>0.3986367880485527</v>
+        <v>0.4893393596950603</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3995650544502595</v>
+        <v>0.3990590730759576</v>
       </c>
       <c r="H73" t="n">
-        <v>1.231026478560298e-05</v>
+        <v>1.074627012688665e-05</v>
       </c>
       <c r="I73" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1.57490417645354e-05</v>
+      </c>
+      <c r="K73" t="n">
         <v>10</v>
       </c>
-      <c r="J73" t="n">
-        <v>14</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M73" t="n">
-        <v>0.5882352941176471</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R73" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.28</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T73" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="U73" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.26</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
     <row r="74">
@@ -5658,55 +5740,61 @@
         <v>2011</v>
       </c>
       <c r="E74" t="n">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7347527706734868</v>
+        <v>0.7779166666666667</v>
       </c>
       <c r="G74" t="n">
-        <v>0.211632995105019</v>
+        <v>0.2060673812544923</v>
       </c>
       <c r="H74" t="n">
-        <v>0.290971252672042</v>
+        <v>0.01939288522046403</v>
       </c>
       <c r="I74" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J74" t="n">
-        <v>8</v>
+        <v>0.447406994974005</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L74" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M74" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W74" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T74" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="75">
@@ -5729,55 +5817,61 @@
         <v>2011</v>
       </c>
       <c r="E75" t="n">
-        <v>0.78</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7494857430151548</v>
+        <v>0.7307786576168929</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1893035912855366</v>
+        <v>0.1965791588189484</v>
       </c>
       <c r="H75" t="n">
-        <v>0.210067349666629</v>
+        <v>0.03</v>
       </c>
       <c r="I75" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.2341946798418972</v>
+      </c>
+      <c r="K75" t="n">
         <v>10</v>
       </c>
-      <c r="J75" t="n">
-        <v>8</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
       <c r="L75" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M75" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O75" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R75" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.16</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T75" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="U75" t="n">
-        <v>0.05333333333333334</v>
+        <v>0.26</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
     <row r="76">
@@ -5800,55 +5894,61 @@
         <v>2011</v>
       </c>
       <c r="E76" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.7133333333333334</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7159967320261438</v>
+        <v>0.5968577694235588</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2143297344446182</v>
+        <v>0.2553968727588654</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1742832213640213</v>
+        <v>0.001872273976914585</v>
       </c>
       <c r="I76" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J76" t="n">
-        <v>4</v>
+        <v>0.1241690367460251</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L76" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M76" t="n">
-        <v>0.7272727272727273</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P76" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R76" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.22</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T76" t="n">
-        <v>0.2133333333333334</v>
+        <v>0.44</v>
       </c>
       <c r="U76" t="n">
-        <v>0.2066666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="77">
@@ -5871,55 +5971,61 @@
         <v>2011</v>
       </c>
       <c r="E77" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.7133333333333334</v>
       </c>
       <c r="F77" t="n">
-        <v>0.7341033966033966</v>
+        <v>0.7294896331738437</v>
       </c>
       <c r="G77" t="n">
-        <v>0.2545645512652898</v>
+        <v>0.2352421144192041</v>
       </c>
       <c r="H77" t="n">
-        <v>0.01054320016443355</v>
+        <v>1.415329497931701e-15</v>
       </c>
       <c r="I77" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.4453078580273849</v>
+      </c>
+      <c r="K77" t="n">
         <v>10</v>
       </c>
-      <c r="J77" t="n">
-        <v>6</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
       <c r="L77" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7692307692307693</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
         <v>0.4</v>
       </c>
       <c r="R77" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="T77" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="U77" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="78">
@@ -5954,42 +6060,48 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
         <v>10</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>15</v>
       </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
       <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N78" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" t="n">
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
         <v>0.4</v>
       </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
       <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
         <v>0.4</v>
       </c>
-      <c r="S78" t="n">
+      <c r="U78" t="n">
         <v>0.3</v>
       </c>
-      <c r="T78" t="n">
+      <c r="V78" t="n">
         <v>0.2</v>
       </c>
-      <c r="U78" t="n">
+      <c r="W78" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -6013,55 +6125,61 @@
         <v>2011</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.76</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8217748917748917</v>
+        <v>0.6730863499245852</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3115666961237586</v>
+        <v>0.2516934821294198</v>
       </c>
       <c r="H79" t="n">
-        <v>0.001923026225120567</v>
+        <v>1.57490417645354e-05</v>
       </c>
       <c r="I79" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>0.06854964202330634</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L79" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M79" t="n">
-        <v>0.8181818181818182</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>0.75</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W79" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0.11</v>
       </c>
     </row>
     <row r="80">
@@ -6084,55 +6202,61 @@
         <v>2012</v>
       </c>
       <c r="E80" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7755602240896359</v>
+        <v>0.7404636591478696</v>
       </c>
       <c r="G80" t="n">
-        <v>0.244125149440979</v>
+        <v>0.2394207846867531</v>
       </c>
       <c r="H80" t="n">
-        <v>0.495036289551843</v>
+        <v>0.447406994974005</v>
       </c>
       <c r="I80" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J80" t="n">
-        <v>8</v>
+        <v>0.489493666697623</v>
       </c>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L80" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M80" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W80" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U80" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="81">
@@ -6155,55 +6279,61 @@
         <v>2012</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9187698412698412</v>
+        <v>0.8720634920634921</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1436554446475785</v>
+        <v>0.1663972369925553</v>
       </c>
       <c r="H81" t="n">
-        <v>0.4495479177068525</v>
+        <v>0.2341946798418972</v>
       </c>
       <c r="I81" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0.5581117732067187</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L81" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M81" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="O81" t="n">
-        <v>0.9</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="P81" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R81" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.09</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T81" t="n">
-        <v>0.09333333333333335</v>
+        <v>0.48</v>
       </c>
       <c r="U81" t="n">
-        <v>0.09666666666666668</v>
+        <v>0.26</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
     <row r="82">
@@ -6226,55 +6356,61 @@
         <v>2012</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9503174603174603</v>
+        <v>0.8473856209150327</v>
       </c>
       <c r="G82" t="n">
-        <v>0.09549164026975632</v>
+        <v>0.1419651061296463</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3973187506198883</v>
+        <v>0.1241690367460251</v>
       </c>
       <c r="I82" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.7221187949180603</v>
+      </c>
+      <c r="K82" t="n">
         <v>9</v>
       </c>
-      <c r="J82" t="n">
-        <v>1</v>
-      </c>
-      <c r="K82" t="n">
-        <v>1</v>
-      </c>
       <c r="L82" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M82" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" t="n">
+        <v>6</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="P82" t="n">
         <v>0.9</v>
       </c>
-      <c r="N82" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P82" t="n">
+      <c r="Q82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R82" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0.92</v>
-      </c>
       <c r="S82" t="n">
-        <v>0.09</v>
+        <v>0.6</v>
       </c>
       <c r="T82" t="n">
-        <v>0.09333333333333335</v>
+        <v>0.6</v>
       </c>
       <c r="U82" t="n">
-        <v>0.09666666666666668</v>
+        <v>0.25</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="83">
@@ -6297,55 +6433,61 @@
         <v>2012</v>
       </c>
       <c r="E83" t="n">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9033974358974358</v>
+        <v>0.6183699633699633</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1253949292607568</v>
+        <v>0.2501616311580228</v>
       </c>
       <c r="H83" t="n">
-        <v>0.4856115797517387</v>
+        <v>0.4453078580273849</v>
       </c>
       <c r="I83" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.5120697478915235</v>
+      </c>
+      <c r="K83" t="n">
         <v>8</v>
       </c>
-      <c r="J83" t="n">
+      <c r="L83" t="n">
+        <v>11</v>
+      </c>
+      <c r="M83" t="n">
         <v>2</v>
       </c>
-      <c r="K83" t="n">
-        <v>2</v>
-      </c>
-      <c r="L83" t="n">
-        <v>13</v>
-      </c>
-      <c r="M83" t="n">
+      <c r="N83" t="n">
+        <v>4</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.5517241379310345</v>
+      </c>
+      <c r="P83" t="n">
         <v>0.8</v>
       </c>
-      <c r="N83" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P83" t="n">
+      <c r="Q83" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="R83" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0.84</v>
-      </c>
       <c r="S83" t="n">
-        <v>0.18</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T83" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="U83" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.36</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0.3066666666666667</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0.2533333333333334</v>
       </c>
     </row>
     <row r="84">
@@ -6368,55 +6510,61 @@
         <v>2012</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7298245614035088</v>
+        <v>0.6464912280701753</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1704497658054301</v>
+        <v>0.189279366024186</v>
       </c>
       <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J84" t="n">
         <v>0.5836298932384343</v>
       </c>
-      <c r="I84" t="n">
+      <c r="K84" t="n">
         <v>10</v>
       </c>
-      <c r="J84" t="n">
-        <v>9</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
       <c r="L84" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M84" t="n">
-        <v>0.6896551724137931</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="R84" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.18</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="U84" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="85">
@@ -6439,55 +6587,61 @@
         <v>2012</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9733333333333334</v>
+        <v>0.92</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9651515151515151</v>
+        <v>0.923109243697479</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1374418432978003</v>
+        <v>0.1019225851531419</v>
       </c>
       <c r="H85" t="n">
-        <v>0.01095831572786022</v>
+        <v>0.06854964202330634</v>
       </c>
       <c r="I85" t="n">
-        <v>10</v>
+        <v>2011</v>
       </c>
       <c r="J85" t="n">
-        <v>2</v>
+        <v>0.5171363410225742</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L85" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O85" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.5625</v>
       </c>
       <c r="R85" t="n">
-        <v>0.92</v>
+        <v>0.1</v>
       </c>
       <c r="S85" t="n">
-        <v>0.04</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="T85" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.68</v>
       </c>
       <c r="U85" t="n">
-        <v>0.01333333333333333</v>
+        <v>0.21</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0.1366666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -6523,7 +6677,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.645</v>
+        <v>0.5610000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -6533,7 +6687,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.732</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="4">
@@ -6543,7 +6697,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.66</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="5">
@@ -6553,7 +6707,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.645</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="6">
@@ -6563,7 +6717,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.725</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="7">
@@ -6573,7 +6727,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.742</v>
+        <v>0.748</v>
       </c>
     </row>
   </sheetData>
@@ -6649,25 +6803,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.645</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.417</v>
       </c>
       <c r="E2" t="n">
-        <v>0.986</v>
+        <v>0.783</v>
       </c>
       <c r="F2" t="n">
-        <v>0.425</v>
+        <v>0.311</v>
       </c>
       <c r="G2" t="n">
-        <v>0.014</v>
+        <v>0.217</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.831</v>
       </c>
       <c r="I2" t="n">
-        <v>0.148</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="3">
@@ -6682,25 +6836,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.732</v>
+        <v>0.747</v>
       </c>
       <c r="D3" t="n">
-        <v>0.658</v>
+        <v>0.452</v>
       </c>
       <c r="E3" t="n">
-        <v>0.971</v>
+        <v>0.783</v>
       </c>
       <c r="F3" t="n">
-        <v>0.546</v>
+        <v>0.352</v>
       </c>
       <c r="G3" t="n">
-        <v>0.029</v>
+        <v>0.217</v>
       </c>
       <c r="H3" t="n">
-        <v>0.463</v>
+        <v>0.719</v>
       </c>
       <c r="I3" t="n">
-        <v>0.116</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="4">
@@ -6715,25 +6869,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.66</v>
+        <v>0.635</v>
       </c>
       <c r="D4" t="n">
-        <v>0.579</v>
+        <v>0.348</v>
       </c>
       <c r="E4" t="n">
-        <v>0.957</v>
+        <v>0.617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.461</v>
+        <v>0.28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.043</v>
+        <v>0.383</v>
       </c>
       <c r="H4" t="n">
         <v>0.5649999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.147</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="5">
@@ -6748,25 +6902,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.645</v>
+        <v>0.607</v>
       </c>
       <c r="D5" t="n">
-        <v>0.593</v>
+        <v>0.399</v>
       </c>
       <c r="E5" t="n">
-        <v>0.886</v>
+        <v>0.696</v>
       </c>
       <c r="F5" t="n">
-        <v>0.544</v>
+        <v>0.33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.114</v>
+        <v>0.304</v>
       </c>
       <c r="H5" t="n">
-        <v>0.435</v>
+        <v>0.614</v>
       </c>
       <c r="I5" t="n">
-        <v>0.178</v>
+        <v>0.366</v>
       </c>
     </row>
     <row r="6">
@@ -6781,25 +6935,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.725</v>
+        <v>0.713</v>
       </c>
       <c r="D6" t="n">
-        <v>0.723</v>
+        <v>0.516</v>
       </c>
       <c r="E6" t="n">
-        <v>0.971</v>
+        <v>0.767</v>
       </c>
       <c r="F6" t="n">
-        <v>0.609</v>
+        <v>0.415</v>
       </c>
       <c r="G6" t="n">
-        <v>0.029</v>
+        <v>0.233</v>
       </c>
       <c r="H6" t="n">
-        <v>0.532</v>
+        <v>0.468</v>
       </c>
       <c r="I6" t="n">
-        <v>0.129</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="7">
@@ -6814,25 +6968,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.742</v>
+        <v>0.748</v>
       </c>
       <c r="D7" t="n">
-        <v>0.754</v>
+        <v>0.523</v>
       </c>
       <c r="E7" t="n">
-        <v>0.971</v>
+        <v>0.8</v>
       </c>
       <c r="F7" t="n">
-        <v>0.656</v>
+        <v>0.403</v>
       </c>
       <c r="G7" t="n">
-        <v>0.029</v>
+        <v>0.2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.421</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.107</v>
+        <v>0.273</v>
       </c>
     </row>
   </sheetData>
@@ -6878,7 +7032,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.645</v>
+        <v>0.5610000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -6888,7 +7042,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.732</v>
+        <v>0.747</v>
       </c>
     </row>
     <row r="4">
@@ -6898,7 +7052,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.66</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="5">
@@ -6908,7 +7062,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.645</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="6">
@@ -6918,7 +7072,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.725</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="7">
@@ -6928,7 +7082,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.742</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="8">
@@ -6943,7 +7097,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.601</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="9">
@@ -6953,7 +7107,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.713</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="10">
@@ -6963,7 +7117,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.655</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11">
@@ -6973,7 +7127,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.654</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="12">
@@ -6983,7 +7137,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.719</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="13">
@@ -6993,7 +7147,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.613</v>
+        <v>0.611</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/results/12b/results_12b_final.xlsx
+++ b/outputs/results/12b/results_12b_final.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U85"/>
+  <dimension ref="A1:W85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -546,55 +556,61 @@
         <v>2001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7083333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="F2" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1831758483242265</v>
+        <v>0.1748327435789417</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09122389628104793</v>
+        <v>0.8099604521224645</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>0.1516689602838912</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2222222222222222</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2916666666666667</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08750000000000001</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05833333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02916666666666667</v>
+        <v>0.75</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -623,49 +639,55 @@
         <v>0.25</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0561472351020488</v>
+        <v>0.06316956412194508</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2823529411764706</v>
+        <v>0.4482543763269847</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>0.253968253968254</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0375</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="T3" t="n">
-        <v>0.025</v>
+        <v>0.92</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0125</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -688,55 +710,61 @@
         <v>2001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.875</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F4" t="n">
-        <v>0.25</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="G4" t="n">
-        <v>0.121742770075798</v>
+        <v>0.07590742409229279</v>
       </c>
       <c r="H4" t="n">
-        <v>0.522675633430481</v>
+        <v>0.3625855445861816</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>0.02856630645692348</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O4" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0375</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="T4" t="n">
-        <v>0.025</v>
+        <v>0.92</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0125</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -759,55 +787,61 @@
         <v>2001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1600052361472709</v>
+        <v>0.18475152768189</v>
       </c>
       <c r="H5" t="n">
-        <v>1.300705435871653e-07</v>
+        <v>0.732139416541368</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>0.5518772399125124</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.075</v>
+        <v>0.125</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05</v>
+        <v>0.84</v>
       </c>
       <c r="U5" t="n">
-        <v>0.025</v>
+        <v>0.7374999999999999</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.8250000000000001</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9125</v>
       </c>
     </row>
     <row r="6">
@@ -830,55 +864,61 @@
         <v>2001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8958333333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2121169116598058</v>
+        <v>0.1426170136823319</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9068219633943428</v>
+        <v>0.6907630522088356</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2857142857142857</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0625</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.88</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02083333333333334</v>
+        <v>0.725</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9083333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -901,55 +941,61 @@
         <v>2001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="F7" t="n">
-        <v>0.25</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1102600918006365</v>
+        <v>0.08803263191827376</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009680070421468673</v>
+        <v>0.1396433145378327</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0.1309722301789648</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0375</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="T7" t="n">
-        <v>0.025</v>
+        <v>0.76</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0125</v>
+        <v>0.7625</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.8416666666666667</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.9208333333333334</v>
       </c>
     </row>
     <row r="8">
@@ -972,55 +1018,61 @@
         <v>2002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5833333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4300547054110133</v>
+        <v>0.4670657351011575</v>
       </c>
       <c r="H8" t="n">
-        <v>0.663812004632659</v>
+        <v>0.1516689602838912</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>0.6790887546384597</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.08</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.125</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08333333333333334</v>
+        <v>0.08</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.2875</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1916666666666667</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.09583333333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1049,49 +1101,55 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0451054236909176</v>
+        <v>0.04761898466902117</v>
       </c>
       <c r="H9" t="n">
-        <v>0.545790035283727</v>
+        <v>0.253968253968254</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.025</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.008333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -1114,55 +1172,61 @@
         <v>2002</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07728493958711624</v>
+        <v>0.08742135763168335</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6937016248703003</v>
+        <v>0.02856630645692348</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.5494585037231445</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>24</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -1185,55 +1249,61 @@
         <v>2002</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5833333333333333</v>
+        <v>0.5416666666666667</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4616694834296106</v>
+        <v>0.4681723323894487</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7417925436734171</v>
+        <v>0.5518772399125124</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>0.669414623823095</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.125</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08333333333333334</v>
+        <v>0.48</v>
       </c>
       <c r="U11" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.1625</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1083333333333333</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.05416666666666667</v>
       </c>
     </row>
     <row r="12">
@@ -1265,46 +1335,52 @@
         <v>0.2130889204417722</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.8425925925925926</v>
       </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.25</v>
+        <v>0.04</v>
       </c>
       <c r="R12" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.075</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="U12" t="n">
-        <v>0.025</v>
+        <v>0.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="13">
@@ -1327,55 +1403,61 @@
         <v>2002</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05070693633000434</v>
+        <v>0.04321958502001893</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2072573464424945</v>
+        <v>0.1309722301789648</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>0.2345202150897926</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0625</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T13" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.68</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02083333333333334</v>
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -1398,56 +1480,32 @@
         <v>2008</v>
       </c>
       <c r="E14" t="n">
-        <v>0.375</v>
+        <v>0.3611111111111112</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5865063598710034</v>
+        <v>0.5764741980828433</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5098728236500527</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.0003426246448590228</v>
-      </c>
-      <c r="I14" t="n">
-        <v>16</v>
-      </c>
+        <v>0.5619095848567998</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.0009144036573601353</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1469,56 +1527,32 @@
         <v>2008</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4895833333333334</v>
+        <v>0.4722222222222222</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6179359243697479</v>
+        <v>0.615</v>
       </c>
       <c r="G15" t="n">
-        <v>0.614984</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>16</v>
-      </c>
+        <v>0.626256</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>9</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1543,53 +1577,29 @@
         <v>0.4861111111111111</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6229916121460238</v>
+        <v>0.6206570537473923</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6358895897865295</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.001354562235064805</v>
-      </c>
-      <c r="I16" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6481840014457703</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.1777777777777778</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.08888888888888889</v>
-      </c>
+        <v>0.001618588343262672</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1611,56 +1621,32 @@
         <v>2008</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3402777777777778</v>
+        <v>0.3055555555555556</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5710335514294451</v>
+        <v>0.595650291221301</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5908596673905517</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4.568221092737065e-05</v>
-      </c>
-      <c r="I17" t="n">
-        <v>16</v>
-      </c>
+        <v>0.5931726647137168</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.1</v>
-      </c>
+        <v>4.021057536987047e-08</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1682,56 +1668,32 @@
         <v>2008</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.3645833333333334</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6124999999999999</v>
+        <v>0.615625</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6832927615033462</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6571553263241421</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>9</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1753,56 +1715,32 @@
         <v>2008</v>
       </c>
       <c r="E19" t="n">
-        <v>0.625</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7252919333082377</v>
+        <v>0.6584886920845453</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6126608297603905</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.421227358443719e-05</v>
-      </c>
-      <c r="I19" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6298669869849081</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.8205128205128205</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.6956521739130435</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.2333333333333333</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.1555555555555556</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.07777777777777778</v>
-      </c>
+        <v>6.824587925004975e-06</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1824,55 +1762,61 @@
         <v>2009</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7714425555618011</v>
+        <v>0.8020515652433222</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2205441333509373</v>
+        <v>0.1786862203649098</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4414598957633341</v>
+        <v>0.0009144036573601353</v>
       </c>
       <c r="I20" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4081214925787585</v>
+      </c>
+      <c r="K20" t="n">
         <v>16</v>
       </c>
-      <c r="J20" t="n">
-        <v>7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8205128205128205</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="R20" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2333333333333333</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="21">
@@ -1895,54 +1839,60 @@
         <v>2009</v>
       </c>
       <c r="E21" t="n">
-        <v>0.638888888888889</v>
+        <v>0.701388888888889</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7317536450645719</v>
+        <v>0.7603154881847337</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2655584566128624</v>
+        <v>0.3791840906911375</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1642315720101805</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.1362556607788215</v>
+      </c>
+      <c r="K21" t="n">
         <v>16</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
         <v>0.64</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
       <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
         <v>0.64</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.3</v>
       </c>
-      <c r="T21" t="n">
+      <c r="V21" t="n">
         <v>0.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1966,55 +1916,61 @@
         <v>2009</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.625</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6546819959044223</v>
+        <v>0.7026570738651352</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3714910447597504</v>
+        <v>0.3353837132453918</v>
       </c>
       <c r="H22" t="n">
-        <v>0.02352490834891796</v>
+        <v>0.001618588343262672</v>
       </c>
       <c r="I22" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.07592270523309708</v>
+      </c>
+      <c r="K22" t="n">
         <v>16</v>
       </c>
-      <c r="J22" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8421052631578947</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.64</v>
       </c>
       <c r="R22" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V22" t="n">
         <v>0.2</v>
       </c>
-      <c r="T22" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.06666666666666667</v>
+      <c r="W22" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="23">
@@ -2037,55 +1993,61 @@
         <v>2009</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7444331219806763</v>
+        <v>0.780553583422829</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2369984395980911</v>
+        <v>0.2052039691114308</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4310298584365538</v>
+        <v>4.021057536987047e-08</v>
       </c>
       <c r="I23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.5145399398756799</v>
+      </c>
+      <c r="K23" t="n">
         <v>16</v>
       </c>
-      <c r="J23" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8205128205128205</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="R23" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2333333333333333</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
@@ -2108,54 +2070,60 @@
         <v>2009</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6458333333333333</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7511458333333333</v>
+        <v>0.7576785714285714</v>
       </c>
       <c r="G24" t="n">
-        <v>0.313669502135048</v>
+        <v>0.4196223700017738</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>16</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>9</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
         <v>0.64</v>
       </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
       <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
         <v>0.64</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.3</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.2</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2179,55 +2147,61 @@
         <v>2009</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6462810453435454</v>
+        <v>0.6758604391716814</v>
       </c>
       <c r="G25" t="n">
-        <v>0.482497914375094</v>
+        <v>0.4773712425629074</v>
       </c>
       <c r="H25" t="n">
-        <v>6.802663028485531e-06</v>
+        <v>6.824587925004975e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J25" t="n">
-        <v>9</v>
+        <v>6.564282741219073e-07</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7804878048780488</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>0.64</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="R25" t="n">
-        <v>0.64</v>
+        <v>0.125</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1</v>
+        <v>0.2875</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.1791666666666667</v>
       </c>
     </row>
     <row r="26">
@@ -2250,55 +2224,61 @@
         <v>2010</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5866666666666666</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6009764796606901</v>
+        <v>0.4970797258297258</v>
       </c>
       <c r="G26" t="n">
-        <v>0.462651516315676</v>
+        <v>0.4422888319123964</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8357399084843402</v>
+        <v>0.4081214925787585</v>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>2009</v>
       </c>
       <c r="J26" t="n">
+        <v>0.9634499061579728</v>
+      </c>
+      <c r="K26" t="n">
         <v>10</v>
       </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6206896551724138</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.27</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2133333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1566666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="27">
@@ -2321,55 +2301,61 @@
         <v>2010</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.45</v>
       </c>
       <c r="F27" t="n">
-        <v>0.42589508530685</v>
+        <v>0.3869000933706816</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3533496577136402</v>
+        <v>0.2861090909090909</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3205606899313307</v>
+        <v>0.1362556607788215</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J27" t="n">
-        <v>15</v>
+        <v>0.1454545454545454</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="S27" t="n">
-        <v>0.3</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2</v>
+        <v>0.52</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.1633333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -2392,55 +2378,61 @@
         <v>2010</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.6466666666666667</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4799596157719728</v>
+        <v>0.4897882183176301</v>
       </c>
       <c r="G28" t="n">
-        <v>0.376446545124054</v>
+        <v>0.2684909701347351</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09784837067127228</v>
+        <v>0.07592270523309708</v>
       </c>
       <c r="I28" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1238209530711174</v>
+      </c>
+      <c r="K28" t="n">
         <v>10</v>
       </c>
-      <c r="J28" t="n">
-        <v>13</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6060606060606061</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.625</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="R28" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1733333333333333</v>
+        <v>0.52</v>
       </c>
       <c r="U28" t="n">
-        <v>0.08666666666666667</v>
+        <v>0.24</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.08000000000000002</v>
       </c>
     </row>
     <row r="29">
@@ -2463,55 +2455,61 @@
         <v>2010</v>
       </c>
       <c r="E29" t="n">
-        <v>0.62</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6987895256916996</v>
+        <v>0.5566383034413726</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4097468804483028</v>
+        <v>0.3560793681180028</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9936514111704592</v>
+        <v>0.5145399398756799</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>2009</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.5269785530168727</v>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M29" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R29" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.37</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T29" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.48</v>
       </c>
       <c r="U29" t="n">
-        <v>0.4566666666666667</v>
+        <v>0.26</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
     <row r="30">
@@ -2534,54 +2532,60 @@
         <v>2010</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4533333333333333</v>
+        <v>0.5766666666666667</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3768990658464343</v>
+        <v>0.4447619047619048</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4962243253487426</v>
+        <v>0.3512219144352108</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2010</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6200000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5147823734236777</v>
+        <v>0.5171432552954291</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4018680147158371</v>
+        <v>0.3175867866242583</v>
       </c>
       <c r="H31" t="n">
-        <v>0.001111154599566572</v>
+        <v>6.564282741219073e-07</v>
       </c>
       <c r="I31" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.001493028636684712</v>
+      </c>
+      <c r="K31" t="n">
         <v>10</v>
       </c>
-      <c r="J31" t="n">
-        <v>13</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6060606060606061</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1733333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U31" t="n">
-        <v>0.08666666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="32">
@@ -2679,52 +2689,58 @@
         <v>0.7933333333333333</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8018414918414918</v>
+        <v>0.7671717171717171</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2288056604495035</v>
+        <v>0.2197304503300977</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5207668870685651</v>
+        <v>0.9634499061579728</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>0.5111020029485533</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.72</v>
+        <v>10</v>
       </c>
       <c r="N32" t="n">
+        <v>15</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W32" t="n">
         <v>0.9</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.13</v>
       </c>
     </row>
     <row r="33">
@@ -2747,55 +2763,61 @@
         <v>2011</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7308333333333333</v>
+        <v>0.7324050510892616</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2267831049810215</v>
+        <v>0.1998151724123472</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5640755320597821</v>
+        <v>0.1454545454545454</v>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>0.4860123473105527</v>
       </c>
       <c r="K33" t="n">
+        <v>10</v>
+      </c>
+      <c r="L33" t="n">
+        <v>13</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>2</v>
       </c>
-      <c r="L33" t="n">
-        <v>11</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.8</v>
-      </c>
       <c r="O33" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="P33" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R33" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.22</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T33" t="n">
-        <v>0.2133333333333334</v>
+        <v>0.48</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2066666666666667</v>
+        <v>0.26</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
     <row r="34">
@@ -2818,55 +2840,61 @@
         <v>2011</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8733333333333333</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8384099672257567</v>
+        <v>0.7890576090576089</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1533974409103394</v>
+        <v>0.1614827215671539</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5449708700180054</v>
+        <v>0.1238209530711174</v>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>0.4115402698516846</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L34" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="R34" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.18</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T34" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U34" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.22</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.07333333333333333</v>
       </c>
     </row>
     <row r="35">
@@ -2889,55 +2917,61 @@
         <v>2011</v>
       </c>
       <c r="E35" t="n">
-        <v>0.76</v>
+        <v>0.5933333333333333</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7557448107448107</v>
+        <v>0.6257344448076713</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2243169500719387</v>
+        <v>0.2792403293069315</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8917110644340588</v>
+        <v>0.5269785530168727</v>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>2010</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>0.07584680866613772</v>
       </c>
       <c r="K35" t="n">
         <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7368421052631579</v>
+        <v>7</v>
       </c>
       <c r="N35" t="n">
-        <v>0.7</v>
+        <v>14</v>
       </c>
       <c r="O35" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="P35" t="n">
         <v>0.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="R35" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S35" t="n">
-        <v>0.25</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="T35" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.68</v>
       </c>
       <c r="U35" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.5099999999999999</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.5733333333333333</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.6366666666666667</v>
       </c>
     </row>
     <row r="36">
@@ -2960,55 +2994,61 @@
         <v>2011</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.59</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5181818181818181</v>
+        <v>0.4894083694083695</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3262565966005779</v>
+        <v>0.3571700515707979</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5384615384615385</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>10</v>
       </c>
-      <c r="J36" t="n">
-        <v>12</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M36" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="R36" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="U36" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="37">
@@ -3031,55 +3071,61 @@
         <v>2011</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8600000000000001</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8255483405483405</v>
+        <v>0.7718950004244122</v>
       </c>
       <c r="G37" t="n">
-        <v>0.175041012584231</v>
+        <v>0.177684972500747</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5896137652913739</v>
+        <v>0.001493028636684712</v>
       </c>
       <c r="I37" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0.4422501340206331</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L37" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W37" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.1066666666666667</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.1033333333333333</v>
       </c>
     </row>
     <row r="38">
@@ -3102,55 +3148,61 @@
         <v>2012</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8057792207792207</v>
+        <v>0.75</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1820026267412815</v>
+        <v>0.2368335084798813</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4569239996556106</v>
+        <v>0.5111020029485533</v>
       </c>
       <c r="I38" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J38" t="n">
-        <v>6</v>
+        <v>0.5225886624680246</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M38" t="n">
-        <v>0.72</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="O38" t="n">
-        <v>0.6</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="P38" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.4</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="R38" t="n">
-        <v>0.72</v>
+        <v>0.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0.19</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T38" t="n">
-        <v>0.16</v>
+        <v>0.68</v>
       </c>
       <c r="U38" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.3066666666666666</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.3033333333333333</v>
       </c>
     </row>
     <row r="39">
@@ -3173,55 +3225,61 @@
         <v>2012</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8733333333333334</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8352480852480851</v>
+        <v>0.7982017543859649</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1579551269153233</v>
+        <v>0.2131794337880235</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4118244893895048</v>
+        <v>0.4860123473105527</v>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>2011</v>
       </c>
       <c r="J39" t="n">
-        <v>5</v>
+        <v>0.6853278735767129</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M39" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" t="n">
+        <v>7</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="P39" t="n">
         <v>0.8</v>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
       <c r="Q39" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="R39" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="S39" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T39" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="U39" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.3</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.2333333333333334</v>
       </c>
     </row>
     <row r="40">
@@ -3244,55 +3302,61 @@
         <v>2012</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.9133333333333333</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8566766566766565</v>
+        <v>0.9031746031746032</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1541679799556732</v>
+        <v>0.173102393746376</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5303398370742798</v>
+        <v>0.4115402698516846</v>
       </c>
       <c r="I40" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.8678404092788696</v>
+      </c>
+      <c r="K40" t="n">
         <v>10</v>
       </c>
-      <c r="J40" t="n">
-        <v>4</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
         <v>0.7142857142857143</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="R40" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.08</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T40" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.1066666666666667</v>
+      </c>
+      <c r="W40" t="n">
         <v>0.05333333333333334</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0.02666666666666667</v>
       </c>
     </row>
     <row r="41">
@@ -3315,55 +3379,61 @@
         <v>2012</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.78</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8432792207792207</v>
+        <v>0.7767912204754309</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2891520057757666</v>
+        <v>0.2079455302986053</v>
       </c>
       <c r="H41" t="n">
-        <v>0.03280988250236398</v>
+        <v>0.07584680866613772</v>
       </c>
       <c r="I41" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.5593965527860587</v>
+      </c>
+      <c r="K41" t="n">
         <v>10</v>
       </c>
-      <c r="J41" t="n">
-        <v>6</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7692307692307693</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
         <v>0.4</v>
       </c>
       <c r="R41" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="U41" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="42">
@@ -3386,55 +3456,61 @@
         <v>2012</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6633333333333333</v>
+        <v>0.8033333333333335</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4930515236397589</v>
+        <v>0.6476923076923077</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3505251175127529</v>
+        <v>0.2020732122590039</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8549222797927462</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J42" t="n">
-        <v>8</v>
+        <v>0.7021276595744681</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L42" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W42" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="43">
@@ -3460,52 +3536,58 @@
         <v>0.8933333333333333</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8709973798131693</v>
+        <v>0.8914624183006535</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1410939947454191</v>
+        <v>0.1925318517127819</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6244520695965369</v>
+        <v>0.4422501340206331</v>
       </c>
       <c r="I43" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.8352672757620179</v>
+      </c>
+      <c r="K43" t="n">
+        <v>10</v>
+      </c>
+      <c r="L43" t="n">
         <v>9</v>
       </c>
-      <c r="J43" t="n">
-        <v>2</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" t="n">
-        <v>13</v>
-      </c>
       <c r="M43" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="O43" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="P43" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="R43" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.11</v>
+        <v>0.6</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.64</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1033333333333333</v>
+        <v>0.18</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="44">
@@ -3534,49 +3616,55 @@
         <v>0.25</v>
       </c>
       <c r="G44" t="n">
-        <v>0.09768099359929368</v>
+        <v>0.103070676358716</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3962694950060163</v>
+        <v>0.8769114735537481</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>0.4413120243615778</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O44" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0375</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="T44" t="n">
-        <v>0.025</v>
+        <v>0.92</v>
       </c>
       <c r="U44" t="n">
-        <v>0.0125</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="45">
@@ -3599,55 +3687,61 @@
         <v>2001</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9791666666666666</v>
+        <v>0.9583333333333333</v>
       </c>
       <c r="F45" t="n">
         <v>0.5</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02668565325738697</v>
+        <v>0.02953767669252843</v>
       </c>
       <c r="H45" t="n">
-        <v>0.270440251572327</v>
+        <v>0.38</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0.2216494845360825</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O45" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.04166666666666666</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
         <v>0.96</v>
       </c>
-      <c r="S45" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0.008333333333333333</v>
-      </c>
       <c r="U45" t="n">
-        <v>0.004166666666666667</v>
+        <v>0.7</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="46">
@@ -3676,49 +3770,55 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.008356071077287197</v>
+        <v>0.02095027640461922</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6254370808601379</v>
+        <v>0.01189725659787655</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.5687749981880188</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>24</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
@@ -3747,49 +3847,55 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="G47" t="n">
-        <v>0.06771062317752044</v>
+        <v>0.07261062545800283</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4054822920698812</v>
+        <v>0.9517144055092077</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>0.008853594147705606</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O47" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0.01666666666666667</v>
+        <v>0.96</v>
       </c>
       <c r="U47" t="n">
-        <v>0.008333333333333333</v>
+        <v>0.7</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="48">
@@ -3821,28 +3927,28 @@
         <v>0.000292205420410548</v>
       </c>
       <c r="H48" t="n">
+        <v>0.9655172413793105</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J48" t="n">
         <v>0.9145299145299146</v>
       </c>
-      <c r="I48" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" t="n">
         <v>24</v>
       </c>
-      <c r="M48" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -3857,10 +3963,16 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>0.7</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="49">
@@ -3889,49 +4001,55 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1195659958439588</v>
+        <v>0.04136041770065001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0009349436569170327</v>
+        <v>0.6163617227386412</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>0.007832598412255322</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O49" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0.01666666666666667</v>
+        <v>0.96</v>
       </c>
       <c r="U49" t="n">
-        <v>0.008333333333333333</v>
+        <v>0.7</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="50">
@@ -3954,55 +4072,61 @@
         <v>2002</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4583333333333334</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="F50" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4757245492139788</v>
+        <v>0.552469161367016</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5448897249792384</v>
+        <v>0.4413120243615778</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J50" t="n">
-        <v>13</v>
+        <v>0.5462131666412225</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O50" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.0625</v>
       </c>
       <c r="R50" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.1625</v>
+        <v>0.625</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1083333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U50" t="n">
-        <v>0.05416666666666667</v>
+        <v>0.1875</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.0625</v>
       </c>
     </row>
     <row r="51">
@@ -4025,55 +4149,61 @@
         <v>2002</v>
       </c>
       <c r="E51" t="n">
-        <v>0.625</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G51" t="n">
-        <v>0.07180640826809585</v>
+        <v>0.07803880422791137</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1848486033749054</v>
+        <v>0.2216494845360825</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J51" t="n">
-        <v>9</v>
+        <v>0.1181558111984809</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1818181818181818</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O51" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.1125</v>
+        <v>0.25</v>
       </c>
       <c r="T51" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="U51" t="n">
-        <v>0.03750000000000001</v>
+        <v>0.7749999999999999</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.925</v>
       </c>
     </row>
     <row r="52">
@@ -4096,55 +4226,61 @@
         <v>2002</v>
       </c>
       <c r="E52" t="n">
-        <v>0.04166666666666669</v>
+        <v>0.125</v>
       </c>
       <c r="F52" t="n">
-        <v>0.04</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1641695648431778</v>
+        <v>0.1741306185722351</v>
       </c>
       <c r="H52" t="n">
-        <v>0.05124238878488541</v>
+        <v>0.5687749981880188</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>0.02443820051848888</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M52" t="n">
-        <v>0.07692307692307693</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O52" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>0.3</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T52" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="U52" t="n">
-        <v>0.1</v>
+        <v>0.75</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="53">
@@ -4167,55 +4303,61 @@
         <v>2002</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4166666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="F53" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3957525842271876</v>
+        <v>0.4808016715904887</v>
       </c>
       <c r="H53" t="n">
-        <v>0.08635327756783583</v>
+        <v>0.008853594147705606</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J53" t="n">
-        <v>14</v>
+        <v>0.003798312429493467</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M53" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O53" t="n">
-        <v>0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.5833333333333334</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0.44</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>0.175</v>
+        <v>0.5</v>
       </c>
       <c r="T53" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="U53" t="n">
-        <v>0.05833333333333334</v>
+        <v>0.85</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.9500000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -4244,49 +4386,55 @@
         <v>0.04</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2126371912881646</v>
+        <v>0.2126371912881645</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.9145299145299146</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J54" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M54" t="n">
-        <v>0.07692307692307693</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O54" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>0.3</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="T54" t="n">
-        <v>0.2</v>
+        <v>0.76</v>
       </c>
       <c r="U54" t="n">
-        <v>0.1</v>
+        <v>0.7625</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.8416666666666667</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.9208333333333334</v>
       </c>
     </row>
     <row r="55">
@@ -4309,55 +4457,61 @@
         <v>2002</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7083333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="F55" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1026603154118692</v>
+        <v>0.1155750950801771</v>
       </c>
       <c r="H55" t="n">
-        <v>0.03830964192992885</v>
+        <v>0.007832598412255322</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J55" t="n">
-        <v>7</v>
+        <v>0.08130551005427263</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2222222222222222</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O55" t="n">
-        <v>0.125</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="R55" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.08750000000000001</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="T55" t="n">
-        <v>0.05833333333333334</v>
+        <v>0.12</v>
       </c>
       <c r="U55" t="n">
-        <v>0.02916666666666667</v>
+        <v>0.275</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.09166666666666667</v>
       </c>
     </row>
     <row r="56">
@@ -4380,56 +4534,32 @@
         <v>2008</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.4930555555555556</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7461318204821494</v>
+        <v>0.6596023405941883</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5269514292019705</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.0004238894723492777</v>
-      </c>
-      <c r="I56" t="n">
-        <v>15</v>
-      </c>
+        <v>0.5949789787154234</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
-        <v>7</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" t="n">
-        <v>2</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.7894736842105263</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0.6818181818181818</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0.2770833333333333</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0.2055555555555555</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0.1340277777777778</v>
-      </c>
+        <v>2.095342901271278e-05</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4451,56 +4581,32 @@
         <v>2008</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6829166666666667</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>0.624008</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6322759999999999</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>9</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4522,56 +4628,32 @@
         <v>2008</v>
       </c>
       <c r="E58" t="n">
-        <v>0.5069444444444444</v>
+        <v>0.5659722222222222</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6754186246867168</v>
+        <v>0.7523041134590047</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6322618722915649</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.0005854230257682502</v>
-      </c>
-      <c r="I58" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6336380839347839</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
-        <v>9</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.001106431591324508</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4593,56 +4675,32 @@
         <v>2008</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4652777777777778</v>
+        <v>0.4305555555555556</v>
       </c>
       <c r="F59" t="n">
-        <v>0.663849557608938</v>
+        <v>0.6709612324837708</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5895138386480303</v>
-      </c>
-      <c r="H59" t="n">
-        <v>6.758511167435938e-06</v>
-      </c>
-      <c r="I59" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6089951922848251</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>9</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N59" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0.1</v>
-      </c>
+        <v>2.262427739229771e-05</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4672,48 +4730,24 @@
       <c r="G60" t="n">
         <v>0.64</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>16</v>
-      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>9</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4735,56 +4769,32 @@
         <v>2008</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4375</v>
+        <v>0.5069444444444444</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6164975491438087</v>
+        <v>0.6792103148077413</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6397414400281456</v>
-      </c>
-      <c r="H61" t="n">
-        <v>4.066190212334127e-07</v>
-      </c>
-      <c r="I61" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6389830189761644</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
-        <v>9</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0.1</v>
-      </c>
+        <v>8.103915832325728e-07</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4806,54 +4816,60 @@
         <v>2009</v>
       </c>
       <c r="E62" t="n">
-        <v>0.5902777777777778</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7317095736389214</v>
+        <v>0.6370509014012303</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4113046110193712</v>
+        <v>0.5073098927030608</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0009987528090520381</v>
+        <v>2.095342901271278e-05</v>
       </c>
       <c r="I62" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.001969129684745444</v>
+      </c>
+      <c r="K62" t="n">
         <v>16</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>9</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
       <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N62" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" t="n">
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
         <v>0.64</v>
       </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
       <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
         <v>0.64</v>
       </c>
-      <c r="S62" t="n">
+      <c r="U62" t="n">
         <v>0.3</v>
       </c>
-      <c r="T62" t="n">
+      <c r="V62" t="n">
         <v>0.2</v>
       </c>
-      <c r="U62" t="n">
+      <c r="W62" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4877,54 +4893,60 @@
         <v>2009</v>
       </c>
       <c r="E63" t="n">
-        <v>0.5208333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6383482142857142</v>
+        <v>0.640595238095238</v>
       </c>
       <c r="G63" t="n">
-        <v>0.593212</v>
+        <v>0.6056919999999999</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>16</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>9</v>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
       <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N63" t="n">
-        <v>1</v>
-      </c>
-      <c r="O63" t="n">
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
         <v>0.64</v>
       </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>1</v>
-      </c>
       <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
         <v>0.64</v>
       </c>
-      <c r="S63" t="n">
+      <c r="U63" t="n">
         <v>0.3</v>
       </c>
-      <c r="T63" t="n">
+      <c r="V63" t="n">
         <v>0.2</v>
       </c>
-      <c r="U63" t="n">
+      <c r="W63" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4948,55 +4970,61 @@
         <v>2009</v>
       </c>
       <c r="E64" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.625</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6652778843057228</v>
+        <v>0.6911767766547178</v>
       </c>
       <c r="G64" t="n">
-        <v>0.6223048567771912</v>
+        <v>0.6291800141334534</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0006677798228338361</v>
+        <v>0.001106431591324508</v>
       </c>
       <c r="I64" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.002162893069908023</v>
+      </c>
+      <c r="K64" t="n">
         <v>16</v>
       </c>
-      <c r="J64" t="n">
-        <v>8</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M64" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R64" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U64" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="65">
@@ -5019,54 +5047,60 @@
         <v>2009</v>
       </c>
       <c r="E65" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4027777777777778</v>
       </c>
       <c r="F65" t="n">
-        <v>0.6603090379935346</v>
+        <v>0.5964394919693833</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5095793659237123</v>
+        <v>0.5884778137842492</v>
       </c>
       <c r="H65" t="n">
-        <v>0.000106223273925163</v>
+        <v>2.262427739229771e-05</v>
       </c>
       <c r="I65" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3.554858606472577e-05</v>
+      </c>
+      <c r="K65" t="n">
         <v>16</v>
       </c>
-      <c r="J65" t="n">
+      <c r="L65" t="n">
         <v>9</v>
       </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
       <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N65" t="n">
-        <v>1</v>
-      </c>
-      <c r="O65" t="n">
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
         <v>0.64</v>
       </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1</v>
-      </c>
       <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
         <v>0.64</v>
       </c>
-      <c r="S65" t="n">
+      <c r="U65" t="n">
         <v>0.3</v>
       </c>
-      <c r="T65" t="n">
+      <c r="V65" t="n">
         <v>0.2</v>
       </c>
-      <c r="U65" t="n">
+      <c r="W65" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5102,42 +5136,48 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>16</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>9</v>
       </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
       <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
         <v>0.64</v>
       </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1</v>
-      </c>
       <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
         <v>0.64</v>
       </c>
-      <c r="S66" t="n">
+      <c r="U66" t="n">
         <v>0.3</v>
       </c>
-      <c r="T66" t="n">
+      <c r="V66" t="n">
         <v>0.2</v>
       </c>
-      <c r="U66" t="n">
+      <c r="W66" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5161,55 +5201,61 @@
         <v>2009</v>
       </c>
       <c r="E67" t="n">
-        <v>0.6041666666666667</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6997313140076298</v>
+        <v>0.6596410192358082</v>
       </c>
       <c r="G67" t="n">
-        <v>0.6367494291863808</v>
+        <v>0.63989224017819</v>
       </c>
       <c r="H67" t="n">
-        <v>1.573236477062979e-05</v>
+        <v>8.103915832325728e-07</v>
       </c>
       <c r="I67" t="n">
-        <v>14</v>
+        <v>2008</v>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>1.074627012688665e-05</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="L67" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M67" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P67" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="R67" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.2541666666666667</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0.2111111111111111</v>
+        <v>0.64</v>
       </c>
       <c r="U67" t="n">
-        <v>0.1680555555555556</v>
+        <v>0.3</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="68">
@@ -5232,55 +5278,61 @@
         <v>2010</v>
       </c>
       <c r="E68" t="n">
-        <v>0.5800000000000001</v>
+        <v>0.3866666666666667</v>
       </c>
       <c r="F68" t="n">
-        <v>0.524963768115942</v>
+        <v>0.4275751041483307</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5030900380759665</v>
+        <v>0.5236534804223293</v>
       </c>
       <c r="H68" t="n">
-        <v>0.989730736166938</v>
+        <v>0.001969129684745444</v>
       </c>
       <c r="I68" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J68" t="n">
-        <v>7</v>
+        <v>0.01939288522046403</v>
       </c>
       <c r="K68" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L68" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M68" t="n">
-        <v>0.5833333333333334</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U68" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0.3166666666666667</v>
+      <c r="V68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="69">
@@ -5303,54 +5355,60 @@
         <v>2010</v>
       </c>
       <c r="E69" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.5733333333333334</v>
       </c>
       <c r="F69" t="n">
-        <v>0.5287121212121212</v>
+        <v>0.4661764705882353</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3544079999999999</v>
+        <v>0.3586799999999999</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K69" t="n">
         <v>10</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>15</v>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
       <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N69" t="n">
-        <v>1</v>
-      </c>
-      <c r="O69" t="n">
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
         <v>0.4</v>
       </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>1</v>
-      </c>
       <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
         <v>0.4</v>
       </c>
-      <c r="S69" t="n">
+      <c r="U69" t="n">
         <v>0.3</v>
       </c>
-      <c r="T69" t="n">
+      <c r="V69" t="n">
         <v>0.2</v>
       </c>
-      <c r="U69" t="n">
+      <c r="W69" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5374,55 +5432,61 @@
         <v>2010</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4633333333333333</v>
+        <v>0.4066666666666667</v>
       </c>
       <c r="F70" t="n">
-        <v>0.451623661426293</v>
+        <v>0.4251940197408969</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3740614056587219</v>
+        <v>0.3805781602859497</v>
       </c>
       <c r="H70" t="n">
-        <v>0.002154259476810694</v>
+        <v>0.002162893069908023</v>
       </c>
       <c r="I70" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.001872273976914585</v>
+      </c>
+      <c r="K70" t="n">
         <v>9</v>
       </c>
-      <c r="J70" t="n">
-        <v>12</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1</v>
-      </c>
       <c r="L70" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M70" t="n">
-        <v>0.5806451612903226</v>
+        <v>1</v>
       </c>
       <c r="N70" t="n">
+        <v>2</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="P70" t="n">
         <v>0.9</v>
       </c>
-      <c r="O70" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="P70" t="n">
+      <c r="Q70" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="R70" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.48</v>
-      </c>
       <c r="S70" t="n">
-        <v>0.31</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T70" t="n">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="U70" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.1766666666666667</v>
       </c>
     </row>
     <row r="71">
@@ -5445,55 +5509,61 @@
         <v>2010</v>
       </c>
       <c r="E71" t="n">
-        <v>0.5733333333333334</v>
+        <v>0.4266666666666667</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4579013143719026</v>
+        <v>0.3962049062049062</v>
       </c>
       <c r="G71" t="n">
-        <v>0.3738023318957465</v>
+        <v>0.4562124845337451</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1000664228085696</v>
+        <v>3.554858606472577e-05</v>
       </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J71" t="n">
-        <v>10</v>
+        <v>1.09072699894247e-11</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L71" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M71" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>0.5</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.375</v>
       </c>
       <c r="R71" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="S71" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.36</v>
       </c>
       <c r="U71" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.37</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="72">
@@ -5516,54 +5586,60 @@
         <v>2010</v>
       </c>
       <c r="E72" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="F72" t="n">
-        <v>0.3800000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="G72" t="n">
-        <v>0.5174561747230945</v>
+        <v>0.4</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>10</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>15</v>
       </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
       <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N72" t="n">
-        <v>1</v>
-      </c>
-      <c r="O72" t="n">
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
         <v>0.4</v>
       </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>1</v>
-      </c>
       <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
         <v>0.4</v>
       </c>
-      <c r="S72" t="n">
+      <c r="U72" t="n">
         <v>0.3</v>
       </c>
-      <c r="T72" t="n">
+      <c r="V72" t="n">
         <v>0.2</v>
       </c>
-      <c r="U72" t="n">
+      <c r="W72" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5587,55 +5663,61 @@
         <v>2010</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5533333333333332</v>
       </c>
       <c r="F73" t="n">
-        <v>0.3986367880485527</v>
+        <v>0.4893393596950603</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3995650544502595</v>
+        <v>0.3990590730759576</v>
       </c>
       <c r="H73" t="n">
-        <v>1.231026478560298e-05</v>
+        <v>1.074627012688665e-05</v>
       </c>
       <c r="I73" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1.57490417645354e-05</v>
+      </c>
+      <c r="K73" t="n">
         <v>10</v>
       </c>
-      <c r="J73" t="n">
-        <v>14</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M73" t="n">
-        <v>0.5882352941176471</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R73" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.28</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T73" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="U73" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.26</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
     <row r="74">
@@ -5658,55 +5740,61 @@
         <v>2011</v>
       </c>
       <c r="E74" t="n">
-        <v>0.74</v>
+        <v>0.7866666666666667</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7347527706734868</v>
+        <v>0.7746482683982684</v>
       </c>
       <c r="G74" t="n">
-        <v>0.211632995105019</v>
+        <v>0.2470532795051399</v>
       </c>
       <c r="H74" t="n">
-        <v>0.290971252672042</v>
+        <v>0.01939288522046403</v>
       </c>
       <c r="I74" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J74" t="n">
-        <v>8</v>
+        <v>0.4975535857170837</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L74" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M74" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W74" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T74" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="75">
@@ -5729,55 +5817,61 @@
         <v>2011</v>
       </c>
       <c r="E75" t="n">
-        <v>0.78</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7494857430151548</v>
+        <v>0.6569981325863679</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1893035912855366</v>
+        <v>0.204650394831429</v>
       </c>
       <c r="H75" t="n">
-        <v>0.210067349666629</v>
+        <v>0.03</v>
       </c>
       <c r="I75" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.2321588011379844</v>
+      </c>
+      <c r="K75" t="n">
         <v>10</v>
       </c>
-      <c r="J75" t="n">
-        <v>8</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
       <c r="L75" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M75" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R75" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.16</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T75" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.44</v>
       </c>
       <c r="U75" t="n">
-        <v>0.05333333333333334</v>
+        <v>0.28</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="76">
@@ -5800,55 +5894,61 @@
         <v>2011</v>
       </c>
       <c r="E76" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7159967320261438</v>
+        <v>0.6418055555555555</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2143297344446182</v>
+        <v>0.2645997703075409</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1742832213640213</v>
+        <v>0.001872273976914585</v>
       </c>
       <c r="I76" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J76" t="n">
-        <v>4</v>
+        <v>0.07813262194395065</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L76" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M76" t="n">
-        <v>0.7272727272727273</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V76" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0.2133333333333334</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0.2066666666666667</v>
+      <c r="W76" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="77">
@@ -5871,55 +5971,61 @@
         <v>2011</v>
       </c>
       <c r="E77" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F77" t="n">
-        <v>0.7341033966033966</v>
+        <v>0.8370337995337994</v>
       </c>
       <c r="G77" t="n">
-        <v>0.2545645512652898</v>
+        <v>0.1954794322925021</v>
       </c>
       <c r="H77" t="n">
-        <v>0.01054320016443355</v>
+        <v>1.09072699894247e-11</v>
       </c>
       <c r="I77" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.5243791980505969</v>
+      </c>
+      <c r="K77" t="n">
         <v>10</v>
       </c>
-      <c r="J77" t="n">
-        <v>6</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
       <c r="L77" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7692307692307693</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
         <v>0.4</v>
       </c>
       <c r="R77" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="T77" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="U77" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="78">
@@ -5948,48 +6054,54 @@
         <v>0.4666666666666667</v>
       </c>
       <c r="G78" t="n">
-        <v>0.3226109650474491</v>
+        <v>0.322610965047449</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
         <v>10</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>15</v>
       </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
       <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N78" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" t="n">
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
         <v>0.4</v>
       </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
       <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
         <v>0.4</v>
       </c>
-      <c r="S78" t="n">
+      <c r="U78" t="n">
         <v>0.3</v>
       </c>
-      <c r="T78" t="n">
+      <c r="V78" t="n">
         <v>0.2</v>
       </c>
-      <c r="U78" t="n">
+      <c r="W78" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -6013,55 +6125,61 @@
         <v>2011</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8217748917748917</v>
+        <v>0.7354014939309056</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3115666961237586</v>
+        <v>0.2487747587928008</v>
       </c>
       <c r="H79" t="n">
-        <v>0.001923026225120567</v>
+        <v>1.57490417645354e-05</v>
       </c>
       <c r="I79" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>0.04638987501456326</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L79" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M79" t="n">
-        <v>0.8181818181818182</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>0.75</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W79" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0.11</v>
       </c>
     </row>
     <row r="80">
@@ -6084,55 +6202,61 @@
         <v>2012</v>
       </c>
       <c r="E80" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7755602240896359</v>
+        <v>0.7404636591478696</v>
       </c>
       <c r="G80" t="n">
-        <v>0.244125149440979</v>
+        <v>0.2382682857653633</v>
       </c>
       <c r="H80" t="n">
-        <v>0.495036289551843</v>
+        <v>0.4975535857170837</v>
       </c>
       <c r="I80" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.4882539184984808</v>
+      </c>
+      <c r="K80" t="n">
+        <v>6</v>
+      </c>
+      <c r="L80" t="n">
+        <v>6</v>
+      </c>
+      <c r="M80" t="n">
+        <v>4</v>
+      </c>
+      <c r="N80" t="n">
         <v>9</v>
       </c>
-      <c r="J80" t="n">
-        <v>8</v>
-      </c>
-      <c r="K80" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" t="n">
-        <v>7</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0.9</v>
-      </c>
       <c r="O80" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="P80" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="R80" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="S80" t="n">
-        <v>0.23</v>
+        <v>0.4</v>
       </c>
       <c r="T80" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="U80" t="n">
-        <v>0.1433333333333333</v>
+        <v>0.4</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="81">
@@ -6155,55 +6279,61 @@
         <v>2012</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9187698412698412</v>
+        <v>0.9338235294117647</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1436554446475785</v>
+        <v>0.1376764914821099</v>
       </c>
       <c r="H81" t="n">
-        <v>0.4495479177068525</v>
+        <v>0.2321588011379844</v>
       </c>
       <c r="I81" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0.5102398570754478</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L81" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M81" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="O81" t="n">
-        <v>0.9</v>
+        <v>0.625</v>
       </c>
       <c r="P81" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="R81" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.09</v>
+        <v>0.8</v>
       </c>
       <c r="T81" t="n">
-        <v>0.09333333333333335</v>
+        <v>0.52</v>
       </c>
       <c r="U81" t="n">
-        <v>0.09666666666666668</v>
+        <v>0.24</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0.08000000000000002</v>
       </c>
     </row>
     <row r="82">
@@ -6226,55 +6356,61 @@
         <v>2012</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9503174603174603</v>
+        <v>0.8756684491978609</v>
       </c>
       <c r="G82" t="n">
-        <v>0.09549164026975632</v>
+        <v>0.132617861032486</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3973187506198883</v>
+        <v>0.07813262194395065</v>
       </c>
       <c r="I82" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0.7102852463722229</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L82" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M82" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="O82" t="n">
-        <v>0.9</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P82" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="W82" t="n">
         <v>0.06666666666666667</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0.09333333333333335</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0.09666666666666668</v>
       </c>
     </row>
     <row r="83">
@@ -6297,55 +6433,61 @@
         <v>2012</v>
       </c>
       <c r="E83" t="n">
-        <v>0.92</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9033974358974358</v>
+        <v>0.7826785714285714</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1253949292607568</v>
+        <v>0.2396272653007037</v>
       </c>
       <c r="H83" t="n">
-        <v>0.4856115797517387</v>
+        <v>0.5243791980505969</v>
       </c>
       <c r="I83" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J83" t="n">
-        <v>2</v>
+        <v>0.7082722288405682</v>
       </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L83" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M83" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="O83" t="n">
-        <v>0.8</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="P83" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="R83" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="U83" t="n">
         <v>0.18</v>
       </c>
-      <c r="T83" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0.1933333333333334</v>
+      <c r="V83" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="84">
@@ -6368,55 +6510,61 @@
         <v>2012</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.6333333333333334</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7298245614035088</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1704497658054301</v>
+        <v>0.2962851030335958</v>
       </c>
       <c r="H84" t="n">
-        <v>0.5836298932384343</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.7243816254416963</v>
+      </c>
+      <c r="K84" t="n">
         <v>10</v>
       </c>
-      <c r="J84" t="n">
-        <v>9</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
       <c r="L84" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M84" t="n">
-        <v>0.6896551724137931</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="R84" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.18</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="U84" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="85">
@@ -6439,55 +6587,61 @@
         <v>2012</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9733333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9651515151515151</v>
+        <v>0.8766666666666666</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1374418432978003</v>
+        <v>0.1354755505234184</v>
       </c>
       <c r="H85" t="n">
-        <v>0.01095831572786022</v>
+        <v>0.04638987501456326</v>
       </c>
       <c r="I85" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.5268779753305677</v>
+      </c>
+      <c r="K85" t="n">
         <v>10</v>
-      </c>
-      <c r="J85" t="n">
-        <v>2</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>13</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9090909090909091</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O85" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R85" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.04</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T85" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="U85" t="n">
-        <v>0.01333333333333333</v>
+        <v>0.26</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -6523,7 +6677,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.645</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="3">
@@ -6533,7 +6687,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.732</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="4">
@@ -6543,7 +6697,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="5">
@@ -6553,7 +6707,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.645</v>
+        <v>0.611</v>
       </c>
     </row>
     <row r="6">
@@ -6563,7 +6717,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.725</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="7">
@@ -6573,7 +6727,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.742</v>
+        <v>0.73</v>
       </c>
     </row>
   </sheetData>
@@ -6649,25 +6803,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.645</v>
+        <v>0.601</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.429</v>
       </c>
       <c r="E2" t="n">
-        <v>0.986</v>
+        <v>0.833</v>
       </c>
       <c r="F2" t="n">
-        <v>0.425</v>
+        <v>0.313</v>
       </c>
       <c r="G2" t="n">
-        <v>0.014</v>
+        <v>0.167</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.847</v>
       </c>
       <c r="I2" t="n">
-        <v>0.148</v>
+        <v>0.303</v>
       </c>
     </row>
     <row r="3">
@@ -6682,25 +6836,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.732</v>
+        <v>0.714</v>
       </c>
       <c r="D3" t="n">
-        <v>0.658</v>
+        <v>0.468</v>
       </c>
       <c r="E3" t="n">
-        <v>0.971</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.546</v>
+        <v>0.356</v>
       </c>
       <c r="G3" t="n">
-        <v>0.029</v>
+        <v>0.188</v>
       </c>
       <c r="H3" t="n">
-        <v>0.463</v>
+        <v>0.635</v>
       </c>
       <c r="I3" t="n">
-        <v>0.116</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="4">
@@ -6715,25 +6869,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="D4" t="n">
-        <v>0.579</v>
+        <v>0.348</v>
       </c>
       <c r="E4" t="n">
-        <v>0.957</v>
+        <v>0.617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.461</v>
+        <v>0.28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.043</v>
+        <v>0.383</v>
       </c>
       <c r="H4" t="n">
         <v>0.5649999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.147</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="5">
@@ -6748,25 +6902,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.645</v>
+        <v>0.611</v>
       </c>
       <c r="D5" t="n">
-        <v>0.593</v>
+        <v>0.42</v>
       </c>
       <c r="E5" t="n">
-        <v>0.886</v>
+        <v>0.717</v>
       </c>
       <c r="F5" t="n">
-        <v>0.544</v>
+        <v>0.383</v>
       </c>
       <c r="G5" t="n">
-        <v>0.114</v>
+        <v>0.283</v>
       </c>
       <c r="H5" t="n">
-        <v>0.435</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.178</v>
+        <v>0.347</v>
       </c>
     </row>
     <row r="6">
@@ -6781,25 +6935,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.725</v>
+        <v>0.722</v>
       </c>
       <c r="D6" t="n">
-        <v>0.723</v>
+        <v>0.517</v>
       </c>
       <c r="E6" t="n">
-        <v>0.971</v>
+        <v>0.783</v>
       </c>
       <c r="F6" t="n">
-        <v>0.609</v>
+        <v>0.393</v>
       </c>
       <c r="G6" t="n">
-        <v>0.029</v>
+        <v>0.217</v>
       </c>
       <c r="H6" t="n">
-        <v>0.532</v>
+        <v>0.543</v>
       </c>
       <c r="I6" t="n">
-        <v>0.129</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="7">
@@ -6814,25 +6968,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.742</v>
+        <v>0.73</v>
       </c>
       <c r="D7" t="n">
-        <v>0.754</v>
+        <v>0.474</v>
       </c>
       <c r="E7" t="n">
-        <v>0.971</v>
+        <v>0.833</v>
       </c>
       <c r="F7" t="n">
-        <v>0.656</v>
+        <v>0.361</v>
       </c>
       <c r="G7" t="n">
-        <v>0.029</v>
+        <v>0.167</v>
       </c>
       <c r="H7" t="n">
-        <v>0.421</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.107</v>
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>
@@ -6878,7 +7032,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.645</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="3">
@@ -6888,7 +7042,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.732</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="4">
@@ -6898,7 +7052,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="5">
@@ -6908,7 +7062,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.645</v>
+        <v>0.611</v>
       </c>
     </row>
     <row r="6">
@@ -6918,7 +7072,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.725</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="7">
@@ -6928,7 +7082,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.742</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="8">
@@ -6943,7 +7097,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.601</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="9">
@@ -6953,7 +7107,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.713</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="10">
@@ -6963,7 +7117,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.655</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="11">
@@ -6973,7 +7127,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.654</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="12">
@@ -6983,7 +7137,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.719</v>
+        <v>0.6830000000000001</v>
       </c>
     </row>
     <row r="13">

--- a/outputs/results/12b/results_12b_final.xlsx
+++ b/outputs/results/12b/results_12b_final.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U85"/>
+  <dimension ref="A1:W85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -552,49 +562,55 @@
         <v>0.125</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1831758483242265</v>
+        <v>0.1836471768396607</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09122389628104793</v>
+        <v>0.8115926439969845</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>0.0956899472488848</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2222222222222222</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2916666666666667</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08750000000000001</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05833333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02916666666666667</v>
+        <v>0.75</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -623,49 +639,55 @@
         <v>0.25</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0561472351020488</v>
+        <v>0.06891600826341861</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2823529411764706</v>
+        <v>0.266969696969697</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>0.3613325202703692</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
-        <v>0.25</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.125</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="R3" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0375</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="T3" t="n">
-        <v>0.025</v>
+        <v>0.8</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0125</v>
+        <v>0.0625</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.02083333333333334</v>
       </c>
     </row>
     <row r="4">
@@ -688,55 +710,61 @@
         <v>2001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.875</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="F4" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G4" t="n">
-        <v>0.121742770075798</v>
+        <v>0.09867394715547562</v>
       </c>
       <c r="H4" t="n">
-        <v>0.522675633430481</v>
+        <v>0.3915393948554993</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>0.396131157875061</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O4" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.125</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R4" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0375</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="U4" t="n">
         <v>0.025</v>
       </c>
-      <c r="U4" t="n">
-        <v>0.0125</v>
+      <c r="V4" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.008333333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -765,49 +793,55 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1600052361472709</v>
+        <v>0.1236799872654891</v>
       </c>
       <c r="H5" t="n">
-        <v>1.300705435871653e-07</v>
+        <v>0.8653971016776723</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>0.000601057282557195</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.075</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05</v>
+        <v>0.88</v>
       </c>
       <c r="U5" t="n">
-        <v>0.025</v>
+        <v>0.725</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9083333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -830,55 +864,61 @@
         <v>2001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8958333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2121169116598058</v>
+        <v>0.131308506841166</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9068219633943428</v>
+        <v>0.8365758754863813</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2857142857142857</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0625</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.88</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02083333333333334</v>
+        <v>0.725</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9083333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -901,55 +941,61 @@
         <v>2001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.875</v>
+        <v>0.7083333333333333</v>
       </c>
       <c r="F7" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1102600918006365</v>
+        <v>0.05297445994623682</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009680070421468673</v>
+        <v>0.4184149980263097</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>8.468308702670781e-05</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0375</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="T7" t="n">
-        <v>0.025</v>
+        <v>0.92</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0125</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -972,55 +1018,61 @@
         <v>2002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5833333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4300547054110133</v>
+        <v>0.4509361566532923</v>
       </c>
       <c r="H8" t="n">
-        <v>0.663812004632659</v>
+        <v>0.0956899472488848</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>0.6527581586631412</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.04</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08333333333333334</v>
+        <v>0.04</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1043,55 +1095,61 @@
         <v>2002</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0451054236909176</v>
+        <v>0.08631381865900589</v>
       </c>
       <c r="H9" t="n">
-        <v>0.545790035283727</v>
+        <v>0.3613325202703692</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.6180347728103447</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.03333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -1120,49 +1178,55 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07728493958711624</v>
+        <v>0.1050450354814529</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6937016248703003</v>
+        <v>0.396131157875061</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.5674696564674377</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.0625</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.02083333333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1185,55 +1249,61 @@
         <v>2002</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5833333333333333</v>
+        <v>0.375</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.0625</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4616694834296106</v>
+        <v>0.5275458417632176</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7417925436734171</v>
+        <v>0.000601057282557195</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>0.5992521907548122</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.04</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08333333333333334</v>
+        <v>0.04</v>
       </c>
       <c r="U11" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -1265,46 +1335,52 @@
         <v>0.2130889204417722</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.8425925925925926</v>
       </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.25</v>
+        <v>0.04</v>
       </c>
       <c r="R12" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.075</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="U12" t="n">
-        <v>0.025</v>
+        <v>0.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="13">
@@ -1327,55 +1403,61 @@
         <v>2002</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05070693633000434</v>
+        <v>0.07594582549224865</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2072573464424945</v>
+        <v>8.468308702670781e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>0.4296837766497136</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.04</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.04</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02083333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
@@ -1398,56 +1480,32 @@
         <v>2008</v>
       </c>
       <c r="E14" t="n">
-        <v>0.375</v>
+        <v>0.3611111111111112</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5865063598710034</v>
+        <v>0.5764741980828433</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5098728236500527</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.0003426246448590228</v>
-      </c>
-      <c r="I14" t="n">
-        <v>16</v>
-      </c>
+        <v>0.5619095848567998</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.0009144036573601353</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1469,56 +1527,32 @@
         <v>2008</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4895833333333334</v>
+        <v>0.4618055555555556</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6179359243697479</v>
+        <v>0.6105471734148205</v>
       </c>
       <c r="G15" t="n">
-        <v>0.614984</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>16</v>
-      </c>
+        <v>0.618112</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>9</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1543,53 +1577,29 @@
         <v>0.4861111111111111</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6229916121460238</v>
+        <v>0.6206570537473923</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6358895897865295</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.001354562235064805</v>
-      </c>
-      <c r="I16" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6481840014457703</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.1777777777777778</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.08888888888888889</v>
-      </c>
+        <v>0.001618588343262672</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1611,56 +1621,32 @@
         <v>2008</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3402777777777778</v>
+        <v>0.3194444444444444</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5710335514294451</v>
+        <v>0.605040609848752</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5908596673905517</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4.568221092737065e-05</v>
-      </c>
-      <c r="I17" t="n">
-        <v>16</v>
-      </c>
+        <v>0.5608136068583145</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.0002006686473018926</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1682,56 +1668,32 @@
         <v>2008</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.3645833333333334</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6124999999999999</v>
+        <v>0.615625</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6832927615033462</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>16</v>
-      </c>
+        <v>0.657155326324142</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>9</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1753,56 +1715,32 @@
         <v>2008</v>
       </c>
       <c r="E19" t="n">
-        <v>0.625</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7252919333082377</v>
+        <v>0.6584886920845453</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6126608297603905</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.421227358443719e-05</v>
-      </c>
-      <c r="I19" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6298669869849081</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.8205128205128205</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.6956521739130435</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.2333333333333333</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.1555555555555556</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.07777777777777778</v>
-      </c>
+        <v>6.824587925004975e-06</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1824,55 +1762,61 @@
         <v>2009</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7714425555618011</v>
+        <v>0.8020515652433222</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2205441333509373</v>
+        <v>0.1786449136473614</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4414598957633341</v>
+        <v>0.0009144036573601353</v>
       </c>
       <c r="I20" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4080939279824498</v>
+      </c>
+      <c r="K20" t="n">
         <v>16</v>
       </c>
-      <c r="J20" t="n">
-        <v>7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8205128205128205</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="R20" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2333333333333333</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="21">
@@ -1895,54 +1839,60 @@
         <v>2009</v>
       </c>
       <c r="E21" t="n">
-        <v>0.638888888888889</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7317536450645719</v>
+        <v>0.7224653053237613</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2655584566128624</v>
+        <v>0.2666777138454674</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1642315720101805</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.2825421152861742</v>
+      </c>
+      <c r="K21" t="n">
         <v>16</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
         <v>0.64</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
       <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
         <v>0.64</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.3</v>
       </c>
-      <c r="T21" t="n">
+      <c r="V21" t="n">
         <v>0.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1966,55 +1916,61 @@
         <v>2009</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6546819959044223</v>
+        <v>0.7228441070117271</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3714910447597504</v>
+        <v>0.3315051198005676</v>
       </c>
       <c r="H22" t="n">
-        <v>0.02352490834891796</v>
+        <v>0.001618588343262672</v>
       </c>
       <c r="I22" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.03533859923481941</v>
+      </c>
+      <c r="K22" t="n">
         <v>16</v>
       </c>
-      <c r="J22" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8421052631578947</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.64</v>
       </c>
       <c r="R22" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V22" t="n">
         <v>0.2</v>
       </c>
-      <c r="T22" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.06666666666666667</v>
+      <c r="W22" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="23">
@@ -2037,55 +1993,61 @@
         <v>2009</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.7638888888888888</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7444331219806763</v>
+        <v>0.8610949677150335</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2369984395980911</v>
+        <v>0.2094815155552946</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4310298584365538</v>
+        <v>0.0002006686473018926</v>
       </c>
       <c r="I23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.6209759339927547</v>
+      </c>
+      <c r="K23" t="n">
         <v>16</v>
       </c>
-      <c r="J23" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8205128205128205</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="R23" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2333333333333333</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
@@ -2108,54 +2070,60 @@
         <v>2009</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6458333333333333</v>
+        <v>0.4027777777777778</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7511458333333333</v>
+        <v>0.605</v>
       </c>
       <c r="G24" t="n">
-        <v>0.313669502135048</v>
+        <v>0.64</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>16</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>9</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
         <v>0.64</v>
       </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
       <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
         <v>0.64</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.3</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.2</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2179,55 +2147,61 @@
         <v>2009</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6462810453435454</v>
+        <v>0.6516699580042981</v>
       </c>
       <c r="G25" t="n">
-        <v>0.482497914375094</v>
+        <v>0.4866952291270553</v>
       </c>
       <c r="H25" t="n">
-        <v>6.802663028485531e-06</v>
+        <v>6.824587925004975e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J25" t="n">
-        <v>9</v>
+        <v>1.235884600519886e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7804878048780488</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
+        <v>0.7567567567567568</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="T25" t="n">
         <v>0.64</v>
       </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.2</v>
-      </c>
       <c r="U25" t="n">
-        <v>0.1</v>
+        <v>0.3208333333333333</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.2555555555555555</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.1902777777777778</v>
       </c>
     </row>
     <row r="26">
@@ -2250,55 +2224,61 @@
         <v>2010</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5866666666666666</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6009764796606901</v>
+        <v>0.4970797258297258</v>
       </c>
       <c r="G26" t="n">
-        <v>0.462651516315676</v>
+        <v>0.462497155461812</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8357399084843402</v>
+        <v>0.4080939279824498</v>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>2009</v>
       </c>
       <c r="J26" t="n">
+        <v>0.9749170792842414</v>
+      </c>
+      <c r="K26" t="n">
         <v>10</v>
       </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6206896551724138</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.27</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2133333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1566666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="27">
@@ -2321,55 +2301,61 @@
         <v>2010</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="F27" t="n">
-        <v>0.42589508530685</v>
+        <v>0.3910463068586638</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3533496577136402</v>
+        <v>0.2553636145459939</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3205606899313307</v>
+        <v>0.2825421152861742</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J27" t="n">
-        <v>15</v>
+        <v>0.2801845156786292</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5714285714285714</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>0.4</v>
+        <v>0.5625</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="S27" t="n">
-        <v>0.3</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1</v>
+        <v>0.33</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.1766666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -2392,55 +2378,61 @@
         <v>2010</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4799596157719728</v>
+        <v>0.5114862914862914</v>
       </c>
       <c r="G28" t="n">
-        <v>0.376446545124054</v>
+        <v>0.2496045082807541</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09784837067127228</v>
+        <v>0.03533859923481941</v>
       </c>
       <c r="I28" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.3069948554039001</v>
+      </c>
+      <c r="K28" t="n">
         <v>10</v>
       </c>
-      <c r="J28" t="n">
-        <v>13</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6060606060606061</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1733333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U28" t="n">
-        <v>0.08666666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="29">
@@ -2463,55 +2455,61 @@
         <v>2010</v>
       </c>
       <c r="E29" t="n">
-        <v>0.62</v>
+        <v>0.5866666666666667</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6987895256916996</v>
+        <v>0.4738095238095238</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4097468804483028</v>
+        <v>0.4101450382236351</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9936514111704592</v>
+        <v>0.6209759339927547</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>2009</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.6909560159080471</v>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M29" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="R29" t="n">
-        <v>0.76</v>
+        <v>0.1</v>
       </c>
       <c r="S29" t="n">
-        <v>0.37</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T29" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="U29" t="n">
-        <v>0.4566666666666667</v>
+        <v>0.33</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.1766666666666667</v>
       </c>
     </row>
     <row r="30">
@@ -2534,54 +2532,60 @@
         <v>2010</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4533333333333333</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3768990658464343</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4962243253487426</v>
+        <v>0.2827410086533262</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5625000000000002</v>
+      </c>
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2010</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5147823734236777</v>
+        <v>0.5318909592822636</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4018680147158371</v>
+        <v>0.2863687222023407</v>
       </c>
       <c r="H31" t="n">
-        <v>0.001111154599566572</v>
+        <v>1.235884600519886e-06</v>
       </c>
       <c r="I31" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.04922765666868816</v>
+      </c>
+      <c r="K31" t="n">
         <v>10</v>
       </c>
-      <c r="J31" t="n">
-        <v>13</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M31" t="n">
-        <v>0.6060606060606061</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1733333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U31" t="n">
-        <v>0.08666666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="32">
@@ -2679,52 +2689,58 @@
         <v>0.7933333333333333</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8018414918414918</v>
+        <v>0.7671717171717171</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2288056604495035</v>
+        <v>0.219576832553966</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5207668870685651</v>
+        <v>0.9749170792842414</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>0.5111454293706877</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.72</v>
+        <v>10</v>
       </c>
       <c r="N32" t="n">
+        <v>15</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W32" t="n">
         <v>0.9</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.13</v>
       </c>
     </row>
     <row r="33">
@@ -2747,55 +2763,61 @@
         <v>2011</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.7533333333333334</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7308333333333333</v>
+        <v>0.7124566661408767</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2267831049810215</v>
+        <v>0.2128446257662256</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5640755320597821</v>
+        <v>0.2801845156786292</v>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>0.5276143793426379</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7272727272727273</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>0.8</v>
       </c>
-      <c r="O33" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0.22</v>
-      </c>
       <c r="T33" t="n">
-        <v>0.2133333333333334</v>
+        <v>0.52</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2066666666666667</v>
+        <v>0.24</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.08000000000000002</v>
       </c>
     </row>
     <row r="34">
@@ -2818,55 +2840,61 @@
         <v>2011</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8733333333333333</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8384099672257567</v>
+        <v>0.7161953242835596</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1533974409103394</v>
+        <v>0.1850810199975967</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5449708700180054</v>
+        <v>0.3069948554039001</v>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>0.4444350302219391</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L34" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U34" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="V34" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="R34" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.1933333333333334</v>
+      <c r="W34" t="n">
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="35">
@@ -2889,55 +2917,61 @@
         <v>2011</v>
       </c>
       <c r="E35" t="n">
-        <v>0.76</v>
+        <v>0.6733333333333333</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7557448107448107</v>
+        <v>0.7199028822055137</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2243169500719387</v>
+        <v>0.2030233027524646</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8917110644340588</v>
+        <v>0.6909560159080471</v>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>2010</v>
       </c>
       <c r="J35" t="n">
+        <v>0.6109477836751329</v>
+      </c>
+      <c r="K35" t="n">
         <v>2</v>
       </c>
-      <c r="K35" t="n">
-        <v>3</v>
-      </c>
       <c r="L35" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7368421052631579</v>
+        <v>8</v>
       </c>
       <c r="N35" t="n">
-        <v>0.7</v>
+        <v>15</v>
       </c>
       <c r="O35" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="P35" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1333333333333333</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0.8</v>
       </c>
       <c r="S35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.68</v>
       </c>
       <c r="U35" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.5599999999999999</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.6400000000000001</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.7200000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -2960,55 +2994,61 @@
         <v>2011</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.61</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5181818181818181</v>
+        <v>0.4905194805194805</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3262565966005779</v>
+        <v>0.2904002018767876</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000002</v>
       </c>
       <c r="I36" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>6</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5</v>
+      </c>
+      <c r="M36" t="n">
+        <v>4</v>
+      </c>
+      <c r="N36" t="n">
         <v>10</v>
       </c>
-      <c r="J36" t="n">
-        <v>12</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>3</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
       <c r="O36" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.8</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="R36" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="S36" t="n">
-        <v>0.24</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T36" t="n">
-        <v>0.16</v>
+        <v>0.64</v>
       </c>
       <c r="U36" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3799999999999999</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.3866666666666667</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.3933333333333334</v>
       </c>
     </row>
     <row r="37">
@@ -3031,55 +3071,61 @@
         <v>2011</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8600000000000001</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8255483405483405</v>
+        <v>0.7423260073260073</v>
       </c>
       <c r="G37" t="n">
-        <v>0.175041012584231</v>
+        <v>0.1744577951050522</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5896137652913739</v>
+        <v>0.04922765666868816</v>
       </c>
       <c r="I37" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0.4661471265280961</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L37" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W37" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.1066666666666667</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.1033333333333333</v>
       </c>
     </row>
     <row r="38">
@@ -3102,55 +3148,61 @@
         <v>2012</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8057792207792207</v>
+        <v>0.75</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1820026267412815</v>
+        <v>0.2370193623775158</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4569239996556106</v>
+        <v>0.5111454293706877</v>
       </c>
       <c r="I38" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J38" t="n">
-        <v>6</v>
+        <v>0.5222298228152165</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M38" t="n">
-        <v>0.72</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="O38" t="n">
-        <v>0.6</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="P38" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.4</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="R38" t="n">
-        <v>0.72</v>
+        <v>0.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0.19</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T38" t="n">
-        <v>0.16</v>
+        <v>0.68</v>
       </c>
       <c r="U38" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.3066666666666666</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.3033333333333333</v>
       </c>
     </row>
     <row r="39">
@@ -3173,55 +3225,61 @@
         <v>2012</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8733333333333334</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8352480852480851</v>
+        <v>0.8236588360040372</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1579551269153233</v>
+        <v>0.2008159237947522</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4118244893895048</v>
+        <v>0.5276143793426379</v>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>2011</v>
       </c>
       <c r="J39" t="n">
-        <v>5</v>
+        <v>0.6957457706122413</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M39" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" t="n">
+        <v>8</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P39" t="n">
         <v>0.8</v>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
       <c r="Q39" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="R39" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="S39" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="T39" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.64</v>
       </c>
       <c r="U39" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.28</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.2266666666666667</v>
       </c>
     </row>
     <row r="40">
@@ -3244,55 +3302,61 @@
         <v>2012</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.9066666666666667</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8566766566766565</v>
+        <v>0.9150735294117648</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1541679799556732</v>
+        <v>0.1717620491981506</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5303398370742798</v>
+        <v>0.4444350302219391</v>
       </c>
       <c r="I40" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.8749179840087891</v>
+      </c>
+      <c r="K40" t="n">
         <v>10</v>
       </c>
-      <c r="J40" t="n">
-        <v>4</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="R40" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.08</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="T40" t="n">
-        <v>0.05333333333333334</v>
+        <v>0.72</v>
       </c>
       <c r="U40" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.14</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.09333333333333334</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.04666666666666667</v>
       </c>
     </row>
     <row r="41">
@@ -3315,55 +3379,61 @@
         <v>2012</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.78</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8432792207792207</v>
+        <v>0.7927777777777777</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2891520057757666</v>
+        <v>0.2100079321674809</v>
       </c>
       <c r="H41" t="n">
-        <v>0.03280988250236398</v>
+        <v>0.6109477836751329</v>
       </c>
       <c r="I41" t="n">
-        <v>10</v>
+        <v>2011</v>
       </c>
       <c r="J41" t="n">
-        <v>6</v>
+        <v>0.5688993840252026</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L41" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7692307692307693</v>
+        <v>5</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O41" t="n">
         <v>0.625</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.4</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="R41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="T41" t="n">
         <v>0.76</v>
       </c>
-      <c r="S41" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0.08000000000000002</v>
-      </c>
       <c r="U41" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.37</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.4133333333333333</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.4566666666666667</v>
       </c>
     </row>
     <row r="42">
@@ -3386,55 +3456,61 @@
         <v>2012</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6633333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4930515236397589</v>
+        <v>0.6253174603174604</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3505251175127529</v>
+        <v>0.2369748790392554</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8549222797927462</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J42" t="n">
-        <v>8</v>
+        <v>0.2453531598513012</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L42" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W42" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="43">
@@ -3457,55 +3533,61 @@
         <v>2012</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.8866666666666667</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8709973798131693</v>
+        <v>0.8771767040149393</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1410939947454191</v>
+        <v>0.1873324920323335</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6244520695965369</v>
+        <v>0.4661471265280961</v>
       </c>
       <c r="I43" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.863739131579775</v>
+      </c>
+      <c r="K43" t="n">
+        <v>10</v>
+      </c>
+      <c r="L43" t="n">
         <v>9</v>
       </c>
-      <c r="J43" t="n">
-        <v>2</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" t="n">
-        <v>13</v>
-      </c>
       <c r="M43" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="O43" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="P43" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="R43" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.11</v>
+        <v>0.6</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.64</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1033333333333333</v>
+        <v>0.18</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="44">
@@ -3534,49 +3616,55 @@
         <v>0.25</v>
       </c>
       <c r="G44" t="n">
-        <v>0.09768099359929368</v>
+        <v>0.0998774808583168</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3962694950060163</v>
+        <v>0.8769114735537481</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>0.3957285086588387</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O44" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0375</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="T44" t="n">
-        <v>0.025</v>
+        <v>0.92</v>
       </c>
       <c r="U44" t="n">
-        <v>0.0125</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="45">
@@ -3599,55 +3687,61 @@
         <v>2001</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9791666666666666</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02668565325738697</v>
+        <v>0.02840650887573965</v>
       </c>
       <c r="H45" t="n">
-        <v>0.270440251572327</v>
+        <v>0.42</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O45" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.04166666666666666</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
         <v>0.96</v>
       </c>
-      <c r="S45" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0.008333333333333333</v>
-      </c>
       <c r="U45" t="n">
-        <v>0.004166666666666667</v>
+        <v>0.7</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="46">
@@ -3670,55 +3764,61 @@
         <v>2001</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0.9583333333333333</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G46" t="n">
-        <v>0.008356071077287197</v>
+        <v>0.03113862313330173</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6254370808601379</v>
+        <v>0.01189725659787655</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.4251637756824493</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>24</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
@@ -3747,49 +3847,55 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="G47" t="n">
-        <v>0.06771062317752044</v>
+        <v>0.07810709097109021</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4054822920698812</v>
+        <v>0.9564123037321103</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>0.03306347002895278</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O47" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="T47" t="n">
         <v>0.92</v>
       </c>
-      <c r="S47" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0.01666666666666667</v>
-      </c>
       <c r="U47" t="n">
-        <v>0.008333333333333333</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="48">
@@ -3821,28 +3927,28 @@
         <v>0.000292205420410548</v>
       </c>
       <c r="H48" t="n">
+        <v>0.9655172413793105</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J48" t="n">
         <v>0.9145299145299146</v>
       </c>
-      <c r="I48" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" t="n">
         <v>24</v>
       </c>
-      <c r="M48" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -3857,10 +3963,16 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>0.7</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="49">
@@ -3883,55 +3995,61 @@
         <v>2001</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1195659958439588</v>
+        <v>0.06967383574717595</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0009349436569170327</v>
+        <v>0.6163617227386412</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>0.178991532866457</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O49" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="T49" t="n">
         <v>0.92</v>
       </c>
-      <c r="S49" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0.01666666666666667</v>
-      </c>
       <c r="U49" t="n">
-        <v>0.008333333333333333</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="50">
@@ -3954,55 +4072,61 @@
         <v>2002</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4583333333333334</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="F50" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4757245492139788</v>
+        <v>0.5530484267646981</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5448897249792384</v>
+        <v>0.3957285086588387</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J50" t="n">
-        <v>13</v>
+        <v>0.5190616493069908</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O50" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.0625</v>
       </c>
       <c r="R50" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.1625</v>
+        <v>0.625</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1083333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U50" t="n">
-        <v>0.05416666666666667</v>
+        <v>0.1875</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.0625</v>
       </c>
     </row>
     <row r="51">
@@ -4025,55 +4149,61 @@
         <v>2002</v>
       </c>
       <c r="E51" t="n">
-        <v>0.625</v>
+        <v>0.5416666666666667</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="G51" t="n">
-        <v>0.07180640826809585</v>
+        <v>0.0709368997954616</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1848486033749054</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J51" t="n">
-        <v>9</v>
+        <v>0.1078055045054479</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1818181818181818</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O51" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.1125</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="T51" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="U51" t="n">
-        <v>0.03750000000000001</v>
+        <v>0.7625</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.8416666666666667</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.9208333333333334</v>
       </c>
     </row>
     <row r="52">
@@ -4096,55 +4226,61 @@
         <v>2002</v>
       </c>
       <c r="E52" t="n">
-        <v>0.04166666666666669</v>
+        <v>0.125</v>
       </c>
       <c r="F52" t="n">
-        <v>0.04</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1641695648431778</v>
+        <v>0.1773403137922287</v>
       </c>
       <c r="H52" t="n">
-        <v>0.05124238878488541</v>
+        <v>0.4251637756824493</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>0.02365847304463387</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M52" t="n">
-        <v>0.07692307692307693</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O52" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>0.3</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="T52" t="n">
-        <v>0.2</v>
+        <v>0.76</v>
       </c>
       <c r="U52" t="n">
-        <v>0.1</v>
+        <v>0.7625</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.8416666666666667</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.9208333333333334</v>
       </c>
     </row>
     <row r="53">
@@ -4167,55 +4303,61 @@
         <v>2002</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4166666666666666</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="F53" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3957525842271876</v>
+        <v>0.3619579387138055</v>
       </c>
       <c r="H53" t="n">
-        <v>0.08635327756783583</v>
+        <v>0.03306347002895278</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J53" t="n">
-        <v>14</v>
+        <v>0.07624087266249258</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M53" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O53" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="R53" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.175</v>
+        <v>0.5</v>
       </c>
       <c r="T53" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.52</v>
       </c>
       <c r="U53" t="n">
-        <v>0.05833333333333334</v>
+        <v>0.15</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="54">
@@ -4247,46 +4389,52 @@
         <v>0.2126371912881646</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.9145299145299146</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J54" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M54" t="n">
-        <v>0.07692307692307693</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O54" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>0.3</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="T54" t="n">
-        <v>0.2</v>
+        <v>0.76</v>
       </c>
       <c r="U54" t="n">
-        <v>0.1</v>
+        <v>0.7625</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.8416666666666667</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.9208333333333334</v>
       </c>
     </row>
     <row r="55">
@@ -4309,55 +4457,61 @@
         <v>2002</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7083333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="F55" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1026603154118692</v>
+        <v>0.04016094608547745</v>
       </c>
       <c r="H55" t="n">
-        <v>0.03830964192992885</v>
+        <v>0.178991532866457</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J55" t="n">
-        <v>7</v>
+        <v>0.005325397351642214</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2222222222222222</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O55" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.2916666666666667</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0.08750000000000001</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0.05833333333333334</v>
+        <v>0.96</v>
       </c>
       <c r="U55" t="n">
-        <v>0.02916666666666667</v>
+        <v>0.7</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="56">
@@ -4380,56 +4534,32 @@
         <v>2008</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.4930555555555556</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7461318204821494</v>
+        <v>0.6596023405941883</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5269514292019705</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.0004238894723492777</v>
-      </c>
-      <c r="I56" t="n">
-        <v>15</v>
-      </c>
+        <v>0.5949789787154234</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
-        <v>7</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" t="n">
-        <v>2</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.7894736842105263</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0.6818181818181818</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0.2770833333333333</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0.2055555555555555</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0.1340277777777778</v>
-      </c>
+        <v>2.095342901271278e-05</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4451,56 +4581,32 @@
         <v>2008</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.4930555555555556</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6829166666666667</v>
+        <v>0.6825</v>
       </c>
       <c r="G57" t="n">
-        <v>0.624008</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6277919999999999</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>9</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4522,56 +4628,32 @@
         <v>2008</v>
       </c>
       <c r="E58" t="n">
-        <v>0.5069444444444444</v>
+        <v>0.5659722222222222</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6754186246867168</v>
+        <v>0.7523041134590047</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6322618722915649</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.0005854230257682502</v>
-      </c>
-      <c r="I58" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6336380839347839</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
-        <v>9</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.001106431591324508</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4593,56 +4675,32 @@
         <v>2008</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4652777777777778</v>
+        <v>0.4583333333333334</v>
       </c>
       <c r="F59" t="n">
-        <v>0.663849557608938</v>
+        <v>0.6833392032052056</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5895138386480303</v>
-      </c>
-      <c r="H59" t="n">
-        <v>6.758511167435938e-06</v>
-      </c>
-      <c r="I59" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6064713636422761</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>9</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N59" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0.1</v>
-      </c>
+        <v>5.23754219088253e-06</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4672,48 +4730,24 @@
       <c r="G60" t="n">
         <v>0.64</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>16</v>
-      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>9</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4735,56 +4769,32 @@
         <v>2008</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4375</v>
+        <v>0.5069444444444444</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6164975491438087</v>
+        <v>0.6792103148077413</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6397414400281456</v>
-      </c>
-      <c r="H61" t="n">
-        <v>4.066190212334127e-07</v>
-      </c>
-      <c r="I61" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6389830189761644</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
-        <v>9</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0.1</v>
-      </c>
+        <v>8.103915832325728e-07</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4806,54 +4816,60 @@
         <v>2009</v>
       </c>
       <c r="E62" t="n">
-        <v>0.5902777777777778</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7317095736389214</v>
+        <v>0.6370509014012303</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4113046110193712</v>
+        <v>0.5073098927030608</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0009987528090520381</v>
+        <v>2.095342901271278e-05</v>
       </c>
       <c r="I62" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.001969129684745444</v>
+      </c>
+      <c r="K62" t="n">
         <v>16</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>9</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
       <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N62" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" t="n">
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
         <v>0.64</v>
       </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
       <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
         <v>0.64</v>
       </c>
-      <c r="S62" t="n">
+      <c r="U62" t="n">
         <v>0.3</v>
       </c>
-      <c r="T62" t="n">
+      <c r="V62" t="n">
         <v>0.2</v>
       </c>
-      <c r="U62" t="n">
+      <c r="W62" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4877,54 +4893,60 @@
         <v>2009</v>
       </c>
       <c r="E63" t="n">
-        <v>0.5208333333333333</v>
+        <v>0.4375000000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6383482142857142</v>
+        <v>0.5838235294117647</v>
       </c>
       <c r="G63" t="n">
-        <v>0.593212</v>
+        <v>0.607796</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>16</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>9</v>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
       <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N63" t="n">
-        <v>1</v>
-      </c>
-      <c r="O63" t="n">
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
         <v>0.64</v>
       </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>1</v>
-      </c>
       <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
         <v>0.64</v>
       </c>
-      <c r="S63" t="n">
+      <c r="U63" t="n">
         <v>0.3</v>
       </c>
-      <c r="T63" t="n">
+      <c r="V63" t="n">
         <v>0.2</v>
       </c>
-      <c r="U63" t="n">
+      <c r="W63" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4948,55 +4970,61 @@
         <v>2009</v>
       </c>
       <c r="E64" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.625</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6652778843057228</v>
+        <v>0.6911767766547178</v>
       </c>
       <c r="G64" t="n">
-        <v>0.6223048567771912</v>
+        <v>0.6291800141334534</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0006677798228338361</v>
+        <v>0.001106431591324508</v>
       </c>
       <c r="I64" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.002162893069908023</v>
+      </c>
+      <c r="K64" t="n">
         <v>16</v>
       </c>
-      <c r="J64" t="n">
-        <v>8</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M64" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R64" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U64" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="65">
@@ -5019,55 +5047,61 @@
         <v>2009</v>
       </c>
       <c r="E65" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="F65" t="n">
-        <v>0.6603090379935346</v>
+        <v>0.5750515865741249</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5095793659237123</v>
+        <v>0.613384449538092</v>
       </c>
       <c r="H65" t="n">
-        <v>0.000106223273925163</v>
+        <v>5.23754219088253e-06</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J65" t="n">
+        <v>3.387688219208574e-07</v>
+      </c>
+      <c r="K65" t="n">
+        <v>15</v>
+      </c>
+      <c r="L65" t="n">
         <v>9</v>
       </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
       <c r="M65" t="n">
-        <v>0.7804878048780488</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="R65" t="n">
-        <v>0.64</v>
+        <v>0.0625</v>
       </c>
       <c r="S65" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="U65" t="n">
-        <v>0.1</v>
+        <v>0.34375</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0.15625</v>
       </c>
     </row>
     <row r="66">
@@ -5102,42 +5136,48 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>16</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>9</v>
       </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
       <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
         <v>0.64</v>
       </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1</v>
-      </c>
       <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
         <v>0.64</v>
       </c>
-      <c r="S66" t="n">
+      <c r="U66" t="n">
         <v>0.3</v>
       </c>
-      <c r="T66" t="n">
+      <c r="V66" t="n">
         <v>0.2</v>
       </c>
-      <c r="U66" t="n">
+      <c r="W66" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5161,55 +5201,61 @@
         <v>2009</v>
       </c>
       <c r="E67" t="n">
-        <v>0.6041666666666667</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6997313140076298</v>
+        <v>0.6596410192358082</v>
       </c>
       <c r="G67" t="n">
-        <v>0.6367494291863808</v>
+        <v>0.63989224017819</v>
       </c>
       <c r="H67" t="n">
-        <v>1.573236477062979e-05</v>
+        <v>8.103915832325728e-07</v>
       </c>
       <c r="I67" t="n">
-        <v>14</v>
+        <v>2008</v>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>1.074627012688665e-05</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="L67" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M67" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P67" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="R67" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.2541666666666667</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0.2111111111111111</v>
+        <v>0.64</v>
       </c>
       <c r="U67" t="n">
-        <v>0.1680555555555556</v>
+        <v>0.3</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="68">
@@ -5232,55 +5278,61 @@
         <v>2010</v>
       </c>
       <c r="E68" t="n">
-        <v>0.5800000000000001</v>
+        <v>0.3866666666666667</v>
       </c>
       <c r="F68" t="n">
-        <v>0.524963768115942</v>
+        <v>0.4275751041483307</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5030900380759665</v>
+        <v>0.5236534804223293</v>
       </c>
       <c r="H68" t="n">
-        <v>0.989730736166938</v>
+        <v>0.001969129684745444</v>
       </c>
       <c r="I68" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J68" t="n">
-        <v>7</v>
+        <v>0.01939288522046403</v>
       </c>
       <c r="K68" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L68" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M68" t="n">
-        <v>0.5833333333333334</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U68" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0.3166666666666667</v>
+      <c r="V68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="69">
@@ -5303,54 +5355,60 @@
         <v>2010</v>
       </c>
       <c r="E69" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.5733333333333334</v>
       </c>
       <c r="F69" t="n">
-        <v>0.5287121212121212</v>
+        <v>0.4463492063492063</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3544079999999999</v>
+        <v>0.3627719999999999</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K69" t="n">
         <v>10</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>15</v>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
       <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N69" t="n">
-        <v>1</v>
-      </c>
-      <c r="O69" t="n">
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
         <v>0.4</v>
       </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>1</v>
-      </c>
       <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
         <v>0.4</v>
       </c>
-      <c r="S69" t="n">
+      <c r="U69" t="n">
         <v>0.3</v>
       </c>
-      <c r="T69" t="n">
+      <c r="V69" t="n">
         <v>0.2</v>
       </c>
-      <c r="U69" t="n">
+      <c r="W69" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5374,55 +5432,61 @@
         <v>2010</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4633333333333333</v>
+        <v>0.4066666666666667</v>
       </c>
       <c r="F70" t="n">
-        <v>0.451623661426293</v>
+        <v>0.4251940197408969</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3740614056587219</v>
+        <v>0.3805781602859497</v>
       </c>
       <c r="H70" t="n">
-        <v>0.002154259476810694</v>
+        <v>0.002162893069908023</v>
       </c>
       <c r="I70" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.001872273976914585</v>
+      </c>
+      <c r="K70" t="n">
         <v>9</v>
       </c>
-      <c r="J70" t="n">
-        <v>12</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1</v>
-      </c>
       <c r="L70" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M70" t="n">
-        <v>0.5806451612903226</v>
+        <v>1</v>
       </c>
       <c r="N70" t="n">
+        <v>2</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="P70" t="n">
         <v>0.9</v>
       </c>
-      <c r="O70" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="P70" t="n">
+      <c r="Q70" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="R70" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.48</v>
-      </c>
       <c r="S70" t="n">
-        <v>0.31</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T70" t="n">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="U70" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.1766666666666667</v>
       </c>
     </row>
     <row r="71">
@@ -5445,55 +5509,61 @@
         <v>2010</v>
       </c>
       <c r="E71" t="n">
-        <v>0.5733333333333334</v>
+        <v>0.44</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4579013143719026</v>
+        <v>0.3979345473367213</v>
       </c>
       <c r="G71" t="n">
-        <v>0.3738023318957465</v>
+        <v>0.451423940346316</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1000664228085696</v>
+        <v>3.387688219208574e-07</v>
       </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J71" t="n">
-        <v>10</v>
+        <v>2.63035578519602e-11</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L71" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M71" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>0.5</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.375</v>
       </c>
       <c r="R71" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="S71" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.36</v>
       </c>
       <c r="U71" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.37</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="72">
@@ -5516,54 +5586,60 @@
         <v>2010</v>
       </c>
       <c r="E72" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="F72" t="n">
-        <v>0.3800000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="G72" t="n">
-        <v>0.5174561747230945</v>
+        <v>0.4</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>10</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>15</v>
       </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
       <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N72" t="n">
-        <v>1</v>
-      </c>
-      <c r="O72" t="n">
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
         <v>0.4</v>
       </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>1</v>
-      </c>
       <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
         <v>0.4</v>
       </c>
-      <c r="S72" t="n">
+      <c r="U72" t="n">
         <v>0.3</v>
       </c>
-      <c r="T72" t="n">
+      <c r="V72" t="n">
         <v>0.2</v>
       </c>
-      <c r="U72" t="n">
+      <c r="W72" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5587,55 +5663,61 @@
         <v>2010</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5533333333333332</v>
       </c>
       <c r="F73" t="n">
-        <v>0.3986367880485527</v>
+        <v>0.4893393596950603</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3995650544502595</v>
+        <v>0.3990590730759576</v>
       </c>
       <c r="H73" t="n">
-        <v>1.231026478560298e-05</v>
+        <v>1.074627012688665e-05</v>
       </c>
       <c r="I73" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1.57490417645354e-05</v>
+      </c>
+      <c r="K73" t="n">
         <v>10</v>
       </c>
-      <c r="J73" t="n">
-        <v>14</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M73" t="n">
-        <v>0.5882352941176471</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R73" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.28</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T73" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="U73" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.26</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
     <row r="74">
@@ -5658,55 +5740,61 @@
         <v>2011</v>
       </c>
       <c r="E74" t="n">
-        <v>0.74</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7347527706734868</v>
+        <v>0.7770292207792208</v>
       </c>
       <c r="G74" t="n">
-        <v>0.211632995105019</v>
+        <v>0.2461289850499148</v>
       </c>
       <c r="H74" t="n">
-        <v>0.290971252672042</v>
+        <v>0.01939288522046403</v>
       </c>
       <c r="I74" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J74" t="n">
-        <v>8</v>
+        <v>0.4967814042781749</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L74" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M74" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W74" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T74" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="75">
@@ -5729,55 +5817,61 @@
         <v>2011</v>
       </c>
       <c r="E75" t="n">
-        <v>0.78</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7494857430151548</v>
+        <v>0.7198062558356676</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1893035912855366</v>
+        <v>0.1970096321509502</v>
       </c>
       <c r="H75" t="n">
-        <v>0.210067349666629</v>
+        <v>0.02</v>
       </c>
       <c r="I75" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.3319613225750403</v>
+      </c>
+      <c r="K75" t="n">
         <v>10</v>
       </c>
-      <c r="J75" t="n">
-        <v>8</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
       <c r="L75" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M75" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R75" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.16</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T75" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.44</v>
       </c>
       <c r="U75" t="n">
-        <v>0.05333333333333334</v>
+        <v>0.28</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="76">
@@ -5800,55 +5894,61 @@
         <v>2011</v>
       </c>
       <c r="E76" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.7</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7159967320261438</v>
+        <v>0.6151850437144554</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2143297344446182</v>
+        <v>0.262241542339325</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1742832213640213</v>
+        <v>0.001872273976914585</v>
       </c>
       <c r="I76" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J76" t="n">
-        <v>4</v>
+        <v>0.07941640168428421</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L76" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M76" t="n">
-        <v>0.7272727272727273</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V76" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0.2133333333333334</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0.2066666666666667</v>
+      <c r="W76" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="77">
@@ -5871,55 +5971,61 @@
         <v>2011</v>
       </c>
       <c r="E77" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="F77" t="n">
-        <v>0.7341033966033966</v>
+        <v>0.7781660444818339</v>
       </c>
       <c r="G77" t="n">
-        <v>0.2545645512652898</v>
+        <v>0.2175764720832342</v>
       </c>
       <c r="H77" t="n">
-        <v>0.01054320016443355</v>
+        <v>2.63035578519602e-11</v>
       </c>
       <c r="I77" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.4867559502447863</v>
+      </c>
+      <c r="K77" t="n">
         <v>10</v>
       </c>
-      <c r="J77" t="n">
-        <v>6</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
       <c r="L77" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7692307692307693</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
         <v>0.4</v>
       </c>
       <c r="R77" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="T77" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="U77" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="78">
@@ -5942,54 +6048,60 @@
         <v>2011</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5933333333333333</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5166666666666666</v>
       </c>
       <c r="G78" t="n">
-        <v>0.3226109650474491</v>
+        <v>0.3047519427326998</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
         <v>10</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>15</v>
       </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
       <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N78" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" t="n">
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
         <v>0.4</v>
       </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
       <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
         <v>0.4</v>
       </c>
-      <c r="S78" t="n">
+      <c r="U78" t="n">
         <v>0.3</v>
       </c>
-      <c r="T78" t="n">
+      <c r="V78" t="n">
         <v>0.2</v>
       </c>
-      <c r="U78" t="n">
+      <c r="W78" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -6013,55 +6125,61 @@
         <v>2011</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8217748917748917</v>
+        <v>0.7478765597147949</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3115666961237586</v>
+        <v>0.2545289773355776</v>
       </c>
       <c r="H79" t="n">
-        <v>0.001923026225120567</v>
+        <v>1.57490417645354e-05</v>
       </c>
       <c r="I79" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>0.02913357342524643</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L79" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M79" t="n">
-        <v>0.8181818181818182</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>0.75</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W79" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0.11</v>
       </c>
     </row>
     <row r="80">
@@ -6084,55 +6202,61 @@
         <v>2012</v>
       </c>
       <c r="E80" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7755602240896359</v>
+        <v>0.7404636591478696</v>
       </c>
       <c r="G80" t="n">
-        <v>0.244125149440979</v>
+        <v>0.2388005571733227</v>
       </c>
       <c r="H80" t="n">
-        <v>0.495036289551843</v>
+        <v>0.4967814042781749</v>
       </c>
       <c r="I80" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.4888298257784414</v>
+      </c>
+      <c r="K80" t="n">
+        <v>6</v>
+      </c>
+      <c r="L80" t="n">
+        <v>6</v>
+      </c>
+      <c r="M80" t="n">
+        <v>4</v>
+      </c>
+      <c r="N80" t="n">
         <v>9</v>
       </c>
-      <c r="J80" t="n">
-        <v>8</v>
-      </c>
-      <c r="K80" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" t="n">
-        <v>7</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0.9</v>
-      </c>
       <c r="O80" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="P80" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="R80" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="S80" t="n">
-        <v>0.23</v>
+        <v>0.4</v>
       </c>
       <c r="T80" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="U80" t="n">
-        <v>0.1433333333333333</v>
+        <v>0.4</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="81">
@@ -6155,55 +6279,61 @@
         <v>2012</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9187698412698412</v>
+        <v>0.8495337995337995</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1436554446475785</v>
+        <v>0.1849251178357994</v>
       </c>
       <c r="H81" t="n">
-        <v>0.4495479177068525</v>
+        <v>0.3319613225750403</v>
       </c>
       <c r="I81" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0.5094198109956143</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L81" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M81" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="O81" t="n">
-        <v>0.9</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="P81" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="R81" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.09</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T81" t="n">
-        <v>0.09333333333333335</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U81" t="n">
-        <v>0.09666666666666668</v>
+        <v>0.22</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0.07333333333333333</v>
       </c>
     </row>
     <row r="82">
@@ -6226,55 +6356,61 @@
         <v>2012</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9503174603174603</v>
+        <v>0.8217261904761904</v>
       </c>
       <c r="G82" t="n">
-        <v>0.09549164026975632</v>
+        <v>0.1618392020463943</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3973187506198883</v>
+        <v>0.07941640168428421</v>
       </c>
       <c r="I82" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0.8856098651885986</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L82" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M82" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="O82" t="n">
-        <v>0.9</v>
+        <v>0.625</v>
       </c>
       <c r="P82" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="R82" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.09</v>
+        <v>0.8</v>
       </c>
       <c r="T82" t="n">
-        <v>0.09333333333333335</v>
+        <v>0.52</v>
       </c>
       <c r="U82" t="n">
-        <v>0.09666666666666668</v>
+        <v>0.24</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0.08000000000000002</v>
       </c>
     </row>
     <row r="83">
@@ -6297,55 +6433,61 @@
         <v>2012</v>
       </c>
       <c r="E83" t="n">
-        <v>0.92</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9033974358974358</v>
+        <v>0.8086796536796537</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1253949292607568</v>
+        <v>0.2363007777025873</v>
       </c>
       <c r="H83" t="n">
-        <v>0.4856115797517387</v>
+        <v>0.4867559502447863</v>
       </c>
       <c r="I83" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J83" t="n">
-        <v>2</v>
+        <v>0.6247725562625868</v>
       </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L83" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>3</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
         <v>0.8</v>
       </c>
-      <c r="N83" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P83" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0.18</v>
-      </c>
       <c r="T83" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.52</v>
       </c>
       <c r="U83" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.24</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0.08000000000000002</v>
       </c>
     </row>
     <row r="84">
@@ -6368,55 +6510,61 @@
         <v>2012</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7298245614035088</v>
+        <v>0.6118782249742002</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1704497658054301</v>
+        <v>0.2359697574832609</v>
       </c>
       <c r="H84" t="n">
-        <v>0.5836298932384343</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.7243816254416962</v>
+      </c>
+      <c r="K84" t="n">
         <v>10</v>
       </c>
-      <c r="J84" t="n">
-        <v>9</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
       <c r="L84" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M84" t="n">
-        <v>0.6896551724137931</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="R84" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.18</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="U84" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="85">
@@ -6439,55 +6587,61 @@
         <v>2012</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9733333333333334</v>
+        <v>0.88</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9651515151515151</v>
+        <v>0.89</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1374418432978003</v>
+        <v>0.1348285493755616</v>
       </c>
       <c r="H85" t="n">
-        <v>0.01095831572786022</v>
+        <v>0.02913357342524643</v>
       </c>
       <c r="I85" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.5370374396345391</v>
+      </c>
+      <c r="K85" t="n">
         <v>10</v>
       </c>
-      <c r="J85" t="n">
-        <v>2</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
       <c r="L85" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9090909090909091</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R85" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="T85" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U85" t="n">
-        <v>0.01333333333333333</v>
+        <v>0.3</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -6523,7 +6677,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.645</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -6533,7 +6687,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.732</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="4">
@@ -6543,7 +6697,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.66</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="5">
@@ -6553,7 +6707,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.645</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="6">
@@ -6563,7 +6717,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.725</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="7">
@@ -6573,7 +6727,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.742</v>
+        <v>0.768</v>
       </c>
     </row>
   </sheetData>
@@ -6649,25 +6803,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.645</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.429</v>
       </c>
       <c r="E2" t="n">
-        <v>0.986</v>
+        <v>0.767</v>
       </c>
       <c r="F2" t="n">
-        <v>0.425</v>
+        <v>0.338</v>
       </c>
       <c r="G2" t="n">
-        <v>0.014</v>
+        <v>0.233</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.736</v>
       </c>
       <c r="I2" t="n">
-        <v>0.148</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="3">
@@ -6682,25 +6836,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.732</v>
+        <v>0.707</v>
       </c>
       <c r="D3" t="n">
-        <v>0.658</v>
+        <v>0.444</v>
       </c>
       <c r="E3" t="n">
-        <v>0.971</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.546</v>
+        <v>0.339</v>
       </c>
       <c r="G3" t="n">
-        <v>0.029</v>
+        <v>0.188</v>
       </c>
       <c r="H3" t="n">
-        <v>0.463</v>
+        <v>0.737</v>
       </c>
       <c r="I3" t="n">
-        <v>0.116</v>
+        <v>0.297</v>
       </c>
     </row>
     <row r="4">
@@ -6715,25 +6869,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.66</v>
+        <v>0.634</v>
       </c>
       <c r="D4" t="n">
-        <v>0.579</v>
+        <v>0.347</v>
       </c>
       <c r="E4" t="n">
-        <v>0.957</v>
+        <v>0.617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.461</v>
+        <v>0.28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.043</v>
+        <v>0.383</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.572</v>
       </c>
       <c r="I4" t="n">
-        <v>0.147</v>
+        <v>0.421</v>
       </c>
     </row>
     <row r="5">
@@ -6748,25 +6902,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.645</v>
+        <v>0.607</v>
       </c>
       <c r="D5" t="n">
-        <v>0.593</v>
+        <v>0.396</v>
       </c>
       <c r="E5" t="n">
-        <v>0.886</v>
+        <v>0.6</v>
       </c>
       <c r="F5" t="n">
-        <v>0.544</v>
+        <v>0.487</v>
       </c>
       <c r="G5" t="n">
-        <v>0.114</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="n">
-        <v>0.435</v>
+        <v>0.503</v>
       </c>
       <c r="I5" t="n">
-        <v>0.178</v>
+        <v>0.421</v>
       </c>
     </row>
     <row r="6">
@@ -6781,25 +6935,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.725</v>
+        <v>0.711</v>
       </c>
       <c r="D6" t="n">
-        <v>0.723</v>
+        <v>0.516</v>
       </c>
       <c r="E6" t="n">
-        <v>0.971</v>
+        <v>0.95</v>
       </c>
       <c r="F6" t="n">
-        <v>0.609</v>
+        <v>0.386</v>
       </c>
       <c r="G6" t="n">
-        <v>0.029</v>
+        <v>0.05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.532</v>
+        <v>0.612</v>
       </c>
       <c r="I6" t="n">
-        <v>0.129</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="7">
@@ -6814,25 +6968,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.742</v>
+        <v>0.768</v>
       </c>
       <c r="D7" t="n">
-        <v>0.754</v>
+        <v>0.591</v>
       </c>
       <c r="E7" t="n">
-        <v>0.971</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.656</v>
+        <v>0.438</v>
       </c>
       <c r="G7" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.421</v>
+        <v>0.571</v>
       </c>
       <c r="I7" t="n">
-        <v>0.107</v>
+        <v>0.114</v>
       </c>
     </row>
   </sheetData>
@@ -6878,7 +7032,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.645</v>
+        <v>0.5639999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -6888,7 +7042,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.732</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="4">
@@ -6898,7 +7052,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.66</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="5">
@@ -6908,7 +7062,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.645</v>
+        <v>0.607</v>
       </c>
     </row>
     <row r="6">
@@ -6918,7 +7072,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.725</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="7">
@@ -6928,7 +7082,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.742</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="8">
@@ -6943,7 +7097,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.601</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="9">
@@ -6953,7 +7107,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.713</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="10">
@@ -6963,7 +7117,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.655</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="11">
@@ -6973,7 +7127,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.654</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="12">
@@ -6983,7 +7137,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.719</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="13">
@@ -6993,7 +7147,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.613</v>
+        <v>0.599</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/results/12b/results_12b_final.xlsx
+++ b/outputs/results/12b/results_12b_final.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U85"/>
+  <dimension ref="A1:W85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -552,49 +562,55 @@
         <v>0.125</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1831758483242265</v>
+        <v>0.183902472519</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09122389628104793</v>
+        <v>0.824763481734981</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>0.09366781192562881</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2222222222222222</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2916666666666667</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08750000000000001</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05833333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02916666666666667</v>
+        <v>0.75</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -617,55 +633,61 @@
         <v>2001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.875</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0561472351020488</v>
+        <v>0.06147632457541007</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2823529411764706</v>
+        <v>0.4742857142857143</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>0.255421686746988</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0375</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="T3" t="n">
-        <v>0.025</v>
+        <v>0.92</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0125</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -694,49 +716,55 @@
         <v>0.25</v>
       </c>
       <c r="G4" t="n">
-        <v>0.121742770075798</v>
+        <v>0.09583664685487747</v>
       </c>
       <c r="H4" t="n">
-        <v>0.522675633430481</v>
+        <v>0.6034270524978638</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>0.3077666461467743</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O4" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T4" t="n">
         <v>0.88</v>
       </c>
-      <c r="S4" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.025</v>
-      </c>
       <c r="U4" t="n">
-        <v>0.0125</v>
+        <v>0.725</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9083333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -759,55 +787,61 @@
         <v>2001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.75</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1600052361472709</v>
+        <v>0.1339398060468739</v>
       </c>
       <c r="H5" t="n">
-        <v>1.300705435871653e-07</v>
+        <v>0.7354114697824092</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>0.003274069877574035</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.075</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05</v>
+        <v>0.88</v>
       </c>
       <c r="U5" t="n">
-        <v>0.025</v>
+        <v>0.725</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9083333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -839,45 +873,51 @@
         <v>0.2121169116598058</v>
       </c>
       <c r="H6" t="n">
+        <v>0.8600000000000002</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.9068219633943428</v>
       </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>19</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>0.2083333333333333</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0.8</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.0625</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.04166666666666667</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.02083333333333334</v>
       </c>
     </row>
@@ -907,49 +947,55 @@
         <v>0.25</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1102600918006365</v>
+        <v>0.09413276843019369</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009680070421468673</v>
+        <v>0.00105943799976914</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0.2570400034209828</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.25</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.125</v>
+        <v>0.04</v>
       </c>
       <c r="R7" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0375</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.025</v>
+        <v>0.04</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0125</v>
+        <v>0.3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -972,55 +1018,61 @@
         <v>2002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5833333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4300547054110133</v>
+        <v>0.4595745595414008</v>
       </c>
       <c r="H8" t="n">
-        <v>0.663812004632659</v>
+        <v>0.09366781192562881</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>0.6662365214086451</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.08</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.125</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08333333333333334</v>
+        <v>0.08</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.2875</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1916666666666667</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.09583333333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1049,49 +1101,55 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0451054236909176</v>
+        <v>0.1514733221717694</v>
       </c>
       <c r="H9" t="n">
-        <v>0.545790035283727</v>
+        <v>0.255421686746988</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7235924997680706</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.1375</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.09166666666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.04583333333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1114,55 +1172,61 @@
         <v>2002</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07728493958711624</v>
+        <v>0.1233740299940109</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6937016248703003</v>
+        <v>0.3077666461467743</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.6854806542396545</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.1375</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.09166666666666667</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.04583333333333334</v>
       </c>
     </row>
     <row r="11">
@@ -1185,55 +1249,61 @@
         <v>2002</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5833333333333333</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4616694834296106</v>
+        <v>0.5472450331373054</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7417925436734171</v>
+        <v>0.003274069877574035</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>0.6269416743022058</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.04</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08333333333333334</v>
+        <v>0.04</v>
       </c>
       <c r="U11" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -1265,46 +1335,52 @@
         <v>0.2130889204417722</v>
       </c>
       <c r="H12" t="n">
+        <v>0.9068219633943428</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.8425925925925926</v>
       </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.05</v>
+        <v>0.96</v>
       </c>
       <c r="U12" t="n">
-        <v>0.025</v>
+        <v>0.7</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="13">
@@ -1327,55 +1403,61 @@
         <v>2002</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05070693633000434</v>
+        <v>0.05130442521701176</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2072573464424945</v>
+        <v>0.2570400034209828</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>0.2671746411108706</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0625</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="T13" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.96</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02083333333333334</v>
+        <v>0.0125</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.008333333333333333</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.004166666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -1398,56 +1480,32 @@
         <v>2008</v>
       </c>
       <c r="E14" t="n">
-        <v>0.375</v>
+        <v>0.3611111111111112</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5865063598710034</v>
+        <v>0.5764741980828433</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5098728236500527</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.0003426246448590228</v>
-      </c>
-      <c r="I14" t="n">
-        <v>16</v>
-      </c>
+        <v>0.5619095848567998</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.0009144036573601353</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1469,56 +1527,32 @@
         <v>2008</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4895833333333334</v>
+        <v>0.4756944444444444</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6179359243697479</v>
+        <v>0.6146793831168831</v>
       </c>
       <c r="G15" t="n">
-        <v>0.614984</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>16</v>
-      </c>
+        <v>0.617432</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>9</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1543,53 +1577,29 @@
         <v>0.4861111111111111</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6229916121460238</v>
+        <v>0.6206570537473923</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6358895897865295</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.001354562235064805</v>
-      </c>
-      <c r="I16" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6481840014457703</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.1777777777777778</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.08888888888888889</v>
-      </c>
+        <v>0.001618588343262672</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1611,56 +1621,32 @@
         <v>2008</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3402777777777778</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5710335514294451</v>
+        <v>0.615819560430334</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5908596673905517</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4.568221092737065e-05</v>
-      </c>
-      <c r="I17" t="n">
-        <v>16</v>
-      </c>
+        <v>0.5678586499265574</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.1</v>
-      </c>
+        <v>3.917439223867385e-05</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1682,56 +1668,32 @@
         <v>2008</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.3645833333333334</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6124999999999999</v>
+        <v>0.615625</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6832927615033462</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>16</v>
-      </c>
+        <v>0.657155326324142</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>9</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1753,56 +1715,32 @@
         <v>2008</v>
       </c>
       <c r="E19" t="n">
-        <v>0.625</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7252919333082377</v>
+        <v>0.6584886920845453</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6126608297603905</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.421227358443719e-05</v>
-      </c>
-      <c r="I19" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6298669869849081</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.8205128205128205</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.6956521739130435</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.2333333333333333</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.1555555555555556</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.07777777777777778</v>
-      </c>
+        <v>6.824587925004975e-06</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1824,55 +1762,61 @@
         <v>2009</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7714425555618011</v>
+        <v>0.8020515652433222</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2205441333509373</v>
+        <v>0.1784266306008024</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4414598957633341</v>
+        <v>0.0009144036573601353</v>
       </c>
       <c r="I20" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4079539304513968</v>
+      </c>
+      <c r="K20" t="n">
         <v>16</v>
       </c>
-      <c r="J20" t="n">
-        <v>7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8205128205128205</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="R20" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2333333333333333</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="21">
@@ -1895,54 +1839,60 @@
         <v>2009</v>
       </c>
       <c r="E21" t="n">
-        <v>0.638888888888889</v>
+        <v>0.75</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7317536450645719</v>
+        <v>0.7647594136492162</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2655584566128624</v>
+        <v>0.212518449067331</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1642315720101805</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.373958245105513</v>
+      </c>
+      <c r="K21" t="n">
         <v>16</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
         <v>0.64</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
       <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
         <v>0.64</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.3</v>
       </c>
-      <c r="T21" t="n">
+      <c r="V21" t="n">
         <v>0.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1966,55 +1916,61 @@
         <v>2009</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.6319444444444444</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6546819959044223</v>
+        <v>0.7165250772068228</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3714910447597504</v>
+        <v>0.3616059124469757</v>
       </c>
       <c r="H22" t="n">
-        <v>0.02352490834891796</v>
+        <v>0.001618588343262672</v>
       </c>
       <c r="I22" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.04926801472902298</v>
+      </c>
+      <c r="K22" t="n">
         <v>16</v>
       </c>
-      <c r="J22" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8421052631578947</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.8</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="R22" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.68</v>
       </c>
       <c r="U22" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.1777777777777778</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.08888888888888889</v>
       </c>
     </row>
     <row r="23">
@@ -2037,55 +1993,61 @@
         <v>2009</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5486111111111112</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7444331219806763</v>
+        <v>0.6347398230410539</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2369984395980911</v>
+        <v>0.4721992357077128</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4310298584365538</v>
+        <v>3.917439223867385e-05</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J23" t="n">
-        <v>7</v>
+        <v>1.491416923608665e-07</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8205128205128205</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="R23" t="n">
-        <v>0.72</v>
+        <v>0.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.3416666666666667</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.3111111111111111</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.2805555555555556</v>
       </c>
     </row>
     <row r="24">
@@ -2108,54 +2070,60 @@
         <v>2009</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6458333333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7511458333333333</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="G24" t="n">
-        <v>0.313669502135048</v>
+        <v>0.5266468393741914</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>16</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>9</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
         <v>0.64</v>
       </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
       <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
         <v>0.64</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.3</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.2</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2179,54 +2147,60 @@
         <v>2009</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5625</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6462810453435454</v>
+        <v>0.6801267135642135</v>
       </c>
       <c r="G25" t="n">
-        <v>0.482497914375094</v>
+        <v>0.4067449695419502</v>
       </c>
       <c r="H25" t="n">
-        <v>6.802663028485531e-06</v>
+        <v>6.824587925004975e-06</v>
       </c>
       <c r="I25" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.001494638011571943</v>
+      </c>
+      <c r="K25" t="n">
         <v>16</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>9</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
         <v>0.64</v>
       </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
       <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
         <v>0.64</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.3</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.2</v>
       </c>
-      <c r="U25" t="n">
+      <c r="W25" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2250,55 +2224,61 @@
         <v>2010</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5933333333333333</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6009764796606901</v>
+        <v>0.4988913200326244</v>
       </c>
       <c r="G26" t="n">
-        <v>0.462651516315676</v>
+        <v>0.4347392537869853</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8357399084843402</v>
+        <v>0.4079539304513968</v>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>2009</v>
       </c>
       <c r="J26" t="n">
+        <v>0.9582302587343468</v>
+      </c>
+      <c r="K26" t="n">
         <v>10</v>
       </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6206896551724138</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.27</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2133333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1566666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="27">
@@ -2321,55 +2301,61 @@
         <v>2010</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="F27" t="n">
-        <v>0.42589508530685</v>
+        <v>0.3526321932281685</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3533496577136402</v>
+        <v>0.2794735377063164</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3205606899313307</v>
+        <v>0.373958245105513</v>
       </c>
       <c r="I27" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.1924198250728863</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>10</v>
       </c>
-      <c r="J27" t="n">
+      <c r="N27" t="n">
         <v>15</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
       <c r="O27" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="28">
@@ -2392,55 +2378,61 @@
         <v>2010</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4799596157719728</v>
+        <v>0.5864274900030049</v>
       </c>
       <c r="G28" t="n">
-        <v>0.376446545124054</v>
+        <v>0.2474653869867325</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09784837067127228</v>
+        <v>0.04926801472902298</v>
       </c>
       <c r="I28" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.2623473107814789</v>
+      </c>
+      <c r="K28" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="J28" t="n">
-        <v>13</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>2</v>
       </c>
-      <c r="M28" t="n">
-        <v>0.6060606060606061</v>
-      </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="R28" t="n">
-        <v>0.48</v>
+        <v>0.2</v>
       </c>
       <c r="S28" t="n">
-        <v>0.26</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1733333333333333</v>
+        <v>0.52</v>
       </c>
       <c r="U28" t="n">
-        <v>0.08666666666666667</v>
+        <v>0.34</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.2933333333333333</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.2466666666666667</v>
       </c>
     </row>
     <row r="29">
@@ -2463,55 +2455,61 @@
         <v>2010</v>
       </c>
       <c r="E29" t="n">
-        <v>0.62</v>
+        <v>0.5333333333333334</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6987895256916996</v>
+        <v>0.4747411412117295</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4097468804483028</v>
+        <v>0.4016432755922882</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9936514111704592</v>
+        <v>1.491416923608665e-07</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>2009</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.003049392998524357</v>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L29" t="n">
         <v>14</v>
       </c>
       <c r="M29" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R29" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.37</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T29" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="U29" t="n">
-        <v>0.4566666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="30">
@@ -2534,54 +2532,60 @@
         <v>2010</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4533333333333333</v>
+        <v>0.3533333333333333</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3768990658464343</v>
+        <v>0.3633333333333333</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4962243253487426</v>
+        <v>0.4934441366574331</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2010</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5147823734236777</v>
+        <v>0.5739809751651856</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4018680147158371</v>
+        <v>0.2692780801075882</v>
       </c>
       <c r="H31" t="n">
-        <v>0.001111154599566572</v>
+        <v>0.001494638011571943</v>
       </c>
       <c r="I31" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.01879973328019077</v>
+      </c>
+      <c r="K31" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" t="n">
         <v>10</v>
       </c>
-      <c r="J31" t="n">
-        <v>13</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>2</v>
       </c>
-      <c r="M31" t="n">
-        <v>0.6060606060606061</v>
-      </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="R31" t="n">
-        <v>0.48</v>
+        <v>0.2</v>
       </c>
       <c r="S31" t="n">
-        <v>0.26</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1733333333333333</v>
+        <v>0.52</v>
       </c>
       <c r="U31" t="n">
-        <v>0.08666666666666667</v>
+        <v>0.34</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.2933333333333333</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.2466666666666667</v>
       </c>
     </row>
     <row r="32">
@@ -2679,52 +2689,58 @@
         <v>0.7933333333333333</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8018414918414918</v>
+        <v>0.7671717171717171</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2288056604495035</v>
+        <v>0.2218198593137752</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5207668870685651</v>
+        <v>0.9582302587343468</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>0.5105825466078018</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.72</v>
+        <v>10</v>
       </c>
       <c r="N32" t="n">
+        <v>15</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W32" t="n">
         <v>0.9</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.13</v>
       </c>
     </row>
     <row r="33">
@@ -2747,55 +2763,61 @@
         <v>2011</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7308333333333333</v>
+        <v>0.7452164502164501</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2267831049810215</v>
+        <v>0.2069822268355797</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5640755320597821</v>
+        <v>0.1924198250728863</v>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>0.5380193748722448</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L33" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7272727272727273</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P33" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R33" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.22</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T33" t="n">
-        <v>0.2133333333333334</v>
+        <v>0.44</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2066666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="34">
@@ -2818,55 +2840,61 @@
         <v>2011</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8733333333333333</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8384099672257567</v>
+        <v>0.7249991185285304</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1533974409103394</v>
+        <v>0.2066832482814789</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5449708700180054</v>
+        <v>0.2623473107814789</v>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>0.4914297759532928</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>0.8</v>
       </c>
-      <c r="N34" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.18</v>
-      </c>
       <c r="T34" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.52</v>
       </c>
       <c r="U34" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.24</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.08000000000000002</v>
       </c>
     </row>
     <row r="35">
@@ -2889,55 +2917,61 @@
         <v>2011</v>
       </c>
       <c r="E35" t="n">
-        <v>0.76</v>
+        <v>0.8133333333333332</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7557448107448107</v>
+        <v>0.7939729225023343</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2243169500719387</v>
+        <v>0.1932266684188501</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8917110644340588</v>
+        <v>0.003049392998524357</v>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>2010</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>0.3973735350576428</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L35" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7368421052631579</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U35" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0.2833333333333333</v>
+      <c r="V35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="36">
@@ -2960,55 +2994,61 @@
         <v>2011</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.61</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5181818181818181</v>
+        <v>0.4905194805194805</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3262565966005779</v>
+        <v>0.2904002018767876</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5384615384615385</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>10</v>
       </c>
-      <c r="J36" t="n">
-        <v>12</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M36" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="R36" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="U36" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="37">
@@ -3031,55 +3071,61 @@
         <v>2011</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8600000000000001</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8255483405483405</v>
+        <v>0.739536297036297</v>
       </c>
       <c r="G37" t="n">
-        <v>0.175041012584231</v>
+        <v>0.1756304491221622</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5896137652913739</v>
+        <v>0.01879973328019077</v>
       </c>
       <c r="I37" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0.3947473376139597</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P37" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R37" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.11</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T37" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.44</v>
       </c>
       <c r="U37" t="n">
-        <v>0.1033333333333333</v>
+        <v>0.28</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="38">
@@ -3102,55 +3148,61 @@
         <v>2012</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8057792207792207</v>
+        <v>0.75</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1820026267412815</v>
+        <v>0.2366755861967188</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4569239996556106</v>
+        <v>0.5105825466078018</v>
       </c>
       <c r="I38" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J38" t="n">
-        <v>6</v>
+        <v>0.5228944177355064</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M38" t="n">
-        <v>0.72</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="O38" t="n">
-        <v>0.6</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="P38" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.4</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="R38" t="n">
-        <v>0.72</v>
+        <v>0.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0.19</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T38" t="n">
-        <v>0.16</v>
+        <v>0.68</v>
       </c>
       <c r="U38" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.3066666666666666</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.3033333333333333</v>
       </c>
     </row>
     <row r="39">
@@ -3173,55 +3225,61 @@
         <v>2012</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8733333333333334</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8352480852480851</v>
+        <v>0.8347527472527472</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1579551269153233</v>
+        <v>0.2128469416100012</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4118244893895048</v>
+        <v>0.5380193748722448</v>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>2011</v>
       </c>
       <c r="J39" t="n">
-        <v>5</v>
+        <v>0.714597698822553</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M39" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" t="n">
+        <v>7</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="P39" t="n">
         <v>0.8</v>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
       <c r="Q39" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="R39" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="S39" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T39" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="U39" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.3</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.2333333333333334</v>
       </c>
     </row>
     <row r="40">
@@ -3244,55 +3302,61 @@
         <v>2012</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.9066666666666667</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8566766566766565</v>
+        <v>0.8942857142857142</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1541679799556732</v>
+        <v>0.1814667135477066</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5303398370742798</v>
+        <v>0.4914297759532928</v>
       </c>
       <c r="I40" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.7904278039932251</v>
+      </c>
+      <c r="K40" t="n">
         <v>10</v>
       </c>
-      <c r="J40" t="n">
-        <v>4</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
         <v>0.7142857142857143</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="R40" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.08</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T40" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.1066666666666667</v>
+      </c>
+      <c r="W40" t="n">
         <v>0.05333333333333334</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0.02666666666666667</v>
       </c>
     </row>
     <row r="41">
@@ -3315,55 +3379,61 @@
         <v>2012</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8432792207792207</v>
+        <v>0.7967507002801121</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2891520057757666</v>
+        <v>0.1954780675216972</v>
       </c>
       <c r="H41" t="n">
-        <v>0.03280988250236398</v>
+        <v>0.3973735350576428</v>
       </c>
       <c r="I41" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.6866329242406795</v>
+      </c>
+      <c r="K41" t="n">
+        <v>9</v>
+      </c>
+      <c r="L41" t="n">
         <v>10</v>
       </c>
-      <c r="J41" t="n">
-        <v>6</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>9</v>
-      </c>
       <c r="M41" t="n">
-        <v>0.7692307692307693</v>
+        <v>1</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O41" t="n">
-        <v>0.625</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.4</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="R41" t="n">
-        <v>0.76</v>
+        <v>0.1</v>
       </c>
       <c r="S41" t="n">
-        <v>0.12</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T41" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U41" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.27</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.2133333333333333</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.1566666666666667</v>
       </c>
     </row>
     <row r="42">
@@ -3386,55 +3456,61 @@
         <v>2012</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6633333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4930515236397589</v>
+        <v>0.6253174603174604</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3505251175127529</v>
+        <v>0.2379027124882539</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8549222797927462</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J42" t="n">
-        <v>8</v>
+        <v>0.2453531598513012</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L42" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W42" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="43">
@@ -3457,55 +3533,61 @@
         <v>2012</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.9133333333333333</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8709973798131693</v>
+        <v>0.9165204678362574</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1410939947454191</v>
+        <v>0.1918600539031995</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6244520695965369</v>
+        <v>0.3947473376139597</v>
       </c>
       <c r="I43" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.8940169384874392</v>
+      </c>
+      <c r="K43" t="n">
         <v>9</v>
       </c>
-      <c r="J43" t="n">
-        <v>2</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
       <c r="L43" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
+        <v>6</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="P43" t="n">
         <v>0.9</v>
       </c>
-      <c r="O43" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R43" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.88</v>
-      </c>
       <c r="S43" t="n">
-        <v>0.11</v>
+        <v>0.6</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1033333333333333</v>
+        <v>0.25</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="44">
@@ -3534,49 +3616,55 @@
         <v>0.25</v>
       </c>
       <c r="G44" t="n">
-        <v>0.09768099359929368</v>
+        <v>0.1002298929359823</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3962694950060163</v>
+        <v>0.8769114735537481</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>0.3845959949559637</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O44" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0375</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="T44" t="n">
-        <v>0.025</v>
+        <v>0.92</v>
       </c>
       <c r="U44" t="n">
-        <v>0.0125</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="45">
@@ -3599,55 +3687,61 @@
         <v>2001</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9791666666666666</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="F45" t="n">
         <v>0.5</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02668565325738697</v>
+        <v>0.02723238810868121</v>
       </c>
       <c r="H45" t="n">
-        <v>0.270440251572327</v>
+        <v>0.13</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0.2931919868611014</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O45" t="n">
         <v>0.5</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R45" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0125</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T45" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="W45" t="n">
         <v>0.008333333333333333</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0.004166666666666667</v>
       </c>
     </row>
     <row r="46">
@@ -3676,49 +3770,55 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.008356071077287197</v>
+        <v>0.01170092914253473</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6254370808601379</v>
+        <v>0.01189725659787655</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.4962072670459747</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.08333333333333334</v>
       </c>
     </row>
     <row r="47">
@@ -3747,49 +3847,55 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="G47" t="n">
-        <v>0.06771062317752044</v>
+        <v>0.06940244339167242</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4054822920698812</v>
+        <v>0.9292010440179749</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>0.2576859717858454</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O47" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="T47" t="n">
         <v>0.92</v>
       </c>
-      <c r="S47" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0.01666666666666667</v>
-      </c>
       <c r="U47" t="n">
-        <v>0.008333333333333333</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="48">
@@ -3821,28 +3927,28 @@
         <v>0.000292205420410548</v>
       </c>
       <c r="H48" t="n">
+        <v>0.9655172413793104</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J48" t="n">
         <v>0.9145299145299146</v>
       </c>
-      <c r="I48" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" t="n">
         <v>24</v>
       </c>
-      <c r="M48" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -3857,10 +3963,16 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>0.7</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="49">
@@ -3883,55 +3995,61 @@
         <v>2001</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1195659958439588</v>
+        <v>0.03591597467672789</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0009349436569170327</v>
+        <v>0.6163617227386412</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>0.05558610661385464</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O49" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0.01666666666666667</v>
+        <v>0.96</v>
       </c>
       <c r="U49" t="n">
-        <v>0.008333333333333333</v>
+        <v>0.7</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="50">
@@ -3954,55 +4072,61 @@
         <v>2002</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4583333333333334</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="F50" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4757245492139788</v>
+        <v>0.5530036021885961</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5448897249792384</v>
+        <v>0.3845959949559637</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J50" t="n">
-        <v>13</v>
+        <v>0.5182068600325433</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O50" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.0625</v>
       </c>
       <c r="R50" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.1625</v>
+        <v>0.625</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1083333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U50" t="n">
-        <v>0.05416666666666667</v>
+        <v>0.1875</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.0625</v>
       </c>
     </row>
     <row r="51">
@@ -4025,55 +4149,61 @@
         <v>2002</v>
       </c>
       <c r="E51" t="n">
-        <v>0.625</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="G51" t="n">
-        <v>0.07180640826809585</v>
+        <v>0.07695708896603329</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1848486033749054</v>
+        <v>0.2931919868611014</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J51" t="n">
-        <v>9</v>
+        <v>0.1859185559427801</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1818181818181818</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O51" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.1125</v>
+        <v>0.25</v>
       </c>
       <c r="T51" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="U51" t="n">
-        <v>0.03750000000000001</v>
+        <v>0.7749999999999999</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.8500000000000001</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.925</v>
       </c>
     </row>
     <row r="52">
@@ -4096,55 +4226,61 @@
         <v>2002</v>
       </c>
       <c r="E52" t="n">
-        <v>0.04166666666666669</v>
+        <v>0.02083333333333331</v>
       </c>
       <c r="F52" t="n">
         <v>0.04</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1641695648431778</v>
+        <v>0.1487904191017151</v>
       </c>
       <c r="H52" t="n">
-        <v>0.05124238878488541</v>
+        <v>0.4962072670459747</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>0.01331331674009562</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M52" t="n">
-        <v>0.07692307692307693</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O52" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>0.3</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T52" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="U52" t="n">
-        <v>0.1</v>
+        <v>0.75</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="53">
@@ -4167,55 +4303,61 @@
         <v>2002</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4166666666666666</v>
+        <v>0.4583333333333334</v>
       </c>
       <c r="F53" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3957525842271876</v>
+        <v>0.4894306619356913</v>
       </c>
       <c r="H53" t="n">
-        <v>0.08635327756783583</v>
+        <v>0.2576859717858454</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J53" t="n">
-        <v>14</v>
+        <v>0.002928210656055177</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M53" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O53" t="n">
-        <v>0.06666666666666667</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.5833333333333334</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0.44</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>0.175</v>
+        <v>0.5</v>
       </c>
       <c r="T53" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="U53" t="n">
-        <v>0.05833333333333334</v>
+        <v>0.85</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.9500000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -4247,46 +4389,52 @@
         <v>0.2126371912881646</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.9145299145299146</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J54" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M54" t="n">
-        <v>0.07692307692307693</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O54" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>0.3</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="T54" t="n">
-        <v>0.2</v>
+        <v>0.76</v>
       </c>
       <c r="U54" t="n">
-        <v>0.1</v>
+        <v>0.7625</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.8416666666666667</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.9208333333333334</v>
       </c>
     </row>
     <row r="55">
@@ -4309,55 +4457,61 @@
         <v>2002</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7083333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F55" t="n">
-        <v>0.125</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1026603154118692</v>
+        <v>0.0649480057726089</v>
       </c>
       <c r="H55" t="n">
-        <v>0.03830964192992885</v>
+        <v>0.05558610661385464</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J55" t="n">
-        <v>7</v>
+        <v>0.006185720481693461</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2222222222222222</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O55" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.2916666666666667</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>0.08750000000000001</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T55" t="n">
-        <v>0.05833333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="U55" t="n">
-        <v>0.02916666666666667</v>
+        <v>0.75</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="56">
@@ -4380,56 +4534,32 @@
         <v>2008</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.4930555555555556</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7461318204821494</v>
+        <v>0.6596023405941883</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5269514292019705</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.0004238894723492777</v>
-      </c>
-      <c r="I56" t="n">
-        <v>15</v>
-      </c>
+        <v>0.5949789787154234</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
-        <v>7</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" t="n">
-        <v>2</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.7894736842105263</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0.6818181818181818</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0.2770833333333333</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0.2055555555555555</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0.1340277777777778</v>
-      </c>
+        <v>2.095342901271278e-05</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4451,56 +4581,32 @@
         <v>2008</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.5069444444444445</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6829166666666667</v>
+        <v>0.68125</v>
       </c>
       <c r="G57" t="n">
-        <v>0.624008</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>16</v>
-      </c>
+        <v>0.622352</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>9</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4522,56 +4628,32 @@
         <v>2008</v>
       </c>
       <c r="E58" t="n">
-        <v>0.5069444444444444</v>
+        <v>0.5659722222222222</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6754186246867168</v>
+        <v>0.7523041134590047</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6322618722915649</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.0005854230257682502</v>
-      </c>
-      <c r="I58" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6336380839347839</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
-        <v>9</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.001106431591324508</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4593,56 +4675,32 @@
         <v>2008</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4652777777777778</v>
+        <v>0.5208333333333333</v>
       </c>
       <c r="F59" t="n">
-        <v>0.663849557608938</v>
+        <v>0.7073819440363558</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5895138386480303</v>
-      </c>
-      <c r="H59" t="n">
-        <v>6.758511167435938e-06</v>
-      </c>
-      <c r="I59" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6094531428289832</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>9</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N59" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0.1</v>
-      </c>
+        <v>5.07818781904332e-06</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4672,48 +4730,24 @@
       <c r="G60" t="n">
         <v>0.64</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>16</v>
-      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>9</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4735,56 +4769,32 @@
         <v>2008</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4375</v>
+        <v>0.5069444444444444</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6164975491438087</v>
+        <v>0.6792103148077413</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6397414400281456</v>
-      </c>
-      <c r="H61" t="n">
-        <v>4.066190212334127e-07</v>
-      </c>
-      <c r="I61" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6389830189761644</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
-        <v>9</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0.1</v>
-      </c>
+        <v>8.103915832325728e-07</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4806,54 +4816,60 @@
         <v>2009</v>
       </c>
       <c r="E62" t="n">
-        <v>0.5902777777777778</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7317095736389214</v>
+        <v>0.6370509014012303</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4113046110193712</v>
+        <v>0.5073098927030608</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0009987528090520381</v>
+        <v>2.095342901271278e-05</v>
       </c>
       <c r="I62" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.001969129684745444</v>
+      </c>
+      <c r="K62" t="n">
         <v>16</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>9</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
       <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N62" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" t="n">
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
         <v>0.64</v>
       </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
       <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
         <v>0.64</v>
       </c>
-      <c r="S62" t="n">
+      <c r="U62" t="n">
         <v>0.3</v>
       </c>
-      <c r="T62" t="n">
+      <c r="V62" t="n">
         <v>0.2</v>
       </c>
-      <c r="U62" t="n">
+      <c r="W62" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4877,54 +4893,60 @@
         <v>2009</v>
       </c>
       <c r="E63" t="n">
-        <v>0.5208333333333333</v>
+        <v>0.4826388888888889</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6383482142857142</v>
+        <v>0.6340295815295816</v>
       </c>
       <c r="G63" t="n">
-        <v>0.593212</v>
+        <v>0.603568</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>16</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>9</v>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
       <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N63" t="n">
-        <v>1</v>
-      </c>
-      <c r="O63" t="n">
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
         <v>0.64</v>
       </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>1</v>
-      </c>
       <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
         <v>0.64</v>
       </c>
-      <c r="S63" t="n">
+      <c r="U63" t="n">
         <v>0.3</v>
       </c>
-      <c r="T63" t="n">
+      <c r="V63" t="n">
         <v>0.2</v>
       </c>
-      <c r="U63" t="n">
+      <c r="W63" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4948,55 +4970,61 @@
         <v>2009</v>
       </c>
       <c r="E64" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.625</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6652778843057228</v>
+        <v>0.6911767766547178</v>
       </c>
       <c r="G64" t="n">
-        <v>0.6223048567771912</v>
+        <v>0.6291800141334534</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0006677798228338361</v>
+        <v>0.001106431591324508</v>
       </c>
       <c r="I64" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.002162893069908023</v>
+      </c>
+      <c r="K64" t="n">
         <v>16</v>
       </c>
-      <c r="J64" t="n">
-        <v>8</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M64" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R64" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U64" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="65">
@@ -5019,55 +5047,61 @@
         <v>2009</v>
       </c>
       <c r="E65" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="F65" t="n">
-        <v>0.6603090379935346</v>
+        <v>0.615084198889346</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5095793659237123</v>
+        <v>0.6068350545527378</v>
       </c>
       <c r="H65" t="n">
-        <v>0.000106223273925163</v>
+        <v>5.07818781904332e-06</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J65" t="n">
+        <v>3.948379697654979e-06</v>
+      </c>
+      <c r="K65" t="n">
+        <v>15</v>
+      </c>
+      <c r="L65" t="n">
         <v>9</v>
       </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
       <c r="M65" t="n">
-        <v>0.7804878048780488</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="R65" t="n">
-        <v>0.64</v>
+        <v>0.0625</v>
       </c>
       <c r="S65" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="U65" t="n">
-        <v>0.1</v>
+        <v>0.34375</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0.15625</v>
       </c>
     </row>
     <row r="66">
@@ -5102,42 +5136,48 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>16</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>9</v>
       </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
       <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
         <v>0.64</v>
       </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1</v>
-      </c>
       <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
         <v>0.64</v>
       </c>
-      <c r="S66" t="n">
+      <c r="U66" t="n">
         <v>0.3</v>
       </c>
-      <c r="T66" t="n">
+      <c r="V66" t="n">
         <v>0.2</v>
       </c>
-      <c r="U66" t="n">
+      <c r="W66" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5161,55 +5201,61 @@
         <v>2009</v>
       </c>
       <c r="E67" t="n">
-        <v>0.6041666666666667</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6997313140076298</v>
+        <v>0.6596410192358082</v>
       </c>
       <c r="G67" t="n">
-        <v>0.6367494291863808</v>
+        <v>0.63989224017819</v>
       </c>
       <c r="H67" t="n">
-        <v>1.573236477062979e-05</v>
+        <v>8.103915832325728e-07</v>
       </c>
       <c r="I67" t="n">
-        <v>14</v>
+        <v>2008</v>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>1.074627012688665e-05</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="L67" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M67" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P67" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="R67" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.2541666666666667</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0.2111111111111111</v>
+        <v>0.64</v>
       </c>
       <c r="U67" t="n">
-        <v>0.1680555555555556</v>
+        <v>0.3</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="68">
@@ -5232,55 +5278,61 @@
         <v>2010</v>
       </c>
       <c r="E68" t="n">
-        <v>0.5800000000000001</v>
+        <v>0.3866666666666667</v>
       </c>
       <c r="F68" t="n">
-        <v>0.524963768115942</v>
+        <v>0.4275751041483307</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5030900380759665</v>
+        <v>0.5236534804223293</v>
       </c>
       <c r="H68" t="n">
-        <v>0.989730736166938</v>
+        <v>0.001969129684745444</v>
       </c>
       <c r="I68" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J68" t="n">
-        <v>7</v>
+        <v>0.01939288522046403</v>
       </c>
       <c r="K68" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L68" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M68" t="n">
-        <v>0.5833333333333334</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U68" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0.3166666666666667</v>
+      <c r="V68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="69">
@@ -5303,54 +5355,60 @@
         <v>2010</v>
       </c>
       <c r="E69" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F69" t="n">
-        <v>0.5287121212121212</v>
+        <v>0.4589763177998472</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3544079999999999</v>
+        <v>0.362852</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K69" t="n">
         <v>10</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>15</v>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
       <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N69" t="n">
-        <v>1</v>
-      </c>
-      <c r="O69" t="n">
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
         <v>0.4</v>
       </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>1</v>
-      </c>
       <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
         <v>0.4</v>
       </c>
-      <c r="S69" t="n">
+      <c r="U69" t="n">
         <v>0.3</v>
       </c>
-      <c r="T69" t="n">
+      <c r="V69" t="n">
         <v>0.2</v>
       </c>
-      <c r="U69" t="n">
+      <c r="W69" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5374,55 +5432,61 @@
         <v>2010</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4633333333333333</v>
+        <v>0.4066666666666667</v>
       </c>
       <c r="F70" t="n">
-        <v>0.451623661426293</v>
+        <v>0.4251940197408969</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3740614056587219</v>
+        <v>0.3805781602859497</v>
       </c>
       <c r="H70" t="n">
-        <v>0.002154259476810694</v>
+        <v>0.002162893069908023</v>
       </c>
       <c r="I70" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.001872273976914585</v>
+      </c>
+      <c r="K70" t="n">
         <v>9</v>
       </c>
-      <c r="J70" t="n">
-        <v>12</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1</v>
-      </c>
       <c r="L70" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M70" t="n">
-        <v>0.5806451612903226</v>
+        <v>1</v>
       </c>
       <c r="N70" t="n">
+        <v>2</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="P70" t="n">
         <v>0.9</v>
       </c>
-      <c r="O70" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="P70" t="n">
+      <c r="Q70" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="R70" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.48</v>
-      </c>
       <c r="S70" t="n">
-        <v>0.31</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T70" t="n">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="U70" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.1766666666666667</v>
       </c>
     </row>
     <row r="71">
@@ -5445,55 +5509,61 @@
         <v>2010</v>
       </c>
       <c r="E71" t="n">
-        <v>0.5733333333333334</v>
+        <v>0.4266666666666667</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4579013143719026</v>
+        <v>0.4421553265575004</v>
       </c>
       <c r="G71" t="n">
-        <v>0.3738023318957465</v>
+        <v>0.4624843771469986</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1000664228085696</v>
+        <v>3.948379697654979e-06</v>
       </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J71" t="n">
-        <v>10</v>
+        <v>3.428299711644413e-12</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L71" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M71" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>0.5</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.375</v>
       </c>
       <c r="R71" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="S71" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.36</v>
       </c>
       <c r="U71" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.37</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="72">
@@ -5516,54 +5586,60 @@
         <v>2010</v>
       </c>
       <c r="E72" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="F72" t="n">
-        <v>0.3800000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="G72" t="n">
-        <v>0.5174561747230945</v>
+        <v>0.4</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>10</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>15</v>
       </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
       <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N72" t="n">
-        <v>1</v>
-      </c>
-      <c r="O72" t="n">
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
         <v>0.4</v>
       </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>1</v>
-      </c>
       <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
         <v>0.4</v>
       </c>
-      <c r="S72" t="n">
+      <c r="U72" t="n">
         <v>0.3</v>
       </c>
-      <c r="T72" t="n">
+      <c r="V72" t="n">
         <v>0.2</v>
       </c>
-      <c r="U72" t="n">
+      <c r="W72" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5587,55 +5663,61 @@
         <v>2010</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5533333333333332</v>
       </c>
       <c r="F73" t="n">
-        <v>0.3986367880485527</v>
+        <v>0.4893393596950603</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3995650544502595</v>
+        <v>0.3990590730759576</v>
       </c>
       <c r="H73" t="n">
-        <v>1.231026478560298e-05</v>
+        <v>1.074627012688665e-05</v>
       </c>
       <c r="I73" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1.57490417645354e-05</v>
+      </c>
+      <c r="K73" t="n">
         <v>10</v>
       </c>
-      <c r="J73" t="n">
-        <v>14</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M73" t="n">
-        <v>0.5882352941176471</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R73" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.28</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T73" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="U73" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.26</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
     <row r="74">
@@ -5658,55 +5740,61 @@
         <v>2011</v>
       </c>
       <c r="E74" t="n">
-        <v>0.74</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7347527706734868</v>
+        <v>0.7770292207792208</v>
       </c>
       <c r="G74" t="n">
-        <v>0.211632995105019</v>
+        <v>0.2463582595538374</v>
       </c>
       <c r="H74" t="n">
-        <v>0.290971252672042</v>
+        <v>0.01939288522046403</v>
       </c>
       <c r="I74" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J74" t="n">
-        <v>8</v>
+        <v>0.4969735277210531</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L74" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M74" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W74" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T74" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="75">
@@ -5729,55 +5817,61 @@
         <v>2011</v>
       </c>
       <c r="E75" t="n">
-        <v>0.78</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7494857430151548</v>
+        <v>0.7360714285714286</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1893035912855366</v>
+        <v>0.1964786027606322</v>
       </c>
       <c r="H75" t="n">
-        <v>0.210067349666629</v>
+        <v>0.02</v>
       </c>
       <c r="I75" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.4087096210523973</v>
+      </c>
+      <c r="K75" t="n">
         <v>10</v>
       </c>
-      <c r="J75" t="n">
-        <v>8</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
       <c r="L75" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M75" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R75" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.16</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U75" t="n">
-        <v>0.05333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="76">
@@ -5800,55 +5894,61 @@
         <v>2011</v>
       </c>
       <c r="E76" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.7</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7159967320261438</v>
+        <v>0.6169126246990024</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2143297344446182</v>
+        <v>0.2500535845756531</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1742832213640213</v>
+        <v>0.001872273976914585</v>
       </c>
       <c r="I76" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J76" t="n">
-        <v>4</v>
+        <v>0.1043751165270805</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L76" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M76" t="n">
-        <v>0.7272727272727273</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P76" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R76" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0.22</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T76" t="n">
-        <v>0.2133333333333334</v>
+        <v>0.44</v>
       </c>
       <c r="U76" t="n">
-        <v>0.2066666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="77">
@@ -5874,52 +5974,58 @@
         <v>0.8066666666666666</v>
       </c>
       <c r="F77" t="n">
-        <v>0.7341033966033966</v>
+        <v>0.7965384615384615</v>
       </c>
       <c r="G77" t="n">
-        <v>0.2545645512652898</v>
+        <v>0.1898875827115368</v>
       </c>
       <c r="H77" t="n">
-        <v>0.01054320016443355</v>
+        <v>3.428299711644413e-12</v>
       </c>
       <c r="I77" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.3030001514644355</v>
+      </c>
+      <c r="K77" t="n">
         <v>10</v>
       </c>
-      <c r="J77" t="n">
-        <v>6</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
       <c r="L77" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7692307692307693</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
         <v>0.4</v>
       </c>
       <c r="R77" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="T77" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="U77" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="78">
@@ -5942,54 +6048,60 @@
         <v>2011</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5933333333333333</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5166666666666666</v>
       </c>
       <c r="G78" t="n">
-        <v>0.3226109650474491</v>
+        <v>0.3043684491626514</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
         <v>10</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>15</v>
       </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
       <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N78" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" t="n">
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
         <v>0.4</v>
       </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
       <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
         <v>0.4</v>
       </c>
-      <c r="S78" t="n">
+      <c r="U78" t="n">
         <v>0.3</v>
       </c>
-      <c r="T78" t="n">
+      <c r="V78" t="n">
         <v>0.2</v>
       </c>
-      <c r="U78" t="n">
+      <c r="W78" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -6013,55 +6125,61 @@
         <v>2011</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8217748917748917</v>
+        <v>0.6561706349206349</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3115666961237586</v>
+        <v>0.2918638367779595</v>
       </c>
       <c r="H79" t="n">
-        <v>0.001923026225120567</v>
+        <v>1.57490417645354e-05</v>
       </c>
       <c r="I79" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>0.03347200218814297</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L79" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M79" t="n">
-        <v>0.8181818181818182</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>0.75</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W79" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0.11</v>
       </c>
     </row>
     <row r="80">
@@ -6084,55 +6202,61 @@
         <v>2012</v>
       </c>
       <c r="E80" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7755602240896359</v>
+        <v>0.7404636591478696</v>
       </c>
       <c r="G80" t="n">
-        <v>0.244125149440979</v>
+        <v>0.2384886068411766</v>
       </c>
       <c r="H80" t="n">
-        <v>0.495036289551843</v>
+        <v>0.4969735277210531</v>
       </c>
       <c r="I80" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.4884933677647814</v>
+      </c>
+      <c r="K80" t="n">
+        <v>6</v>
+      </c>
+      <c r="L80" t="n">
+        <v>6</v>
+      </c>
+      <c r="M80" t="n">
+        <v>4</v>
+      </c>
+      <c r="N80" t="n">
         <v>9</v>
       </c>
-      <c r="J80" t="n">
-        <v>8</v>
-      </c>
-      <c r="K80" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" t="n">
-        <v>7</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0.9</v>
-      </c>
       <c r="O80" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="P80" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="R80" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="S80" t="n">
-        <v>0.23</v>
+        <v>0.4</v>
       </c>
       <c r="T80" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="U80" t="n">
-        <v>0.1433333333333333</v>
+        <v>0.4</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="81">
@@ -6155,55 +6279,61 @@
         <v>2012</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.8866666666666667</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9187698412698412</v>
+        <v>0.9035742035742036</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1436554446475785</v>
+        <v>0.164351825662321</v>
       </c>
       <c r="H81" t="n">
-        <v>0.4495479177068525</v>
+        <v>0.4087096210523973</v>
       </c>
       <c r="I81" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.543597530793051</v>
+      </c>
+      <c r="K81" t="n">
         <v>9</v>
       </c>
-      <c r="J81" t="n">
-        <v>1</v>
-      </c>
-      <c r="K81" t="n">
-        <v>1</v>
-      </c>
       <c r="L81" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M81" t="n">
+        <v>1</v>
+      </c>
+      <c r="N81" t="n">
+        <v>7</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P81" t="n">
         <v>0.9</v>
       </c>
-      <c r="N81" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P81" t="n">
+      <c r="Q81" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="R81" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0.92</v>
-      </c>
       <c r="S81" t="n">
-        <v>0.09</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T81" t="n">
-        <v>0.09333333333333335</v>
+        <v>0.64</v>
       </c>
       <c r="U81" t="n">
-        <v>0.09666666666666668</v>
+        <v>0.23</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="82">
@@ -6226,55 +6356,61 @@
         <v>2012</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9503174603174603</v>
+        <v>0.8263519761971774</v>
       </c>
       <c r="G82" t="n">
-        <v>0.09549164026975632</v>
+        <v>0.1702698320150375</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3973187506198883</v>
+        <v>0.1043751165270805</v>
       </c>
       <c r="I82" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0.8295921683311462</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L82" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M82" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="O82" t="n">
-        <v>0.9</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="P82" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="R82" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.09</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T82" t="n">
-        <v>0.09333333333333335</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U82" t="n">
-        <v>0.09666666666666668</v>
+        <v>0.22</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0.07333333333333333</v>
       </c>
     </row>
     <row r="83">
@@ -6297,55 +6433,61 @@
         <v>2012</v>
       </c>
       <c r="E83" t="n">
-        <v>0.92</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9033974358974358</v>
+        <v>0.8060279997779998</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1253949292607568</v>
+        <v>0.1801088023321449</v>
       </c>
       <c r="H83" t="n">
-        <v>0.4856115797517387</v>
+        <v>0.3030001514644355</v>
       </c>
       <c r="I83" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J83" t="n">
-        <v>2</v>
+        <v>0.4302635583750712</v>
       </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L83" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M83" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="O83" t="n">
-        <v>0.8</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="P83" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="R83" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0.18</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T83" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U83" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.22</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0.07333333333333333</v>
       </c>
     </row>
     <row r="84">
@@ -6368,55 +6510,61 @@
         <v>2012</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.7433333333333334</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7298245614035088</v>
+        <v>0.6128070175438597</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1704497658054301</v>
+        <v>0.2359697574832609</v>
       </c>
       <c r="H84" t="n">
-        <v>0.5836298932384343</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.7243816254416963</v>
+      </c>
+      <c r="K84" t="n">
         <v>10</v>
       </c>
-      <c r="J84" t="n">
-        <v>9</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
       <c r="L84" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M84" t="n">
-        <v>0.6896551724137931</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="R84" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.18</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="U84" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="85">
@@ -6439,55 +6587,61 @@
         <v>2012</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9733333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9651515151515151</v>
+        <v>0.8854545454545454</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1374418432978003</v>
+        <v>0.1334178195366149</v>
       </c>
       <c r="H85" t="n">
-        <v>0.01095831572786022</v>
+        <v>0.03347200218814297</v>
       </c>
       <c r="I85" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.5402199142929789</v>
+      </c>
+      <c r="K85" t="n">
         <v>10</v>
-      </c>
-      <c r="J85" t="n">
-        <v>2</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>13</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9090909090909091</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O85" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R85" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.04</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T85" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="U85" t="n">
-        <v>0.01333333333333333</v>
+        <v>0.26</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -6523,7 +6677,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.645</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="3">
@@ -6533,7 +6687,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.732</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="4">
@@ -6543,7 +6697,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.66</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="5">
@@ -6553,7 +6707,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.645</v>
+        <v>0.587</v>
       </c>
     </row>
     <row r="6">
@@ -6563,7 +6717,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.725</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="7">
@@ -6573,7 +6727,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.742</v>
+        <v>0.752</v>
       </c>
     </row>
   </sheetData>
@@ -6649,25 +6803,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.645</v>
+        <v>0.61</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.463</v>
       </c>
       <c r="E2" t="n">
-        <v>0.986</v>
+        <v>0.833</v>
       </c>
       <c r="F2" t="n">
-        <v>0.425</v>
+        <v>0.334</v>
       </c>
       <c r="G2" t="n">
-        <v>0.014</v>
+        <v>0.167</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.701</v>
       </c>
       <c r="I2" t="n">
-        <v>0.148</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="3">
@@ -6682,25 +6836,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.732</v>
+        <v>0.759</v>
       </c>
       <c r="D3" t="n">
-        <v>0.658</v>
+        <v>0.554</v>
       </c>
       <c r="E3" t="n">
-        <v>0.971</v>
+        <v>0.95</v>
       </c>
       <c r="F3" t="n">
-        <v>0.546</v>
+        <v>0.424</v>
       </c>
       <c r="G3" t="n">
-        <v>0.029</v>
+        <v>0.05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.463</v>
+        <v>0.707</v>
       </c>
       <c r="I3" t="n">
-        <v>0.116</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="4">
@@ -6715,25 +6869,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.66</v>
+        <v>0.635</v>
       </c>
       <c r="D4" t="n">
-        <v>0.579</v>
+        <v>0.348</v>
       </c>
       <c r="E4" t="n">
-        <v>0.957</v>
+        <v>0.617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.461</v>
+        <v>0.28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.043</v>
+        <v>0.383</v>
       </c>
       <c r="H4" t="n">
         <v>0.5649999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.147</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="5">
@@ -6748,25 +6902,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.645</v>
+        <v>0.587</v>
       </c>
       <c r="D5" t="n">
-        <v>0.593</v>
+        <v>0.431</v>
       </c>
       <c r="E5" t="n">
-        <v>0.886</v>
+        <v>0.775</v>
       </c>
       <c r="F5" t="n">
-        <v>0.544</v>
+        <v>0.339</v>
       </c>
       <c r="G5" t="n">
-        <v>0.114</v>
+        <v>0.225</v>
       </c>
       <c r="H5" t="n">
-        <v>0.435</v>
+        <v>0.706</v>
       </c>
       <c r="I5" t="n">
-        <v>0.178</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="6">
@@ -6781,25 +6935,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.725</v>
+        <v>0.723</v>
       </c>
       <c r="D6" t="n">
-        <v>0.723</v>
+        <v>0.356</v>
       </c>
       <c r="E6" t="n">
-        <v>0.971</v>
+        <v>0.633</v>
       </c>
       <c r="F6" t="n">
-        <v>0.609</v>
+        <v>0.273</v>
       </c>
       <c r="G6" t="n">
-        <v>0.029</v>
+        <v>0.367</v>
       </c>
       <c r="H6" t="n">
-        <v>0.532</v>
+        <v>0.494</v>
       </c>
       <c r="I6" t="n">
-        <v>0.129</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="7">
@@ -6814,25 +6968,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.742</v>
+        <v>0.752</v>
       </c>
       <c r="D7" t="n">
-        <v>0.754</v>
+        <v>0.477</v>
       </c>
       <c r="E7" t="n">
-        <v>0.971</v>
+        <v>0.8</v>
       </c>
       <c r="F7" t="n">
-        <v>0.656</v>
+        <v>0.367</v>
       </c>
       <c r="G7" t="n">
-        <v>0.029</v>
+        <v>0.2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.421</v>
+        <v>0.572</v>
       </c>
       <c r="I7" t="n">
-        <v>0.107</v>
+        <v>0.274</v>
       </c>
     </row>
   </sheetData>
@@ -6878,7 +7032,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.645</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="3">
@@ -6888,7 +7042,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.732</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="4">
@@ -6898,7 +7052,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.66</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="5">
@@ -6908,7 +7062,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.645</v>
+        <v>0.587</v>
       </c>
     </row>
     <row r="6">
@@ -6918,7 +7072,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.725</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="7">
@@ -6928,7 +7082,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.742</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="8">
@@ -6943,7 +7097,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.601</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="9">
@@ -6953,7 +7107,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.713</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="10">
@@ -6963,7 +7117,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.655</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="11">
@@ -6973,7 +7127,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.654</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="12">
@@ -6983,7 +7137,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.719</v>
+        <v>0.6830000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -6993,7 +7147,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.613</v>
+        <v>0.591</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/results/12b/results_12b_final.xlsx
+++ b/outputs/results/12b/results_12b_final.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U85"/>
+  <dimension ref="A1:W85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -546,55 +556,61 @@
         <v>2001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7083333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="F2" t="n">
-        <v>0.125</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1831758483242265</v>
+        <v>0.1744590487261879</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09122389628104793</v>
+        <v>0.8155395937313684</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>0.1547823758982739</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2222222222222222</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2916666666666667</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08750000000000001</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05833333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02916666666666667</v>
+        <v>0.75</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -623,49 +639,55 @@
         <v>0.25</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0561472351020488</v>
+        <v>0.06752772929538177</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2823529411764706</v>
+        <v>0.4163589056123644</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>0.3749390092717082</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T3" t="n">
         <v>0.88</v>
       </c>
-      <c r="S3" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.025</v>
-      </c>
       <c r="U3" t="n">
-        <v>0.0125</v>
+        <v>0.725</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9083333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -694,48 +716,54 @@
         <v>0.25</v>
       </c>
       <c r="G4" t="n">
-        <v>0.121742770075798</v>
+        <v>0.09270568937063217</v>
       </c>
       <c r="H4" t="n">
-        <v>0.522675633430481</v>
+        <v>0.4557756781578064</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J4" t="n">
+        <v>0.4937949180603027</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>21</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.4</v>
       </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0.25</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>0.125</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.88</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.0375</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>0.025</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.0125</v>
       </c>
     </row>
@@ -765,49 +793,55 @@
         <v>0.1428571428571428</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1600052361472709</v>
+        <v>0.1598110179055897</v>
       </c>
       <c r="H5" t="n">
-        <v>1.300705435871653e-07</v>
+        <v>0.7425996941658441</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>9.721343959994393e-06</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.075</v>
+        <v>0.125</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05</v>
+        <v>0.84</v>
       </c>
       <c r="U5" t="n">
-        <v>0.025</v>
+        <v>0.7374999999999999</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.8250000000000001</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9125</v>
       </c>
     </row>
     <row r="6">
@@ -830,55 +864,61 @@
         <v>2001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8958333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2121169116598058</v>
+        <v>0.131308506841166</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9068219633943428</v>
+        <v>0.5276073619631904</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2857142857142857</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0625</v>
+        <v>0.125</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.84</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02083333333333334</v>
+        <v>0.7374999999999999</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.8250000000000001</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9125</v>
       </c>
     </row>
     <row r="7">
@@ -907,49 +947,55 @@
         <v>0.25</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1102600918006365</v>
+        <v>0.08963486939941545</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009680070421468673</v>
+        <v>0.372483973655639</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0.1960681366386046</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="T7" t="n">
         <v>0.88</v>
       </c>
-      <c r="S7" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.025</v>
-      </c>
       <c r="U7" t="n">
-        <v>0.0125</v>
+        <v>0.725</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.9083333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -972,55 +1018,61 @@
         <v>2002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5833333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4300547054110133</v>
+        <v>0.4878508671032211</v>
       </c>
       <c r="H8" t="n">
-        <v>0.663812004632659</v>
+        <v>0.1547823758982739</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>0.722333532112304</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.125</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08333333333333334</v>
+        <v>0.12</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.275</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.09166666666666667</v>
       </c>
     </row>
     <row r="9">
@@ -1049,49 +1101,55 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0451054236909176</v>
+        <v>0.1578978541124817</v>
       </c>
       <c r="H9" t="n">
-        <v>0.545790035283727</v>
+        <v>0.3749390092717082</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.6595054534218241</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.1375</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.09166666666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.04583333333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1120,49 +1178,55 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07728493958711624</v>
+        <v>0.1278676092624664</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6937016248703003</v>
+        <v>0.4937949180603027</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.6003971099853516</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.075</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="11">
@@ -1191,49 +1255,55 @@
         <v>0.09090909090909091</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4616694834296106</v>
+        <v>0.3905151043561459</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7417925436734171</v>
+        <v>9.721343959994393e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>0.6301980747531493</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.04</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08333333333333334</v>
+        <v>0.04</v>
       </c>
       <c r="U11" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -1265,46 +1335,52 @@
         <v>0.2130889204417722</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J12" t="n">
         <v>0.8425925925925926</v>
       </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.25</v>
+        <v>0.04</v>
       </c>
       <c r="R12" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.075</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="U12" t="n">
-        <v>0.025</v>
+        <v>0.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="13">
@@ -1327,55 +1403,61 @@
         <v>2002</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05070693633000434</v>
+        <v>0.09839355053774224</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2072573464424945</v>
+        <v>0.1960681366386046</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>0.4645777302077684</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0625</v>
+        <v>0.875</v>
       </c>
       <c r="T13" t="n">
-        <v>0.04166666666666667</v>
+        <v>0.16</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02083333333333334</v>
+        <v>0.2625</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.08750000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1398,56 +1480,32 @@
         <v>2008</v>
       </c>
       <c r="E14" t="n">
-        <v>0.375</v>
+        <v>0.3611111111111112</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5865063598710034</v>
+        <v>0.5764741980828433</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5098728236500527</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.0003426246448590228</v>
-      </c>
-      <c r="I14" t="n">
-        <v>16</v>
-      </c>
+        <v>0.5619095848567998</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.0009144036573601353</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1469,56 +1527,32 @@
         <v>2008</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4895833333333334</v>
+        <v>0.46875</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6179359243697479</v>
+        <v>0.5931410256410257</v>
       </c>
       <c r="G15" t="n">
-        <v>0.614984</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6171759999999999</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>9</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1543,53 +1577,29 @@
         <v>0.4861111111111111</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6229916121460238</v>
+        <v>0.6206570537473923</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6358895897865295</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.001354562235064805</v>
-      </c>
-      <c r="I16" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6481840014457703</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.1777777777777778</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.08888888888888889</v>
-      </c>
+        <v>0.001618588343262672</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1611,56 +1621,32 @@
         <v>2008</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3402777777777778</v>
+        <v>0.3263888888888889</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5710335514294451</v>
+        <v>0.6024273057551847</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5908596673905517</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4.568221092737065e-05</v>
-      </c>
-      <c r="I17" t="n">
-        <v>16</v>
-      </c>
+        <v>0.5800951792431204</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.1</v>
-      </c>
+        <v>2.184374888593759e-06</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1682,56 +1668,32 @@
         <v>2008</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3055555555555556</v>
+        <v>0.3645833333333334</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6124999999999999</v>
+        <v>0.615625</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6832927615033462</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>16</v>
-      </c>
+        <v>0.657155326324142</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>9</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1753,56 +1715,32 @@
         <v>2008</v>
       </c>
       <c r="E19" t="n">
-        <v>0.625</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7252919333082377</v>
+        <v>0.6584886920845453</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6126608297603905</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.421227358443719e-05</v>
-      </c>
-      <c r="I19" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6298669869849081</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.8205128205128205</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.6956521739130435</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.2333333333333333</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.1555555555555556</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.07777777777777778</v>
-      </c>
+        <v>6.824587925004975e-06</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1824,55 +1762,61 @@
         <v>2009</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6805555555555556</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7714425555618011</v>
+        <v>0.8020515652433222</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2205441333509373</v>
+        <v>0.1786424005525714</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4414598957633341</v>
+        <v>0.0009144036573601353</v>
       </c>
       <c r="I20" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4080922612677221</v>
+      </c>
+      <c r="K20" t="n">
         <v>16</v>
       </c>
-      <c r="J20" t="n">
-        <v>7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8205128205128205</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="R20" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2333333333333333</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="21">
@@ -1895,54 +1839,60 @@
         <v>2009</v>
       </c>
       <c r="E21" t="n">
-        <v>0.638888888888889</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7317536450645719</v>
+        <v>0.752265340868282</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2655584566128624</v>
+        <v>0.3983915445608542</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1642315720101805</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.07457637267229507</v>
+      </c>
+      <c r="K21" t="n">
         <v>16</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
         <v>0.64</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
       <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
         <v>0.64</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.3</v>
       </c>
-      <c r="T21" t="n">
+      <c r="V21" t="n">
         <v>0.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1966,55 +1916,61 @@
         <v>2009</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5694444444444444</v>
+        <v>0.6041666666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6546819959044223</v>
+        <v>0.6954883368050937</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3714910447597504</v>
+        <v>0.394990086555481</v>
       </c>
       <c r="H22" t="n">
-        <v>0.02352490834891796</v>
+        <v>0.001618588343262672</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J22" t="n">
-        <v>6</v>
+        <v>0.01044152770191431</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8421052631578947</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="R22" t="n">
-        <v>0.76</v>
+        <v>0.0625</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.64</v>
       </c>
       <c r="U22" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.3104166666666667</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.2277777777777778</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.1451388888888889</v>
       </c>
     </row>
     <row r="23">
@@ -2037,55 +1993,61 @@
         <v>2009</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5902777777777778</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7444331219806763</v>
+        <v>0.6794341333331271</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2369984395980911</v>
+        <v>0.246500335584939</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4310298584365538</v>
+        <v>2.184374888593759e-06</v>
       </c>
       <c r="I23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.3006573748803016</v>
+      </c>
+      <c r="K23" t="n">
         <v>16</v>
       </c>
-      <c r="J23" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8205128205128205</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="R23" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2333333333333333</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
@@ -2108,54 +2070,60 @@
         <v>2009</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6458333333333333</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7511458333333333</v>
+        <v>0.7576785714285714</v>
       </c>
       <c r="G24" t="n">
-        <v>0.313669502135048</v>
+        <v>0.4196223700017738</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>16</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>9</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
         <v>0.64</v>
       </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
       <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
         <v>0.64</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.3</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.2</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2179,55 +2147,61 @@
         <v>2009</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6462810453435454</v>
+        <v>0.6510299081246971</v>
       </c>
       <c r="G25" t="n">
-        <v>0.482497914375094</v>
+        <v>0.5763391265026868</v>
       </c>
       <c r="H25" t="n">
-        <v>6.802663028485531e-06</v>
+        <v>6.824587925004975e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J25" t="n">
-        <v>9</v>
+        <v>0.0004500148532554012</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7804878048780488</v>
+        <v>3</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
+        <v>0.7428571428571429</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T25" t="n">
         <v>0.64</v>
       </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.2</v>
-      </c>
       <c r="U25" t="n">
-        <v>0.1</v>
+        <v>0.3312499999999999</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.2833333333333333</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.2354166666666667</v>
       </c>
     </row>
     <row r="26">
@@ -2250,55 +2224,61 @@
         <v>2010</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5933333333333333</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6009764796606901</v>
+        <v>0.5070797258297258</v>
       </c>
       <c r="G26" t="n">
-        <v>0.462651516315676</v>
+        <v>0.4628346016439969</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8357399084843402</v>
+        <v>0.4080922612677221</v>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>2009</v>
       </c>
       <c r="J26" t="n">
+        <v>0.9750801608040135</v>
+      </c>
+      <c r="K26" t="n">
         <v>10</v>
       </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6206896551724138</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.27</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2133333333333333</v>
+        <v>0.44</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1566666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="27">
@@ -2321,54 +2301,60 @@
         <v>2010</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.46</v>
       </c>
       <c r="F27" t="n">
-        <v>0.42589508530685</v>
+        <v>0.3746607610655598</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3533496577136402</v>
+        <v>0.2511882758334823</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3205606899313307</v>
+        <v>0.07457637267229507</v>
       </c>
       <c r="I27" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.2380004550854753</v>
+      </c>
+      <c r="K27" t="n">
         <v>10</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>15</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
         <v>0.4</v>
       </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
       <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
         <v>0.4</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>0.3</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>0.2</v>
       </c>
-      <c r="U27" t="n">
+      <c r="W27" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2392,55 +2378,61 @@
         <v>2010</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4799596157719728</v>
+        <v>0.5868831168831168</v>
       </c>
       <c r="G28" t="n">
-        <v>0.376446545124054</v>
+        <v>0.2109296470880508</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09784837067127228</v>
+        <v>0.01044152770191431</v>
       </c>
       <c r="I28" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.4148781001567841</v>
+      </c>
+      <c r="K28" t="n">
         <v>10</v>
       </c>
-      <c r="J28" t="n">
-        <v>13</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6060606060606061</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1733333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U28" t="n">
-        <v>0.08666666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="29">
@@ -2463,55 +2455,61 @@
         <v>2010</v>
       </c>
       <c r="E29" t="n">
-        <v>0.62</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6987895256916996</v>
+        <v>0.4762719298245614</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4097468804483028</v>
+        <v>0.3476468724025764</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9936514111704592</v>
+        <v>0.3006573748803016</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>2009</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.7856655915715843</v>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M29" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.37</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U29" t="n">
-        <v>0.4566666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="30">
@@ -2534,54 +2532,60 @@
         <v>2010</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4533333333333333</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3768990658464343</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4962243253487426</v>
+        <v>0.2827410086533261</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5625000000000001</v>
+      </c>
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2010</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6266666666666667</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5147823734236777</v>
+        <v>0.4998778998778999</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4018680147158371</v>
+        <v>0.3511263807040516</v>
       </c>
       <c r="H31" t="n">
-        <v>0.001111154599566572</v>
+        <v>0.0004500148532554012</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J31" t="n">
-        <v>13</v>
+        <v>0.0002443372126331038</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L31" t="n">
+        <v>8</v>
+      </c>
+      <c r="M31" t="n">
         <v>2</v>
       </c>
-      <c r="M31" t="n">
-        <v>0.6060606060606061</v>
-      </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O31" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0.48</v>
+        <v>0.2</v>
       </c>
       <c r="S31" t="n">
-        <v>0.26</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1733333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="U31" t="n">
-        <v>0.08666666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.2333333333333334</v>
       </c>
     </row>
     <row r="32">
@@ -2679,52 +2689,58 @@
         <v>0.7933333333333333</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8018414918414918</v>
+        <v>0.7671717171717171</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2288056604495035</v>
+        <v>0.2195188895442178</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5207668870685651</v>
+        <v>0.9750801608040135</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>0.5111617722220765</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.72</v>
+        <v>10</v>
       </c>
       <c r="N32" t="n">
+        <v>15</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W32" t="n">
         <v>0.9</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.13</v>
       </c>
     </row>
     <row r="33">
@@ -2747,55 +2763,61 @@
         <v>2011</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7308333333333333</v>
+        <v>0.6962212349054454</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2267831049810215</v>
+        <v>0.2151514604106469</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5640755320597821</v>
+        <v>0.2380004550854753</v>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>0.5382634391560808</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M33" t="n">
-        <v>0.7272727272727273</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>0.8</v>
       </c>
-      <c r="O33" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0.22</v>
-      </c>
       <c r="T33" t="n">
-        <v>0.2133333333333334</v>
+        <v>0.52</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2066666666666667</v>
+        <v>0.24</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.08000000000000002</v>
       </c>
     </row>
     <row r="34">
@@ -2818,55 +2840,61 @@
         <v>2011</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8733333333333333</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8384099672257567</v>
+        <v>0.7517456073338425</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1533974409103394</v>
+        <v>0.1691862940788269</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5449708700180054</v>
+        <v>0.4148781001567841</v>
       </c>
       <c r="I34" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.4115010499954224</v>
+      </c>
+      <c r="K34" t="n">
         <v>8</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
+        <v>5</v>
+      </c>
+      <c r="M34" t="n">
         <v>2</v>
       </c>
-      <c r="K34" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" t="n">
-        <v>13</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="P34" t="n">
         <v>0.8</v>
       </c>
-      <c r="N34" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="R34" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.84</v>
-      </c>
       <c r="S34" t="n">
-        <v>0.18</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T34" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.72</v>
       </c>
       <c r="U34" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.24</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.2133333333333333</v>
       </c>
     </row>
     <row r="35">
@@ -2889,55 +2917,61 @@
         <v>2011</v>
       </c>
       <c r="E35" t="n">
-        <v>0.76</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7557448107448107</v>
+        <v>0.7723316879199232</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2243169500719387</v>
+        <v>0.2022117841037502</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8917110644340588</v>
+        <v>0.7856655915715843</v>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>2010</v>
       </c>
       <c r="J35" t="n">
+        <v>0.475761242470103</v>
+      </c>
+      <c r="K35" t="n">
         <v>2</v>
       </c>
-      <c r="K35" t="n">
-        <v>3</v>
-      </c>
       <c r="L35" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7368421052631579</v>
+        <v>8</v>
       </c>
       <c r="N35" t="n">
-        <v>0.7</v>
+        <v>15</v>
       </c>
       <c r="O35" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="P35" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1333333333333333</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0.8</v>
       </c>
       <c r="S35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.68</v>
       </c>
       <c r="U35" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.5599999999999999</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.6400000000000001</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.7200000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -2960,55 +2994,61 @@
         <v>2011</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.61</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5181818181818181</v>
+        <v>0.4905194805194805</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3262565966005779</v>
+        <v>0.2904002018767876</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="I36" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>6</v>
+      </c>
+      <c r="L36" t="n">
+        <v>5</v>
+      </c>
+      <c r="M36" t="n">
+        <v>4</v>
+      </c>
+      <c r="N36" t="n">
         <v>10</v>
       </c>
-      <c r="J36" t="n">
-        <v>12</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>3</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
       <c r="O36" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.8</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="R36" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="S36" t="n">
-        <v>0.24</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T36" t="n">
-        <v>0.16</v>
+        <v>0.64</v>
       </c>
       <c r="U36" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3799999999999999</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.3866666666666667</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.3933333333333334</v>
       </c>
     </row>
     <row r="37">
@@ -3031,55 +3071,61 @@
         <v>2011</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8600000000000001</v>
+        <v>0.8466666666666667</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8255483405483405</v>
+        <v>0.7757815713698066</v>
       </c>
       <c r="G37" t="n">
-        <v>0.175041012584231</v>
+        <v>0.1660159828001671</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5896137652913739</v>
+        <v>0.0002443372126331038</v>
       </c>
       <c r="I37" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0.4584611042031131</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L37" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M37" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W37" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.1066666666666667</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.1033333333333333</v>
       </c>
     </row>
     <row r="38">
@@ -3102,55 +3148,61 @@
         <v>2012</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8057792207792207</v>
+        <v>0.75</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1820026267412815</v>
+        <v>0.2387060211144147</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4569239996556106</v>
+        <v>0.5111617722220765</v>
       </c>
       <c r="I38" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J38" t="n">
+        <v>0.5190238143337146</v>
+      </c>
+      <c r="K38" t="n">
         <v>6</v>
       </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
       <c r="L38" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
+        <v>4</v>
+      </c>
+      <c r="N38" t="n">
+        <v>12</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T38" t="n">
         <v>0.72</v>
       </c>
-      <c r="N38" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0.16</v>
-      </c>
       <c r="U38" t="n">
-        <v>0.13</v>
+        <v>0.34</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.3600000000000001</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.3800000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -3173,55 +3225,61 @@
         <v>2012</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8733333333333334</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8352480852480851</v>
+        <v>0.8294887955182072</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1579551269153233</v>
+        <v>0.2038064865465258</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4118244893895048</v>
+        <v>0.5382634391560808</v>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>2011</v>
       </c>
       <c r="J39" t="n">
-        <v>5</v>
+        <v>0.6572222263525432</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M39" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O39" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="Q39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="V39" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="R39" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0.09999999999999999</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0.03333333333333333</v>
+      <c r="W39" t="n">
+        <v>0.3166666666666667</v>
       </c>
     </row>
     <row r="40">
@@ -3244,55 +3302,61 @@
         <v>2012</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.9266666666666667</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8566766566766565</v>
+        <v>0.928054298642534</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1541679799556732</v>
+        <v>0.155754029750824</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5303398370742798</v>
+        <v>0.4115010499954224</v>
       </c>
       <c r="I40" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.8891028165817261</v>
+      </c>
+      <c r="K40" t="n">
         <v>10</v>
       </c>
-      <c r="J40" t="n">
-        <v>4</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="R40" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.08</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="T40" t="n">
-        <v>0.05333333333333334</v>
+        <v>0.72</v>
       </c>
       <c r="U40" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.14</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.09333333333333334</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.04666666666666667</v>
       </c>
     </row>
     <row r="41">
@@ -3315,55 +3379,61 @@
         <v>2012</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.7866666666666667</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8432792207792207</v>
+        <v>0.7741000227842333</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2891520057757666</v>
+        <v>0.2223893756159505</v>
       </c>
       <c r="H41" t="n">
-        <v>0.03280988250236398</v>
+        <v>0.475761242470103</v>
       </c>
       <c r="I41" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.5828792785778369</v>
+      </c>
+      <c r="K41" t="n">
+        <v>8</v>
+      </c>
+      <c r="L41" t="n">
         <v>10</v>
       </c>
-      <c r="J41" t="n">
-        <v>6</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>9</v>
-      </c>
       <c r="M41" t="n">
-        <v>0.7692307692307693</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O41" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.4</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="R41" t="n">
-        <v>0.76</v>
+        <v>0.2</v>
       </c>
       <c r="S41" t="n">
-        <v>0.12</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T41" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.52</v>
       </c>
       <c r="U41" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.34</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.2933333333333333</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.2466666666666667</v>
       </c>
     </row>
     <row r="42">
@@ -3386,55 +3456,61 @@
         <v>2012</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6633333333333333</v>
+        <v>0.7633333333333334</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4930515236397589</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3505251175127529</v>
+        <v>0.2353427766003119</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8549222797927462</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J42" t="n">
-        <v>8</v>
+        <v>0.7021276595744681</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L42" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W42" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="43">
@@ -3457,55 +3533,61 @@
         <v>2012</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8709973798131693</v>
+        <v>0.9344444444444445</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1410939947454191</v>
+        <v>0.1670085027850982</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6244520695965369</v>
+        <v>0.4584611042031131</v>
       </c>
       <c r="I43" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.7541433276532644</v>
+      </c>
+      <c r="K43" t="n">
         <v>9</v>
       </c>
-      <c r="J43" t="n">
-        <v>2</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
       <c r="L43" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
+        <v>7</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P43" t="n">
         <v>0.9</v>
       </c>
-      <c r="O43" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="R43" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.88</v>
-      </c>
       <c r="S43" t="n">
-        <v>0.11</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.64</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1033333333333333</v>
+        <v>0.23</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="44">
@@ -3534,49 +3616,55 @@
         <v>0.25</v>
       </c>
       <c r="G44" t="n">
-        <v>0.09768099359929368</v>
+        <v>0.0998307413358711</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3962694950060163</v>
+        <v>0.8769114735537481</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>0.4295940390947498</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O44" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>0.0375</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="T44" t="n">
-        <v>0.025</v>
+        <v>0.92</v>
       </c>
       <c r="U44" t="n">
-        <v>0.0125</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="45">
@@ -3599,55 +3687,61 @@
         <v>2001</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9791666666666666</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02668565325738697</v>
+        <v>0.02568096038181508</v>
       </c>
       <c r="H45" t="n">
-        <v>0.270440251572327</v>
+        <v>0.16</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0.2792022792022792</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O45" t="n">
         <v>0.5</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R45" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.0125</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="T45" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="W45" t="n">
         <v>0.008333333333333333</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0.004166666666666667</v>
       </c>
     </row>
     <row r="46">
@@ -3676,49 +3770,55 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.008356071077287197</v>
+        <v>0.001625449978746474</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6254370808601379</v>
+        <v>0.01189725659787655</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.8917864561080933</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
         <v>24</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
@@ -3747,49 +3847,55 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="G47" t="n">
-        <v>0.06771062317752044</v>
+        <v>0.08426755770168746</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4054822920698812</v>
+        <v>0.9199555479670994</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>0.1468521620487998</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O47" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="T47" t="n">
         <v>0.92</v>
       </c>
-      <c r="S47" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0.01666666666666667</v>
-      </c>
       <c r="U47" t="n">
-        <v>0.008333333333333333</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="48">
@@ -3821,28 +3927,28 @@
         <v>0.000292205420410548</v>
       </c>
       <c r="H48" t="n">
+        <v>0.9655172413793102</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J48" t="n">
         <v>0.9145299145299146</v>
       </c>
-      <c r="I48" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" t="n">
         <v>24</v>
       </c>
-      <c r="M48" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -3857,10 +3963,16 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>0.7</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="49">
@@ -3883,55 +3995,61 @@
         <v>2001</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1195659958439588</v>
+        <v>0.03714612877531491</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0009349436569170327</v>
+        <v>0.6163617227386412</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>0.0622231937242497</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="O49" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.08333333333333333</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0.01666666666666667</v>
+        <v>0.96</v>
       </c>
       <c r="U49" t="n">
-        <v>0.008333333333333333</v>
+        <v>0.7</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="50">
@@ -3954,55 +4072,61 @@
         <v>2002</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4583333333333334</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="F50" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4757245492139788</v>
+        <v>0.5536229445150034</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5448897249792384</v>
+        <v>0.4295940390947498</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J50" t="n">
-        <v>13</v>
+        <v>0.4934466123531245</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1333333333333333</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O50" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.0625</v>
       </c>
       <c r="R50" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.1625</v>
+        <v>0.625</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1083333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U50" t="n">
-        <v>0.05416666666666667</v>
+        <v>0.1875</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.0625</v>
       </c>
     </row>
     <row r="51">
@@ -4025,55 +4149,61 @@
         <v>2002</v>
       </c>
       <c r="E51" t="n">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="G51" t="n">
-        <v>0.07180640826809585</v>
+        <v>0.07180272878626004</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1848486033749054</v>
+        <v>0.2792022792022792</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J51" t="n">
-        <v>9</v>
+        <v>0.1741254673547568</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M51" t="n">
-        <v>0.1818181818181818</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O51" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
-        <v>0.1125</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="T51" t="n">
-        <v>0.07500000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="U51" t="n">
-        <v>0.03750000000000001</v>
+        <v>0.7625</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.8416666666666667</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0.9208333333333334</v>
       </c>
     </row>
     <row r="52">
@@ -4096,55 +4226,61 @@
         <v>2002</v>
       </c>
       <c r="E52" t="n">
-        <v>0.04166666666666669</v>
+        <v>0.04166666666666663</v>
       </c>
       <c r="F52" t="n">
-        <v>0.04</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1641695648431778</v>
+        <v>0.1595597267150879</v>
       </c>
       <c r="H52" t="n">
-        <v>0.05124238878488541</v>
+        <v>0.8917864561080933</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>0.03496183454990387</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0.07692307692307693</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O52" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>0.3</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="T52" t="n">
-        <v>0.2</v>
+        <v>0.92</v>
       </c>
       <c r="U52" t="n">
-        <v>0.1</v>
+        <v>0.7124999999999999</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.8083333333333333</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.9041666666666667</v>
       </c>
     </row>
     <row r="53">
@@ -4167,54 +4303,60 @@
         <v>2002</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4166666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="F53" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.4540818066676219</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1468521620487998</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.5146742278905792</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>14</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>10</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="G53" t="n">
-        <v>0.3957525842271876</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.08635327756783583</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" t="n">
-        <v>14</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>10</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="R53" t="n">
+      <c r="T53" t="n">
         <v>0.44</v>
       </c>
-      <c r="S53" t="n">
+      <c r="U53" t="n">
         <v>0.175</v>
       </c>
-      <c r="T53" t="n">
+      <c r="V53" t="n">
         <v>0.1166666666666667</v>
       </c>
-      <c r="U53" t="n">
+      <c r="W53" t="n">
         <v>0.05833333333333334</v>
       </c>
     </row>
@@ -4247,46 +4389,52 @@
         <v>0.2126371912881646</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.9145299145299146</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2001</v>
       </c>
       <c r="J54" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M54" t="n">
-        <v>0.07692307692307693</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O54" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>0.3</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="T54" t="n">
-        <v>0.2</v>
+        <v>0.76</v>
       </c>
       <c r="U54" t="n">
-        <v>0.1</v>
+        <v>0.7625</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.8416666666666667</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.9208333333333334</v>
       </c>
     </row>
     <row r="55">
@@ -4309,55 +4457,61 @@
         <v>2002</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7083333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="F55" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.05001800835805292</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.0622231937242497</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.1018875259007074</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>10</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>14</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U55" t="n">
         <v>0.125</v>
       </c>
-      <c r="G55" t="n">
-        <v>0.1026603154118692</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.03830964192992885</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" t="n">
-        <v>7</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>17</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0.2916666666666667</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0.08750000000000001</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0.05833333333333334</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0.02916666666666667</v>
+      <c r="V55" t="n">
+        <v>0.08333333333333334</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.04166666666666667</v>
       </c>
     </row>
     <row r="56">
@@ -4380,56 +4534,32 @@
         <v>2008</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5763888888888888</v>
+        <v>0.4930555555555556</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7461318204821494</v>
+        <v>0.6596023405941883</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5269514292019705</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.0004238894723492777</v>
-      </c>
-      <c r="I56" t="n">
-        <v>15</v>
-      </c>
+        <v>0.5949789787154234</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
-        <v>7</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" t="n">
-        <v>2</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.7894736842105263</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0.6818181818181818</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0.2770833333333333</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0.2055555555555555</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0.1340277777777778</v>
-      </c>
+        <v>2.095342901271278e-05</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4451,56 +4581,32 @@
         <v>2008</v>
       </c>
       <c r="E57" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.4236111111111111</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6829166666666667</v>
+        <v>0.6675</v>
       </c>
       <c r="G57" t="n">
-        <v>0.624008</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6291559999999999</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>9</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4522,56 +4628,32 @@
         <v>2008</v>
       </c>
       <c r="E58" t="n">
-        <v>0.5069444444444444</v>
+        <v>0.5659722222222222</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6754186246867168</v>
+        <v>0.7523041134590047</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6322618722915649</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.0005854230257682502</v>
-      </c>
-      <c r="I58" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6336380839347839</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
-        <v>9</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.001106431591324508</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4593,56 +4675,32 @@
         <v>2008</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4652777777777778</v>
+        <v>0.4375</v>
       </c>
       <c r="F59" t="n">
-        <v>0.663849557608938</v>
+        <v>0.6714975519756825</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5895138386480303</v>
-      </c>
-      <c r="H59" t="n">
-        <v>6.758511167435938e-06</v>
-      </c>
-      <c r="I59" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6166151047994155</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>9</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N59" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0.1</v>
-      </c>
+        <v>2.34390353308865e-06</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4672,48 +4730,24 @@
       <c r="G60" t="n">
         <v>0.64</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>16</v>
-      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>9</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4735,56 +4769,32 @@
         <v>2008</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4375</v>
+        <v>0.5069444444444444</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6164975491438087</v>
+        <v>0.6792103148077413</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6397414400281456</v>
-      </c>
-      <c r="H61" t="n">
-        <v>4.066190212334127e-07</v>
-      </c>
-      <c r="I61" t="n">
-        <v>16</v>
-      </c>
+        <v>0.6389830189761644</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
-        <v>9</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N61" t="n">
-        <v>1</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0.1</v>
-      </c>
+        <v>8.103915832325728e-07</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4806,54 +4816,60 @@
         <v>2009</v>
       </c>
       <c r="E62" t="n">
-        <v>0.5902777777777778</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7317095736389214</v>
+        <v>0.6370509014012303</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4113046110193712</v>
+        <v>0.5073098927030608</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0009987528090520381</v>
+        <v>2.095342901271278e-05</v>
       </c>
       <c r="I62" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.001969129684745444</v>
+      </c>
+      <c r="K62" t="n">
         <v>16</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>9</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
       <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N62" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" t="n">
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
         <v>0.64</v>
       </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
       <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
         <v>0.64</v>
       </c>
-      <c r="S62" t="n">
+      <c r="U62" t="n">
         <v>0.3</v>
       </c>
-      <c r="T62" t="n">
+      <c r="V62" t="n">
         <v>0.2</v>
       </c>
-      <c r="U62" t="n">
+      <c r="W62" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4877,54 +4893,60 @@
         <v>2009</v>
       </c>
       <c r="E63" t="n">
-        <v>0.5208333333333333</v>
+        <v>0.607638888888889</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6383482142857142</v>
+        <v>0.6909456168831168</v>
       </c>
       <c r="G63" t="n">
-        <v>0.593212</v>
+        <v>0.5986439999999998</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>16</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>9</v>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
       <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N63" t="n">
-        <v>1</v>
-      </c>
-      <c r="O63" t="n">
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
         <v>0.64</v>
       </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>1</v>
-      </c>
       <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
         <v>0.64</v>
       </c>
-      <c r="S63" t="n">
+      <c r="U63" t="n">
         <v>0.3</v>
       </c>
-      <c r="T63" t="n">
+      <c r="V63" t="n">
         <v>0.2</v>
       </c>
-      <c r="U63" t="n">
+      <c r="W63" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4948,55 +4970,61 @@
         <v>2009</v>
       </c>
       <c r="E64" t="n">
-        <v>0.5347222222222222</v>
+        <v>0.625</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6652778843057228</v>
+        <v>0.6911767766547178</v>
       </c>
       <c r="G64" t="n">
-        <v>0.6223048567771912</v>
+        <v>0.6291800141334534</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0006677798228338361</v>
+        <v>0.001106431591324508</v>
       </c>
       <c r="I64" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.002162893069908023</v>
+      </c>
+      <c r="K64" t="n">
         <v>16</v>
       </c>
-      <c r="J64" t="n">
-        <v>8</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M64" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R64" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U64" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="65">
@@ -5019,55 +5047,61 @@
         <v>2009</v>
       </c>
       <c r="E65" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.3680555555555556</v>
       </c>
       <c r="F65" t="n">
-        <v>0.6603090379935346</v>
+        <v>0.5808906214427652</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5095793659237123</v>
+        <v>0.6249560463337027</v>
       </c>
       <c r="H65" t="n">
-        <v>0.000106223273925163</v>
+        <v>2.34390353308865e-06</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J65" t="n">
+        <v>3.976776466115631e-07</v>
+      </c>
+      <c r="K65" t="n">
+        <v>15</v>
+      </c>
+      <c r="L65" t="n">
         <v>9</v>
       </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
       <c r="M65" t="n">
-        <v>0.7804878048780488</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="R65" t="n">
-        <v>0.64</v>
+        <v>0.0625</v>
       </c>
       <c r="S65" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="U65" t="n">
-        <v>0.1</v>
+        <v>0.34375</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0.15625</v>
       </c>
     </row>
     <row r="66">
@@ -5102,42 +5136,48 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>16</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>9</v>
       </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
       <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
         <v>0.64</v>
       </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1</v>
-      </c>
       <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
         <v>0.64</v>
       </c>
-      <c r="S66" t="n">
+      <c r="U66" t="n">
         <v>0.3</v>
       </c>
-      <c r="T66" t="n">
+      <c r="V66" t="n">
         <v>0.2</v>
       </c>
-      <c r="U66" t="n">
+      <c r="W66" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5161,55 +5201,61 @@
         <v>2009</v>
       </c>
       <c r="E67" t="n">
-        <v>0.6041666666666667</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6997313140076298</v>
+        <v>0.6596410192358082</v>
       </c>
       <c r="G67" t="n">
-        <v>0.6367494291863808</v>
+        <v>0.63989224017819</v>
       </c>
       <c r="H67" t="n">
-        <v>1.573236477062979e-05</v>
+        <v>8.103915832325728e-07</v>
       </c>
       <c r="I67" t="n">
-        <v>14</v>
+        <v>2008</v>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>1.074627012688665e-05</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="L67" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M67" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P67" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="R67" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.2541666666666667</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0.2111111111111111</v>
+        <v>0.64</v>
       </c>
       <c r="U67" t="n">
-        <v>0.1680555555555556</v>
+        <v>0.3</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="68">
@@ -5232,55 +5278,61 @@
         <v>2010</v>
       </c>
       <c r="E68" t="n">
-        <v>0.5800000000000001</v>
+        <v>0.3866666666666667</v>
       </c>
       <c r="F68" t="n">
-        <v>0.524963768115942</v>
+        <v>0.4275751041483307</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5030900380759665</v>
+        <v>0.5236534804223293</v>
       </c>
       <c r="H68" t="n">
-        <v>0.989730736166938</v>
+        <v>0.001969129684745444</v>
       </c>
       <c r="I68" t="n">
-        <v>7</v>
+        <v>2009</v>
       </c>
       <c r="J68" t="n">
-        <v>7</v>
+        <v>0.01939288522046403</v>
       </c>
       <c r="K68" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L68" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M68" t="n">
-        <v>0.5833333333333334</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U68" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0.3166666666666667</v>
+      <c r="V68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="69">
@@ -5303,54 +5355,60 @@
         <v>2010</v>
       </c>
       <c r="E69" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F69" t="n">
-        <v>0.5287121212121212</v>
+        <v>0.4516666666666667</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3544079999999999</v>
+        <v>0.373884</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K69" t="n">
         <v>10</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>15</v>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
       <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N69" t="n">
-        <v>1</v>
-      </c>
-      <c r="O69" t="n">
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
         <v>0.4</v>
       </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>1</v>
-      </c>
       <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
         <v>0.4</v>
       </c>
-      <c r="S69" t="n">
+      <c r="U69" t="n">
         <v>0.3</v>
       </c>
-      <c r="T69" t="n">
+      <c r="V69" t="n">
         <v>0.2</v>
       </c>
-      <c r="U69" t="n">
+      <c r="W69" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5374,55 +5432,61 @@
         <v>2010</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4633333333333333</v>
+        <v>0.4066666666666667</v>
       </c>
       <c r="F70" t="n">
-        <v>0.451623661426293</v>
+        <v>0.4251940197408969</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3740614056587219</v>
+        <v>0.3805781602859497</v>
       </c>
       <c r="H70" t="n">
-        <v>0.002154259476810694</v>
+        <v>0.002162893069908023</v>
       </c>
       <c r="I70" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.001872273976914585</v>
+      </c>
+      <c r="K70" t="n">
         <v>9</v>
       </c>
-      <c r="J70" t="n">
-        <v>12</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1</v>
-      </c>
       <c r="L70" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M70" t="n">
-        <v>0.5806451612903226</v>
+        <v>1</v>
       </c>
       <c r="N70" t="n">
+        <v>2</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="P70" t="n">
         <v>0.9</v>
       </c>
-      <c r="O70" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="P70" t="n">
+      <c r="Q70" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="R70" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.48</v>
-      </c>
       <c r="S70" t="n">
-        <v>0.31</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T70" t="n">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="U70" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.1766666666666667</v>
       </c>
     </row>
     <row r="71">
@@ -5445,55 +5509,61 @@
         <v>2010</v>
       </c>
       <c r="E71" t="n">
-        <v>0.5733333333333334</v>
+        <v>0.46</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4579013143719026</v>
+        <v>0.4095672383172383</v>
       </c>
       <c r="G71" t="n">
-        <v>0.3738023318957465</v>
+        <v>0.4452204748286615</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1000664228085696</v>
+        <v>3.976776466115631e-07</v>
       </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J71" t="n">
-        <v>10</v>
+        <v>1.59871938234418e-10</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L71" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M71" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>0.5</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.375</v>
       </c>
       <c r="R71" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="S71" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.36</v>
       </c>
       <c r="U71" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.37</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="72">
@@ -5516,54 +5586,60 @@
         <v>2010</v>
       </c>
       <c r="E72" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="F72" t="n">
-        <v>0.3800000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="G72" t="n">
-        <v>0.5174561747230945</v>
+        <v>0.4</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>10</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>15</v>
       </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
       <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N72" t="n">
-        <v>1</v>
-      </c>
-      <c r="O72" t="n">
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
         <v>0.4</v>
       </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>1</v>
-      </c>
       <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
         <v>0.4</v>
       </c>
-      <c r="S72" t="n">
+      <c r="U72" t="n">
         <v>0.3</v>
       </c>
-      <c r="T72" t="n">
+      <c r="V72" t="n">
         <v>0.2</v>
       </c>
-      <c r="U72" t="n">
+      <c r="W72" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5587,55 +5663,61 @@
         <v>2010</v>
       </c>
       <c r="E73" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5533333333333332</v>
       </c>
       <c r="F73" t="n">
-        <v>0.3986367880485527</v>
+        <v>0.4893393596950603</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3995650544502595</v>
+        <v>0.3990590730759576</v>
       </c>
       <c r="H73" t="n">
-        <v>1.231026478560298e-05</v>
+        <v>1.074627012688665e-05</v>
       </c>
       <c r="I73" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1.57490417645354e-05</v>
+      </c>
+      <c r="K73" t="n">
         <v>10</v>
       </c>
-      <c r="J73" t="n">
-        <v>14</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M73" t="n">
-        <v>0.5882352941176471</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R73" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0.28</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T73" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.48</v>
       </c>
       <c r="U73" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.26</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
     <row r="74">
@@ -5658,55 +5740,61 @@
         <v>2011</v>
       </c>
       <c r="E74" t="n">
-        <v>0.74</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7347527706734868</v>
+        <v>0.7770292207792208</v>
       </c>
       <c r="G74" t="n">
-        <v>0.211632995105019</v>
+        <v>0.2466167777023096</v>
       </c>
       <c r="H74" t="n">
-        <v>0.290971252672042</v>
+        <v>0.01939288522046403</v>
       </c>
       <c r="I74" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J74" t="n">
-        <v>8</v>
+        <v>0.4971893896919169</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L74" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M74" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W74" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T74" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="75">
@@ -5729,55 +5817,61 @@
         <v>2011</v>
       </c>
       <c r="E75" t="n">
-        <v>0.78</v>
+        <v>0.7666666666666666</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7494857430151548</v>
+        <v>0.6856746031746032</v>
       </c>
       <c r="G75" t="n">
-        <v>0.1893035912855366</v>
+        <v>0.1980980936519386</v>
       </c>
       <c r="H75" t="n">
-        <v>0.210067349666629</v>
+        <v>0.02</v>
       </c>
       <c r="I75" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.3570521197805805</v>
+      </c>
+      <c r="K75" t="n">
         <v>10</v>
       </c>
-      <c r="J75" t="n">
-        <v>8</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
       <c r="L75" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M75" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R75" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0.16</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U75" t="n">
-        <v>0.05333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="76">
@@ -5800,55 +5894,61 @@
         <v>2011</v>
       </c>
       <c r="E76" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.6866666666666666</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7159967320261438</v>
+        <v>0.5870549333707228</v>
       </c>
       <c r="G76" t="n">
-        <v>0.2143297344446182</v>
+        <v>0.2594301402568817</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1742832213640213</v>
+        <v>0.001872273976914585</v>
       </c>
       <c r="I76" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J76" t="n">
-        <v>4</v>
+        <v>0.08724962174892426</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L76" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M76" t="n">
-        <v>0.7272727272727273</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V76" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0.2133333333333334</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0.2066666666666667</v>
+      <c r="W76" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="77">
@@ -5871,55 +5971,61 @@
         <v>2011</v>
       </c>
       <c r="E77" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="F77" t="n">
-        <v>0.7341033966033966</v>
+        <v>0.7600595238095238</v>
       </c>
       <c r="G77" t="n">
-        <v>0.2545645512652898</v>
+        <v>0.1960012633099031</v>
       </c>
       <c r="H77" t="n">
-        <v>0.01054320016443355</v>
+        <v>1.59871938234418e-10</v>
       </c>
       <c r="I77" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.6869635807000314</v>
+      </c>
+      <c r="K77" t="n">
         <v>10</v>
       </c>
-      <c r="J77" t="n">
-        <v>6</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
       <c r="L77" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M77" t="n">
-        <v>0.7692307692307693</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
         <v>0.4</v>
       </c>
       <c r="R77" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="T77" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="U77" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="78">
@@ -5942,54 +6048,60 @@
         <v>2011</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5933333333333333</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5166666666666666</v>
       </c>
       <c r="G78" t="n">
-        <v>0.3226109650474491</v>
+        <v>0.3051634487541793</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
         <v>10</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>15</v>
       </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
       <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N78" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" t="n">
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
         <v>0.4</v>
       </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
       <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
         <v>0.4</v>
       </c>
-      <c r="S78" t="n">
+      <c r="U78" t="n">
         <v>0.3</v>
       </c>
-      <c r="T78" t="n">
+      <c r="V78" t="n">
         <v>0.2</v>
       </c>
-      <c r="U78" t="n">
+      <c r="W78" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -6013,55 +6125,61 @@
         <v>2011</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8866666666666667</v>
+        <v>0.7133333333333334</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8217748917748917</v>
+        <v>0.6129856693014587</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3115666961237586</v>
+        <v>0.2614105721953216</v>
       </c>
       <c r="H79" t="n">
-        <v>0.001923026225120567</v>
+        <v>1.57490417645354e-05</v>
       </c>
       <c r="I79" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>0.08790260362874189</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L79" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M79" t="n">
-        <v>0.8181818181818182</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>0.75</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W79" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0.11</v>
       </c>
     </row>
     <row r="80">
@@ -6084,55 +6202,61 @@
         <v>2012</v>
       </c>
       <c r="E80" t="n">
-        <v>0.7666666666666666</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="F80" t="n">
-        <v>0.7755602240896359</v>
+        <v>0.7404636591478696</v>
       </c>
       <c r="G80" t="n">
-        <v>0.244125149440979</v>
+        <v>0.2380812482757207</v>
       </c>
       <c r="H80" t="n">
-        <v>0.495036289551843</v>
+        <v>0.4971893896919169</v>
       </c>
       <c r="I80" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.4880514104121095</v>
+      </c>
+      <c r="K80" t="n">
+        <v>6</v>
+      </c>
+      <c r="L80" t="n">
+        <v>6</v>
+      </c>
+      <c r="M80" t="n">
+        <v>4</v>
+      </c>
+      <c r="N80" t="n">
         <v>9</v>
       </c>
-      <c r="J80" t="n">
-        <v>8</v>
-      </c>
-      <c r="K80" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" t="n">
-        <v>7</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0.9</v>
-      </c>
       <c r="O80" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="P80" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="R80" t="n">
-        <v>0.64</v>
+        <v>0.4</v>
       </c>
       <c r="S80" t="n">
-        <v>0.23</v>
+        <v>0.4</v>
       </c>
       <c r="T80" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="U80" t="n">
-        <v>0.1433333333333333</v>
+        <v>0.4</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="81">
@@ -6155,55 +6279,61 @@
         <v>2012</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9400000000000001</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9187698412698412</v>
+        <v>0.8495337995337995</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1436554446475785</v>
+        <v>0.1852112385712333</v>
       </c>
       <c r="H81" t="n">
-        <v>0.4495479177068525</v>
+        <v>0.3570521197805805</v>
       </c>
       <c r="I81" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0.5213560531412951</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L81" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M81" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="O81" t="n">
-        <v>0.9</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="P81" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="R81" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0.09</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T81" t="n">
-        <v>0.09333333333333335</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U81" t="n">
-        <v>0.09666666666666668</v>
+        <v>0.22</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0.07333333333333333</v>
       </c>
     </row>
     <row r="82">
@@ -6226,55 +6356,61 @@
         <v>2012</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9503174603174603</v>
+        <v>0.7922527472527472</v>
       </c>
       <c r="G82" t="n">
-        <v>0.09549164026975632</v>
+        <v>0.1798732876777649</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3973187506198883</v>
+        <v>0.08724962174892426</v>
       </c>
       <c r="I82" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0.3382894098758698</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L82" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M82" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="O82" t="n">
-        <v>0.9</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="P82" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R82" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>0.09</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T82" t="n">
-        <v>0.09333333333333335</v>
+        <v>0.48</v>
       </c>
       <c r="U82" t="n">
-        <v>0.09666666666666668</v>
+        <v>0.26</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
     <row r="83">
@@ -6297,55 +6433,61 @@
         <v>2012</v>
       </c>
       <c r="E83" t="n">
-        <v>0.92</v>
+        <v>0.8533333333333333</v>
       </c>
       <c r="F83" t="n">
-        <v>0.9033974358974358</v>
+        <v>0.8237554112554112</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1253949292607568</v>
+        <v>0.164742186526448</v>
       </c>
       <c r="H83" t="n">
-        <v>0.4856115797517387</v>
+        <v>0.6869635807000314</v>
       </c>
       <c r="I83" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J83" t="n">
-        <v>2</v>
+        <v>0.4719219990701075</v>
       </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L83" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M83" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="N83" t="n">
-        <v>0.8</v>
+        <v>12</v>
       </c>
       <c r="O83" t="n">
-        <v>0.8</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="P83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S83" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S83" t="n">
-        <v>0.18</v>
-      </c>
       <c r="T83" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.68</v>
       </c>
       <c r="U83" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.41</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0.4400000000000001</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0.47</v>
       </c>
     </row>
     <row r="84">
@@ -6368,55 +6510,61 @@
         <v>2012</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.71</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7298245614035088</v>
+        <v>0.5947619047619047</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1704497658054301</v>
+        <v>0.2632196656657813</v>
       </c>
       <c r="H84" t="n">
-        <v>0.5836298932384343</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.7243816254416963</v>
+      </c>
+      <c r="K84" t="n">
         <v>10</v>
       </c>
-      <c r="J84" t="n">
-        <v>9</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
       <c r="L84" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M84" t="n">
-        <v>0.6896551724137931</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="R84" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0.18</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>0.12</v>
+        <v>0.4</v>
       </c>
       <c r="U84" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="85">
@@ -6439,55 +6587,61 @@
         <v>2012</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9733333333333334</v>
+        <v>0.8533333333333333</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9651515151515151</v>
+        <v>0.8597394220846233</v>
       </c>
       <c r="G85" t="n">
-        <v>0.1374418432978003</v>
+        <v>0.1385942945331236</v>
       </c>
       <c r="H85" t="n">
-        <v>0.01095831572786022</v>
+        <v>0.08790260362874189</v>
       </c>
       <c r="I85" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.4819285066319294</v>
+      </c>
+      <c r="K85" t="n">
         <v>10</v>
       </c>
-      <c r="J85" t="n">
-        <v>2</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
       <c r="L85" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M85" t="n">
-        <v>0.9090909090909091</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O85" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="R85" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>0.04</v>
+        <v>0.8</v>
       </c>
       <c r="T85" t="n">
-        <v>0.02666666666666667</v>
+        <v>0.52</v>
       </c>
       <c r="U85" t="n">
-        <v>0.01333333333333333</v>
+        <v>0.24</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0.08000000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -6523,7 +6677,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.645</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="3">
@@ -6533,7 +6687,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.732</v>
+        <v>0.753</v>
       </c>
     </row>
     <row r="4">
@@ -6543,7 +6697,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.66</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="5">
@@ -6553,7 +6707,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.645</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="6">
@@ -6573,7 +6727,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.742</v>
+        <v>0.774</v>
       </c>
     </row>
   </sheetData>
@@ -6649,25 +6803,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.645</v>
+        <v>0.599</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.429</v>
       </c>
       <c r="E2" t="n">
-        <v>0.986</v>
+        <v>0.767</v>
       </c>
       <c r="F2" t="n">
-        <v>0.425</v>
+        <v>0.338</v>
       </c>
       <c r="G2" t="n">
-        <v>0.014</v>
+        <v>0.233</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.743</v>
       </c>
       <c r="I2" t="n">
-        <v>0.148</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="3">
@@ -6682,25 +6836,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.732</v>
+        <v>0.753</v>
       </c>
       <c r="D3" t="n">
-        <v>0.658</v>
+        <v>0.447</v>
       </c>
       <c r="E3" t="n">
-        <v>0.971</v>
+        <v>0.752</v>
       </c>
       <c r="F3" t="n">
-        <v>0.546</v>
+        <v>0.36</v>
       </c>
       <c r="G3" t="n">
-        <v>0.029</v>
+        <v>0.248</v>
       </c>
       <c r="H3" t="n">
-        <v>0.463</v>
+        <v>0.615</v>
       </c>
       <c r="I3" t="n">
-        <v>0.116</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="4">
@@ -6715,25 +6869,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.66</v>
+        <v>0.641</v>
       </c>
       <c r="D4" t="n">
-        <v>0.579</v>
+        <v>0.347</v>
       </c>
       <c r="E4" t="n">
-        <v>0.957</v>
+        <v>0.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.461</v>
+        <v>0.294</v>
       </c>
       <c r="G4" t="n">
-        <v>0.043</v>
+        <v>0.4</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.536</v>
       </c>
       <c r="I4" t="n">
-        <v>0.147</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="5">
@@ -6748,25 +6902,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.645</v>
+        <v>0.636</v>
       </c>
       <c r="D5" t="n">
-        <v>0.593</v>
+        <v>0.389</v>
       </c>
       <c r="E5" t="n">
-        <v>0.886</v>
+        <v>0.667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.544</v>
+        <v>0.421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.114</v>
+        <v>0.333</v>
       </c>
       <c r="H5" t="n">
-        <v>0.435</v>
+        <v>0.632</v>
       </c>
       <c r="I5" t="n">
-        <v>0.178</v>
+        <v>0.393</v>
       </c>
     </row>
     <row r="6">
@@ -6784,22 +6938,22 @@
         <v>0.725</v>
       </c>
       <c r="D6" t="n">
-        <v>0.723</v>
+        <v>0.452</v>
       </c>
       <c r="E6" t="n">
-        <v>0.971</v>
+        <v>0.783</v>
       </c>
       <c r="F6" t="n">
-        <v>0.609</v>
+        <v>0.346</v>
       </c>
       <c r="G6" t="n">
-        <v>0.029</v>
+        <v>0.217</v>
       </c>
       <c r="H6" t="n">
-        <v>0.532</v>
+        <v>0.635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.129</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -6814,25 +6968,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.742</v>
+        <v>0.774</v>
       </c>
       <c r="D7" t="n">
-        <v>0.754</v>
+        <v>0.571</v>
       </c>
       <c r="E7" t="n">
-        <v>0.971</v>
+        <v>0.956</v>
       </c>
       <c r="F7" t="n">
-        <v>0.656</v>
+        <v>0.441</v>
       </c>
       <c r="G7" t="n">
-        <v>0.029</v>
+        <v>0.044</v>
       </c>
       <c r="H7" t="n">
-        <v>0.421</v>
+        <v>0.511</v>
       </c>
       <c r="I7" t="n">
-        <v>0.107</v>
+        <v>0.137</v>
       </c>
     </row>
   </sheetData>
@@ -6878,7 +7032,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.645</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="3">
@@ -6888,7 +7042,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.732</v>
+        <v>0.753</v>
       </c>
     </row>
     <row r="4">
@@ -6898,7 +7052,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.66</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="5">
@@ -6908,7 +7062,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.645</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="6">
@@ -6928,7 +7082,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.742</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="8">
@@ -6943,7 +7097,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.601</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="9">
@@ -6953,7 +7107,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.713</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -6963,7 +7117,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.655</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="11">
@@ -6973,7 +7127,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.654</v>
+        <v>0.621</v>
       </c>
     </row>
     <row r="12">
@@ -6983,7 +7137,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.719</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="13">
@@ -6993,7 +7147,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.613</v>
+        <v>0.592</v>
       </c>
     </row>
   </sheetData>
